--- a/(枠)◯年度一式/産廃原簿.xlsx
+++ b/(枠)◯年度一式/産廃原簿.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\layhi\OneDrive\ドキュメント\日報月報他\(枠)◯年度一式\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61B81D99-F037-4FE7-8AA0-39DB19912D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D51A5CA-F132-48AB-BAA0-9000D6CBC30C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12555" yWindow="660" windowWidth="16245" windowHeight="14565" tabRatio="942" firstSheet="13" activeTab="24" xr2:uid="{5AD5A155-4AC2-4929-A579-33332D170D49}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="20100" windowHeight="14565" tabRatio="942" firstSheet="10" activeTab="24" xr2:uid="{5AD5A155-4AC2-4929-A579-33332D170D49}"/>
   </bookViews>
   <sheets>
     <sheet name="受付04" sheetId="20" r:id="rId1"/>
@@ -1080,13 +1080,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1095,22 +1092,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1129,6 +1117,18 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -1938,7 +1938,7 @@
       <c r="I4" s="25"/>
       <c r="J4" s="25"/>
       <c r="K4" s="25" t="str">
-        <f t="shared" ref="K4:K43" si="2">IF(E4="","",IF(E4="国保中央病院","医療","水産"))</f>
+        <f>IF(E4="","",IF(E4="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       <c r="I5" s="25"/>
       <c r="J5" s="25"/>
       <c r="K5" s="25" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="K5:K43" si="2">IF(E5="","",IF(E5="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -2985,7 +2985,7 @@
       <c r="I48" s="25"/>
       <c r="J48" s="25"/>
       <c r="K48" s="25" t="str">
-        <f t="shared" ref="K48:K87" si="5">IF(E48="","",IF(E48="国保中央病院","医療","水産"))</f>
+        <f>IF(E48="","",IF(E48="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       <c r="I49" s="25"/>
       <c r="J49" s="25"/>
       <c r="K49" s="25" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="K49:K87" si="5">IF(E49="","",IF(E49="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -3902,25 +3902,25 @@
       </c>
     </row>
     <row r="87" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="25">
+      <c r="A87" s="36">
         <v>80</v>
       </c>
-      <c r="B87" s="27"/>
-      <c r="C87" s="25"/>
-      <c r="D87" s="26"/>
+      <c r="B87" s="37"/>
+      <c r="C87" s="36"/>
+      <c r="D87" s="38"/>
       <c r="E87" s="39"/>
-      <c r="F87" s="29"/>
-      <c r="G87" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="H87" s="25" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="I87" s="25"/>
-      <c r="J87" s="25"/>
-      <c r="K87" s="25" t="str">
+      <c r="F87" s="40"/>
+      <c r="G87" s="40" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H87" s="36" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="I87" s="36"/>
+      <c r="J87" s="36"/>
+      <c r="K87" s="36" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -3947,9 +3947,6 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="5">
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="K4:K43 K48:K87" xr:uid="{E10F9F99-950C-435A-8D06-595E78CEEC64}">
-      <formula1>"医療,水産,木くず"</formula1>
-    </dataValidation>
     <dataValidation type="whole" imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I48:J87 I4:J43" xr:uid="{F0C886D5-7DA2-4651-943F-9AE070DC71D3}">
       <formula1>1</formula1>
       <formula2>99999</formula2>
@@ -3960,6 +3957,9 @@
     <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:G43 B48:B87 F48:G87 B4:B43" xr:uid="{F6448C9F-5642-4F58-9F75-08527C7D3626}"/>
     <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="E4:E43 E48:E87" xr:uid="{94CB6721-868A-4DF6-839D-83BD1F741BB5}">
       <formula1>"国保中央病院,道立鬼脇診療所,カムイウイスキー,福士水産㈱,糀谷商店,米田商店"</formula1>
+    </dataValidation>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="K4:K43 K48:K87" xr:uid="{DEF5E9DB-B497-4E71-81F6-3AE6535A8D49}">
+      <formula1>"医療,動植"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -4070,7 +4070,7 @@
       <c r="I4" s="25"/>
       <c r="J4" s="25"/>
       <c r="K4" s="25" t="str">
-        <f t="shared" ref="K4:K43" si="2">IF(E4="","",IF(E4="国保中央病院","医療","水産"))</f>
+        <f>IF(E4="","",IF(E4="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       <c r="I5" s="25"/>
       <c r="J5" s="25"/>
       <c r="K5" s="25" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="K5:K43" si="2">IF(E5="","",IF(E5="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -5117,7 +5117,7 @@
       <c r="I48" s="25"/>
       <c r="J48" s="25"/>
       <c r="K48" s="25" t="str">
-        <f t="shared" ref="K48:K87" si="5">IF(E48="","",IF(E48="国保中央病院","医療","水産"))</f>
+        <f>IF(E48="","",IF(E48="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -5141,7 +5141,7 @@
       <c r="I49" s="25"/>
       <c r="J49" s="25"/>
       <c r="K49" s="25" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="K49:K87" si="5">IF(E49="","",IF(E49="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -6034,25 +6034,25 @@
       </c>
     </row>
     <row r="87" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="25">
+      <c r="A87" s="36">
         <v>80</v>
       </c>
-      <c r="B87" s="27"/>
-      <c r="C87" s="25"/>
-      <c r="D87" s="26"/>
+      <c r="B87" s="37"/>
+      <c r="C87" s="36"/>
+      <c r="D87" s="38"/>
       <c r="E87" s="39"/>
-      <c r="F87" s="29"/>
-      <c r="G87" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="H87" s="25" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="I87" s="25"/>
-      <c r="J87" s="25"/>
-      <c r="K87" s="25" t="str">
+      <c r="F87" s="40"/>
+      <c r="G87" s="40" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H87" s="36" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="I87" s="36"/>
+      <c r="J87" s="36"/>
+      <c r="K87" s="36" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -6079,19 +6079,19 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="5">
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="K4:K43 K48:K87" xr:uid="{668CE25C-CC83-4118-80CB-36CD3FD4A132}">
-      <formula1>"医療,水産,木くず"</formula1>
-    </dataValidation>
-    <dataValidation type="whole" imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I48:J87 I4:J43" xr:uid="{5D574161-E37D-4DFA-9210-09797FD9CB15}">
+    <dataValidation type="whole" imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I48:J87 I4:J43" xr:uid="{85BEBA61-80B3-48D7-884A-26922CEF1FD7}">
       <formula1>1</formula1>
       <formula2>99999</formula2>
     </dataValidation>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C48:C87 C4:C43" xr:uid="{2EDA4B3C-F23B-41CB-9825-352E2372D3C0}">
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C48:C87 C4:C43" xr:uid="{C7A54FF9-E69F-488D-9412-A38347A4FD72}">
       <formula1>"鴛 泊,鬼 脇,沓 形,仙法志"</formula1>
     </dataValidation>
-    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:G43 B48:B87 F48:G87 B4:B43" xr:uid="{CAD570C5-A57F-4F0F-AFE0-20957439096A}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="E4:E43 E48:E87" xr:uid="{E3606E07-B11D-40A5-9C9D-0129C4EE4CDE}">
+    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:G43 B48:B87 F48:G87 B4:B43" xr:uid="{59B9B57A-4FFB-4A52-8931-0E286E747145}"/>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="E4:E43 E48:E87" xr:uid="{AC2001A1-3130-4057-B035-FAC79655288F}">
       <formula1>"国保中央病院,道立鬼脇診療所,カムイウイスキー,福士水産㈱,糀谷商店,米田商店"</formula1>
+    </dataValidation>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="K4:K43 K48:K87" xr:uid="{E8A38895-95DF-49A6-98D0-77700EB002E4}">
+      <formula1>"医療,動植"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -6202,7 +6202,7 @@
       <c r="I4" s="25"/>
       <c r="J4" s="25"/>
       <c r="K4" s="25" t="str">
-        <f t="shared" ref="K4:K43" si="2">IF(E4="","",IF(E4="国保中央病院","医療","水産"))</f>
+        <f>IF(E4="","",IF(E4="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       <c r="I5" s="25"/>
       <c r="J5" s="25"/>
       <c r="K5" s="25" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="K5:K43" si="2">IF(E5="","",IF(E5="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -7249,7 +7249,7 @@
       <c r="I48" s="25"/>
       <c r="J48" s="25"/>
       <c r="K48" s="25" t="str">
-        <f t="shared" ref="K48:K87" si="5">IF(E48="","",IF(E48="国保中央病院","医療","水産"))</f>
+        <f>IF(E48="","",IF(E48="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -7273,7 +7273,7 @@
       <c r="I49" s="25"/>
       <c r="J49" s="25"/>
       <c r="K49" s="25" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="K49:K87" si="5">IF(E49="","",IF(E49="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -8166,25 +8166,25 @@
       </c>
     </row>
     <row r="87" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="25">
+      <c r="A87" s="36">
         <v>80</v>
       </c>
-      <c r="B87" s="27"/>
-      <c r="C87" s="25"/>
-      <c r="D87" s="26"/>
+      <c r="B87" s="37"/>
+      <c r="C87" s="36"/>
+      <c r="D87" s="38"/>
       <c r="E87" s="39"/>
-      <c r="F87" s="29"/>
-      <c r="G87" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="H87" s="25" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="I87" s="25"/>
-      <c r="J87" s="25"/>
-      <c r="K87" s="25" t="str">
+      <c r="F87" s="40"/>
+      <c r="G87" s="40" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H87" s="36" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="I87" s="36"/>
+      <c r="J87" s="36"/>
+      <c r="K87" s="36" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -8211,19 +8211,19 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="5">
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="K4:K43 K48:K87" xr:uid="{97C23737-BAA8-45E9-81FE-9F2ECE696B35}">
-      <formula1>"医療,水産,木くず"</formula1>
-    </dataValidation>
-    <dataValidation type="whole" imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I48:J87 I4:J43" xr:uid="{C53E3B19-50F6-4E98-8495-30C713ACBF79}">
+    <dataValidation type="whole" imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I48:J87 I4:J43" xr:uid="{64948D59-6D24-4B3A-A6C9-9F935F7ED3CB}">
       <formula1>1</formula1>
       <formula2>99999</formula2>
     </dataValidation>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C48:C87 C4:C43" xr:uid="{417F6BBA-92FB-41DD-B012-84F25BE8E5E4}">
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C48:C87 C4:C43" xr:uid="{34C82252-36E0-4CB8-B963-C4B54CB11B36}">
       <formula1>"鴛 泊,鬼 脇,沓 形,仙法志"</formula1>
     </dataValidation>
-    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:G43 B48:B87 F48:G87 B4:B43" xr:uid="{C6AF3F02-8216-4110-BB8C-2A688828D83C}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="E4:E43 E48:E87" xr:uid="{653072E6-FFD6-4D50-B1E9-10192FC5908F}">
+    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:G43 B48:B87 F48:G87 B4:B43" xr:uid="{03E25E33-3AA3-4529-A3B4-841D74C7BCB8}"/>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="E4:E43 E48:E87" xr:uid="{86FBC33D-99BA-4D8F-BE96-142BFDFAFD3D}">
       <formula1>"国保中央病院,道立鬼脇診療所,カムイウイスキー,福士水産㈱,糀谷商店,米田商店"</formula1>
+    </dataValidation>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="K4:K43 K48:K87" xr:uid="{F56A4331-D560-4C87-B9D1-384D62CAAAF3}">
+      <formula1>"医療,動植"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -8334,7 +8334,7 @@
       <c r="I4" s="25"/>
       <c r="J4" s="25"/>
       <c r="K4" s="25" t="str">
-        <f t="shared" ref="K4:K43" si="2">IF(E4="","",IF(E4="国保中央病院","医療","水産"))</f>
+        <f>IF(E4="","",IF(E4="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
       <c r="I5" s="25"/>
       <c r="J5" s="25"/>
       <c r="K5" s="25" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="K5:K43" si="2">IF(E5="","",IF(E5="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -9381,7 +9381,7 @@
       <c r="I48" s="25"/>
       <c r="J48" s="25"/>
       <c r="K48" s="25" t="str">
-        <f t="shared" ref="K48:K87" si="5">IF(E48="","",IF(E48="国保中央病院","医療","水産"))</f>
+        <f>IF(E48="","",IF(E48="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -9405,7 +9405,7 @@
       <c r="I49" s="25"/>
       <c r="J49" s="25"/>
       <c r="K49" s="25" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="K49:K87" si="5">IF(E49="","",IF(E49="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -10298,25 +10298,25 @@
       </c>
     </row>
     <row r="87" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="25">
+      <c r="A87" s="36">
         <v>80</v>
       </c>
-      <c r="B87" s="27"/>
-      <c r="C87" s="25"/>
-      <c r="D87" s="26"/>
+      <c r="B87" s="37"/>
+      <c r="C87" s="36"/>
+      <c r="D87" s="38"/>
       <c r="E87" s="39"/>
-      <c r="F87" s="29"/>
-      <c r="G87" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="H87" s="25" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="I87" s="25"/>
-      <c r="J87" s="25"/>
-      <c r="K87" s="25" t="str">
+      <c r="F87" s="40"/>
+      <c r="G87" s="40" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H87" s="36" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="I87" s="36"/>
+      <c r="J87" s="36"/>
+      <c r="K87" s="36" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -10343,19 +10343,19 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="5">
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="K4:K43 K48:K87" xr:uid="{104078F1-B3D1-4D84-BBDE-3AF16837A699}">
-      <formula1>"医療,水産,木くず"</formula1>
-    </dataValidation>
-    <dataValidation type="whole" imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I48:J87 I4:J43" xr:uid="{831557EE-C55F-408C-821F-2611B47B174D}">
+    <dataValidation type="whole" imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I48:J87 I4:J43" xr:uid="{B68738C8-3BC2-490A-8C10-3F4FDA768278}">
       <formula1>1</formula1>
       <formula2>99999</formula2>
     </dataValidation>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C48:C87 C4:C43" xr:uid="{96C72B5A-7F5A-40F7-8797-F224B5D71BE5}">
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C48:C87 C4:C43" xr:uid="{2DF8F357-A098-463B-A5AA-20E2CE713125}">
       <formula1>"鴛 泊,鬼 脇,沓 形,仙法志"</formula1>
     </dataValidation>
-    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:G43 B48:B87 F48:G87 B4:B43" xr:uid="{ED59EC4C-6269-4AC3-8CE8-93DC92FC464C}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="E4:E43 E48:E87" xr:uid="{0F202BF9-AEC4-4DA3-BFF6-73A1A2E94BD2}">
+    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:G43 B48:B87 F48:G87 B4:B43" xr:uid="{BE8B833B-5A84-4DCE-B4E2-5614A5DB9048}"/>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="E4:E43 E48:E87" xr:uid="{20A738B6-D677-4AC9-96B8-D59BFEA00F93}">
       <formula1>"国保中央病院,道立鬼脇診療所,カムイウイスキー,福士水産㈱,糀谷商店,米田商店"</formula1>
+    </dataValidation>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="K4:K43 K48:K87" xr:uid="{ABFAD6A9-A7F2-4E01-A2A0-0F3398BE860A}">
+      <formula1>"医療,動植"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -10392,11 +10392,11 @@
       <c r="D1" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="65" t="s">
+      <c r="E1" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
       <c r="J1" s="21"/>
       <c r="K1" s="22"/>
     </row>
@@ -10413,16 +10413,16 @@
       <c r="D2" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="59" t="s">
+      <c r="E2" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="61" t="s">
+      <c r="F2" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="62" t="s">
+      <c r="G2" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="63" t="s">
+      <c r="H2" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="55" t="s">
@@ -10431,7 +10431,7 @@
       <c r="J2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="64" t="s">
+      <c r="K2" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -10440,13 +10440,13 @@
       <c r="B3" s="56"/>
       <c r="C3" s="56"/>
       <c r="D3" s="58"/>
-      <c r="E3" s="60"/>
+      <c r="E3" s="63"/>
       <c r="F3" s="56"/>
       <c r="G3" s="58"/>
-      <c r="H3" s="60"/>
+      <c r="H3" s="63"/>
       <c r="I3" s="56"/>
       <c r="J3" s="56"/>
-      <c r="K3" s="64"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="7">
@@ -10659,11 +10659,11 @@
       <c r="D15" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="65" t="s">
+      <c r="E15" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="65"/>
-      <c r="G15" s="65"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="64"/>
       <c r="J15" s="21"/>
       <c r="K15" s="22"/>
     </row>
@@ -10680,16 +10680,16 @@
       <c r="D16" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="59" t="s">
+      <c r="E16" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="61" t="s">
+      <c r="F16" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="62" t="s">
+      <c r="G16" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="63" t="s">
+      <c r="H16" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I16" s="55" t="s">
@@ -10698,7 +10698,7 @@
       <c r="J16" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="64" t="s">
+      <c r="K16" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -10707,13 +10707,13 @@
       <c r="B17" s="56"/>
       <c r="C17" s="56"/>
       <c r="D17" s="58"/>
-      <c r="E17" s="60"/>
+      <c r="E17" s="63"/>
       <c r="F17" s="56"/>
       <c r="G17" s="58"/>
-      <c r="H17" s="60"/>
+      <c r="H17" s="63"/>
       <c r="I17" s="56"/>
       <c r="J17" s="56"/>
-      <c r="K17" s="64"/>
+      <c r="K17" s="60"/>
     </row>
     <row r="18" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7">
@@ -10926,11 +10926,11 @@
       <c r="D29" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E29" s="65" t="s">
+      <c r="E29" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="65"/>
-      <c r="G29" s="65"/>
+      <c r="F29" s="64"/>
+      <c r="G29" s="64"/>
       <c r="J29" s="21"/>
       <c r="K29" s="22"/>
     </row>
@@ -10947,16 +10947,16 @@
       <c r="D30" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E30" s="59" t="s">
+      <c r="E30" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F30" s="61" t="s">
+      <c r="F30" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G30" s="62" t="s">
+      <c r="G30" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="63" t="s">
+      <c r="H30" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I30" s="55" t="s">
@@ -10965,7 +10965,7 @@
       <c r="J30" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K30" s="64" t="s">
+      <c r="K30" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -10974,13 +10974,13 @@
       <c r="B31" s="56"/>
       <c r="C31" s="56"/>
       <c r="D31" s="58"/>
-      <c r="E31" s="60"/>
+      <c r="E31" s="63"/>
       <c r="F31" s="56"/>
       <c r="G31" s="58"/>
-      <c r="H31" s="60"/>
+      <c r="H31" s="63"/>
       <c r="I31" s="56"/>
       <c r="J31" s="56"/>
-      <c r="K31" s="64"/>
+      <c r="K31" s="60"/>
     </row>
     <row r="32" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7">
@@ -11193,11 +11193,11 @@
       <c r="D43" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E43" s="65" t="s">
+      <c r="E43" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="65"/>
-      <c r="G43" s="65"/>
+      <c r="F43" s="64"/>
+      <c r="G43" s="64"/>
       <c r="J43" s="21"/>
       <c r="K43" s="22"/>
     </row>
@@ -11214,16 +11214,16 @@
       <c r="D44" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="59" t="s">
+      <c r="E44" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="61" t="s">
+      <c r="F44" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G44" s="62" t="s">
+      <c r="G44" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H44" s="63" t="s">
+      <c r="H44" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I44" s="55" t="s">
@@ -11232,7 +11232,7 @@
       <c r="J44" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="64" t="s">
+      <c r="K44" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -11241,13 +11241,13 @@
       <c r="B45" s="56"/>
       <c r="C45" s="56"/>
       <c r="D45" s="58"/>
-      <c r="E45" s="60"/>
+      <c r="E45" s="63"/>
       <c r="F45" s="56"/>
       <c r="G45" s="58"/>
-      <c r="H45" s="60"/>
+      <c r="H45" s="63"/>
       <c r="I45" s="56"/>
       <c r="J45" s="56"/>
-      <c r="K45" s="64"/>
+      <c r="K45" s="60"/>
     </row>
     <row r="46" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7">
@@ -11460,11 +11460,11 @@
       <c r="D57" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E57" s="65" t="s">
+      <c r="E57" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="65"/>
-      <c r="G57" s="65"/>
+      <c r="F57" s="64"/>
+      <c r="G57" s="64"/>
       <c r="J57" s="21"/>
       <c r="K57" s="22"/>
     </row>
@@ -11481,16 +11481,16 @@
       <c r="D58" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="59" t="s">
+      <c r="E58" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F58" s="61" t="s">
+      <c r="F58" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G58" s="62" t="s">
+      <c r="G58" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H58" s="63" t="s">
+      <c r="H58" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I58" s="55" t="s">
@@ -11499,7 +11499,7 @@
       <c r="J58" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K58" s="64" t="s">
+      <c r="K58" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -11508,13 +11508,13 @@
       <c r="B59" s="56"/>
       <c r="C59" s="56"/>
       <c r="D59" s="58"/>
-      <c r="E59" s="60"/>
+      <c r="E59" s="63"/>
       <c r="F59" s="56"/>
       <c r="G59" s="58"/>
-      <c r="H59" s="60"/>
+      <c r="H59" s="63"/>
       <c r="I59" s="56"/>
       <c r="J59" s="56"/>
-      <c r="K59" s="64"/>
+      <c r="K59" s="60"/>
     </row>
     <row r="60" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="7">
@@ -11727,11 +11727,11 @@
       <c r="D71" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E71" s="65" t="s">
+      <c r="E71" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F71" s="65"/>
-      <c r="G71" s="65"/>
+      <c r="F71" s="64"/>
+      <c r="G71" s="64"/>
       <c r="J71" s="21"/>
       <c r="K71" s="22"/>
     </row>
@@ -11748,16 +11748,16 @@
       <c r="D72" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E72" s="59" t="s">
+      <c r="E72" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F72" s="61" t="s">
+      <c r="F72" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G72" s="62" t="s">
+      <c r="G72" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H72" s="63" t="s">
+      <c r="H72" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I72" s="55" t="s">
@@ -11766,7 +11766,7 @@
       <c r="J72" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K72" s="64" t="s">
+      <c r="K72" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -11775,13 +11775,13 @@
       <c r="B73" s="56"/>
       <c r="C73" s="56"/>
       <c r="D73" s="58"/>
-      <c r="E73" s="60"/>
+      <c r="E73" s="63"/>
       <c r="F73" s="56"/>
       <c r="G73" s="58"/>
-      <c r="H73" s="60"/>
+      <c r="H73" s="63"/>
       <c r="I73" s="56"/>
       <c r="J73" s="56"/>
-      <c r="K73" s="64"/>
+      <c r="K73" s="60"/>
     </row>
     <row r="74" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="7">
@@ -11994,11 +11994,11 @@
       <c r="D85" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E85" s="65" t="s">
+      <c r="E85" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F85" s="65"/>
-      <c r="G85" s="65"/>
+      <c r="F85" s="64"/>
+      <c r="G85" s="64"/>
       <c r="J85" s="21"/>
       <c r="K85" s="22"/>
     </row>
@@ -12015,16 +12015,16 @@
       <c r="D86" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E86" s="59" t="s">
+      <c r="E86" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F86" s="61" t="s">
+      <c r="F86" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G86" s="62" t="s">
+      <c r="G86" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H86" s="63" t="s">
+      <c r="H86" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I86" s="55" t="s">
@@ -12033,7 +12033,7 @@
       <c r="J86" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K86" s="64" t="s">
+      <c r="K86" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -12042,13 +12042,13 @@
       <c r="B87" s="56"/>
       <c r="C87" s="56"/>
       <c r="D87" s="58"/>
-      <c r="E87" s="60"/>
+      <c r="E87" s="63"/>
       <c r="F87" s="56"/>
       <c r="G87" s="58"/>
-      <c r="H87" s="60"/>
+      <c r="H87" s="63"/>
       <c r="I87" s="56"/>
       <c r="J87" s="56"/>
-      <c r="K87" s="64"/>
+      <c r="K87" s="60"/>
     </row>
     <row r="88" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="7">
@@ -12261,11 +12261,11 @@
       <c r="D99" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E99" s="65" t="s">
+      <c r="E99" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F99" s="65"/>
-      <c r="G99" s="65"/>
+      <c r="F99" s="64"/>
+      <c r="G99" s="64"/>
       <c r="J99" s="21"/>
       <c r="K99" s="22"/>
     </row>
@@ -12282,16 +12282,16 @@
       <c r="D100" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E100" s="59" t="s">
+      <c r="E100" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F100" s="61" t="s">
+      <c r="F100" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G100" s="62" t="s">
+      <c r="G100" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H100" s="63" t="s">
+      <c r="H100" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I100" s="55" t="s">
@@ -12300,7 +12300,7 @@
       <c r="J100" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K100" s="64" t="s">
+      <c r="K100" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -12309,13 +12309,13 @@
       <c r="B101" s="56"/>
       <c r="C101" s="56"/>
       <c r="D101" s="58"/>
-      <c r="E101" s="60"/>
+      <c r="E101" s="63"/>
       <c r="F101" s="56"/>
       <c r="G101" s="58"/>
-      <c r="H101" s="60"/>
+      <c r="H101" s="63"/>
       <c r="I101" s="56"/>
       <c r="J101" s="56"/>
-      <c r="K101" s="64"/>
+      <c r="K101" s="60"/>
     </row>
     <row r="102" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="7">
@@ -12528,11 +12528,11 @@
       <c r="D113" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E113" s="65" t="s">
+      <c r="E113" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F113" s="65"/>
-      <c r="G113" s="65"/>
+      <c r="F113" s="64"/>
+      <c r="G113" s="64"/>
       <c r="J113" s="21"/>
       <c r="K113" s="22"/>
     </row>
@@ -12549,16 +12549,16 @@
       <c r="D114" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E114" s="59" t="s">
+      <c r="E114" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F114" s="61" t="s">
+      <c r="F114" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G114" s="62" t="s">
+      <c r="G114" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H114" s="63" t="s">
+      <c r="H114" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I114" s="55" t="s">
@@ -12567,7 +12567,7 @@
       <c r="J114" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K114" s="64" t="s">
+      <c r="K114" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -12576,13 +12576,13 @@
       <c r="B115" s="56"/>
       <c r="C115" s="56"/>
       <c r="D115" s="58"/>
-      <c r="E115" s="60"/>
+      <c r="E115" s="63"/>
       <c r="F115" s="56"/>
       <c r="G115" s="58"/>
-      <c r="H115" s="60"/>
+      <c r="H115" s="63"/>
       <c r="I115" s="56"/>
       <c r="J115" s="56"/>
-      <c r="K115" s="64"/>
+      <c r="K115" s="60"/>
     </row>
     <row r="116" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="7">
@@ -12795,11 +12795,11 @@
       <c r="D127" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E127" s="65" t="s">
+      <c r="E127" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F127" s="65"/>
-      <c r="G127" s="65"/>
+      <c r="F127" s="64"/>
+      <c r="G127" s="64"/>
       <c r="J127" s="21"/>
       <c r="K127" s="22"/>
     </row>
@@ -12816,16 +12816,16 @@
       <c r="D128" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E128" s="59" t="s">
+      <c r="E128" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F128" s="61" t="s">
+      <c r="F128" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G128" s="62" t="s">
+      <c r="G128" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H128" s="63" t="s">
+      <c r="H128" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I128" s="55" t="s">
@@ -12834,7 +12834,7 @@
       <c r="J128" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K128" s="64" t="s">
+      <c r="K128" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -12843,13 +12843,13 @@
       <c r="B129" s="56"/>
       <c r="C129" s="56"/>
       <c r="D129" s="58"/>
-      <c r="E129" s="60"/>
+      <c r="E129" s="63"/>
       <c r="F129" s="56"/>
       <c r="G129" s="58"/>
-      <c r="H129" s="60"/>
+      <c r="H129" s="63"/>
       <c r="I129" s="56"/>
       <c r="J129" s="56"/>
-      <c r="K129" s="64"/>
+      <c r="K129" s="60"/>
     </row>
     <row r="130" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="7">
@@ -13062,11 +13062,11 @@
       <c r="D141" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E141" s="65" t="s">
+      <c r="E141" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F141" s="65"/>
-      <c r="G141" s="65"/>
+      <c r="F141" s="64"/>
+      <c r="G141" s="64"/>
       <c r="J141" s="21"/>
       <c r="K141" s="22"/>
     </row>
@@ -13083,16 +13083,16 @@
       <c r="D142" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E142" s="59" t="s">
+      <c r="E142" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F142" s="61" t="s">
+      <c r="F142" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G142" s="62" t="s">
+      <c r="G142" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H142" s="63" t="s">
+      <c r="H142" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I142" s="55" t="s">
@@ -13101,7 +13101,7 @@
       <c r="J142" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K142" s="64" t="s">
+      <c r="K142" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -13110,13 +13110,13 @@
       <c r="B143" s="56"/>
       <c r="C143" s="56"/>
       <c r="D143" s="58"/>
-      <c r="E143" s="60"/>
+      <c r="E143" s="63"/>
       <c r="F143" s="56"/>
       <c r="G143" s="58"/>
-      <c r="H143" s="60"/>
+      <c r="H143" s="63"/>
       <c r="I143" s="56"/>
       <c r="J143" s="56"/>
-      <c r="K143" s="64"/>
+      <c r="K143" s="60"/>
     </row>
     <row r="144" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144" s="7">
@@ -13329,11 +13329,11 @@
       <c r="D155" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E155" s="65" t="s">
+      <c r="E155" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F155" s="65"/>
-      <c r="G155" s="65"/>
+      <c r="F155" s="64"/>
+      <c r="G155" s="64"/>
       <c r="J155" s="21"/>
       <c r="K155" s="22"/>
     </row>
@@ -13350,16 +13350,16 @@
       <c r="D156" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E156" s="59" t="s">
+      <c r="E156" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F156" s="61" t="s">
+      <c r="F156" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G156" s="62" t="s">
+      <c r="G156" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H156" s="63" t="s">
+      <c r="H156" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I156" s="55" t="s">
@@ -13368,7 +13368,7 @@
       <c r="J156" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K156" s="64" t="s">
+      <c r="K156" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -13377,13 +13377,13 @@
       <c r="B157" s="56"/>
       <c r="C157" s="56"/>
       <c r="D157" s="58"/>
-      <c r="E157" s="60"/>
+      <c r="E157" s="63"/>
       <c r="F157" s="56"/>
       <c r="G157" s="58"/>
-      <c r="H157" s="60"/>
+      <c r="H157" s="63"/>
       <c r="I157" s="56"/>
       <c r="J157" s="56"/>
-      <c r="K157" s="64"/>
+      <c r="K157" s="60"/>
     </row>
     <row r="158" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A158" s="7">
@@ -13596,11 +13596,11 @@
       <c r="D169" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E169" s="65" t="s">
+      <c r="E169" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F169" s="65"/>
-      <c r="G169" s="65"/>
+      <c r="F169" s="64"/>
+      <c r="G169" s="64"/>
       <c r="J169" s="21"/>
       <c r="K169" s="22"/>
     </row>
@@ -13617,16 +13617,16 @@
       <c r="D170" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E170" s="59" t="s">
+      <c r="E170" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F170" s="61" t="s">
+      <c r="F170" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G170" s="62" t="s">
+      <c r="G170" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H170" s="63" t="s">
+      <c r="H170" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I170" s="55" t="s">
@@ -13635,7 +13635,7 @@
       <c r="J170" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K170" s="64" t="s">
+      <c r="K170" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -13644,13 +13644,13 @@
       <c r="B171" s="56"/>
       <c r="C171" s="56"/>
       <c r="D171" s="58"/>
-      <c r="E171" s="60"/>
+      <c r="E171" s="63"/>
       <c r="F171" s="56"/>
       <c r="G171" s="58"/>
-      <c r="H171" s="60"/>
+      <c r="H171" s="63"/>
       <c r="I171" s="56"/>
       <c r="J171" s="56"/>
-      <c r="K171" s="64"/>
+      <c r="K171" s="60"/>
     </row>
     <row r="172" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A172" s="7">
@@ -13863,11 +13863,11 @@
       <c r="D183" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E183" s="65" t="s">
+      <c r="E183" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F183" s="65"/>
-      <c r="G183" s="65"/>
+      <c r="F183" s="64"/>
+      <c r="G183" s="64"/>
       <c r="J183" s="21"/>
       <c r="K183" s="22"/>
     </row>
@@ -13884,16 +13884,16 @@
       <c r="D184" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E184" s="59" t="s">
+      <c r="E184" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F184" s="61" t="s">
+      <c r="F184" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G184" s="62" t="s">
+      <c r="G184" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H184" s="63" t="s">
+      <c r="H184" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I184" s="55" t="s">
@@ -13902,7 +13902,7 @@
       <c r="J184" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K184" s="64" t="s">
+      <c r="K184" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -13911,13 +13911,13 @@
       <c r="B185" s="56"/>
       <c r="C185" s="56"/>
       <c r="D185" s="58"/>
-      <c r="E185" s="60"/>
+      <c r="E185" s="63"/>
       <c r="F185" s="56"/>
       <c r="G185" s="58"/>
-      <c r="H185" s="60"/>
+      <c r="H185" s="63"/>
       <c r="I185" s="56"/>
       <c r="J185" s="56"/>
-      <c r="K185" s="64"/>
+      <c r="K185" s="60"/>
     </row>
     <row r="186" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A186" s="7">
@@ -14130,11 +14130,11 @@
       <c r="D197" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E197" s="65" t="s">
+      <c r="E197" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F197" s="65"/>
-      <c r="G197" s="65"/>
+      <c r="F197" s="64"/>
+      <c r="G197" s="64"/>
       <c r="J197" s="21"/>
       <c r="K197" s="22"/>
     </row>
@@ -14151,16 +14151,16 @@
       <c r="D198" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E198" s="59" t="s">
+      <c r="E198" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F198" s="61" t="s">
+      <c r="F198" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G198" s="62" t="s">
+      <c r="G198" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H198" s="63" t="s">
+      <c r="H198" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I198" s="55" t="s">
@@ -14169,7 +14169,7 @@
       <c r="J198" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K198" s="64" t="s">
+      <c r="K198" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -14178,13 +14178,13 @@
       <c r="B199" s="56"/>
       <c r="C199" s="56"/>
       <c r="D199" s="58"/>
-      <c r="E199" s="60"/>
+      <c r="E199" s="63"/>
       <c r="F199" s="56"/>
       <c r="G199" s="58"/>
-      <c r="H199" s="60"/>
+      <c r="H199" s="63"/>
       <c r="I199" s="56"/>
       <c r="J199" s="56"/>
-      <c r="K199" s="64"/>
+      <c r="K199" s="60"/>
     </row>
     <row r="200" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A200" s="7">
@@ -14397,11 +14397,11 @@
       <c r="D211" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E211" s="72" t="s">
+      <c r="E211" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="F211" s="72"/>
-      <c r="G211" s="72"/>
+      <c r="F211" s="68"/>
+      <c r="G211" s="68"/>
       <c r="J211" s="21"/>
       <c r="K211" s="22"/>
     </row>
@@ -14415,19 +14415,19 @@
       <c r="C212" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="D212" s="66" t="s">
+      <c r="D212" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="E212" s="73" t="s">
+      <c r="E212" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="F212" s="75" t="s">
+      <c r="F212" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="G212" s="68" t="s">
+      <c r="G212" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="H212" s="70" t="s">
+      <c r="H212" s="66" t="s">
         <v>4</v>
       </c>
       <c r="I212" s="55" t="s">
@@ -14436,7 +14436,7 @@
       <c r="J212" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K212" s="64" t="s">
+      <c r="K212" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -14444,14 +14444,14 @@
       <c r="A213" s="56"/>
       <c r="B213" s="56"/>
       <c r="C213" s="56"/>
-      <c r="D213" s="67"/>
-      <c r="E213" s="74"/>
-      <c r="F213" s="64"/>
-      <c r="G213" s="69"/>
-      <c r="H213" s="71"/>
+      <c r="D213" s="75"/>
+      <c r="E213" s="70"/>
+      <c r="F213" s="60"/>
+      <c r="G213" s="73"/>
+      <c r="H213" s="67"/>
       <c r="I213" s="56"/>
       <c r="J213" s="56"/>
-      <c r="K213" s="64"/>
+      <c r="K213" s="60"/>
     </row>
     <row r="214" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A214" s="7">
@@ -14664,11 +14664,11 @@
       <c r="D225" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E225" s="65" t="s">
+      <c r="E225" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F225" s="65"/>
-      <c r="G225" s="65"/>
+      <c r="F225" s="64"/>
+      <c r="G225" s="64"/>
       <c r="J225" s="21"/>
       <c r="K225" s="22"/>
     </row>
@@ -14685,16 +14685,16 @@
       <c r="D226" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E226" s="59" t="s">
+      <c r="E226" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F226" s="61" t="s">
+      <c r="F226" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G226" s="62" t="s">
+      <c r="G226" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H226" s="63" t="s">
+      <c r="H226" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I226" s="55" t="s">
@@ -14703,7 +14703,7 @@
       <c r="J226" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K226" s="64" t="s">
+      <c r="K226" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -14712,13 +14712,13 @@
       <c r="B227" s="56"/>
       <c r="C227" s="56"/>
       <c r="D227" s="58"/>
-      <c r="E227" s="60"/>
+      <c r="E227" s="63"/>
       <c r="F227" s="56"/>
       <c r="G227" s="58"/>
-      <c r="H227" s="60"/>
+      <c r="H227" s="63"/>
       <c r="I227" s="56"/>
       <c r="J227" s="56"/>
-      <c r="K227" s="64"/>
+      <c r="K227" s="60"/>
     </row>
     <row r="228" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A228" s="7">
@@ -14931,11 +14931,11 @@
       <c r="D239" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E239" s="65" t="s">
+      <c r="E239" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F239" s="65"/>
-      <c r="G239" s="65"/>
+      <c r="F239" s="64"/>
+      <c r="G239" s="64"/>
       <c r="J239" s="21"/>
       <c r="K239" s="22"/>
     </row>
@@ -14952,16 +14952,16 @@
       <c r="D240" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E240" s="59" t="s">
+      <c r="E240" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F240" s="61" t="s">
+      <c r="F240" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G240" s="62" t="s">
+      <c r="G240" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H240" s="63" t="s">
+      <c r="H240" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I240" s="55" t="s">
@@ -14970,7 +14970,7 @@
       <c r="J240" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K240" s="64" t="s">
+      <c r="K240" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -14979,13 +14979,13 @@
       <c r="B241" s="56"/>
       <c r="C241" s="56"/>
       <c r="D241" s="58"/>
-      <c r="E241" s="60"/>
+      <c r="E241" s="63"/>
       <c r="F241" s="56"/>
       <c r="G241" s="58"/>
-      <c r="H241" s="60"/>
+      <c r="H241" s="63"/>
       <c r="I241" s="56"/>
       <c r="J241" s="56"/>
-      <c r="K241" s="64"/>
+      <c r="K241" s="60"/>
     </row>
     <row r="242" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A242" s="7">
@@ -15198,11 +15198,11 @@
       <c r="D253" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E253" s="65" t="s">
+      <c r="E253" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F253" s="65"/>
-      <c r="G253" s="65"/>
+      <c r="F253" s="64"/>
+      <c r="G253" s="64"/>
       <c r="J253" s="21"/>
       <c r="K253" s="22"/>
     </row>
@@ -15219,16 +15219,16 @@
       <c r="D254" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E254" s="59" t="s">
+      <c r="E254" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F254" s="61" t="s">
+      <c r="F254" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G254" s="62" t="s">
+      <c r="G254" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H254" s="63" t="s">
+      <c r="H254" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I254" s="55" t="s">
@@ -15237,7 +15237,7 @@
       <c r="J254" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K254" s="64" t="s">
+      <c r="K254" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -15246,13 +15246,13 @@
       <c r="B255" s="56"/>
       <c r="C255" s="56"/>
       <c r="D255" s="58"/>
-      <c r="E255" s="60"/>
+      <c r="E255" s="63"/>
       <c r="F255" s="56"/>
       <c r="G255" s="58"/>
-      <c r="H255" s="60"/>
+      <c r="H255" s="63"/>
       <c r="I255" s="56"/>
       <c r="J255" s="56"/>
-      <c r="K255" s="64"/>
+      <c r="K255" s="60"/>
     </row>
     <row r="256" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A256" s="7">
@@ -15465,11 +15465,11 @@
       <c r="D267" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E267" s="65" t="s">
+      <c r="E267" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F267" s="65"/>
-      <c r="G267" s="65"/>
+      <c r="F267" s="64"/>
+      <c r="G267" s="64"/>
       <c r="J267" s="21"/>
       <c r="K267" s="22"/>
     </row>
@@ -15486,16 +15486,16 @@
       <c r="D268" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E268" s="59" t="s">
+      <c r="E268" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F268" s="61" t="s">
+      <c r="F268" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G268" s="62" t="s">
+      <c r="G268" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H268" s="63" t="s">
+      <c r="H268" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I268" s="55" t="s">
@@ -15504,7 +15504,7 @@
       <c r="J268" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K268" s="64" t="s">
+      <c r="K268" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -15513,13 +15513,13 @@
       <c r="B269" s="56"/>
       <c r="C269" s="56"/>
       <c r="D269" s="58"/>
-      <c r="E269" s="60"/>
+      <c r="E269" s="63"/>
       <c r="F269" s="56"/>
       <c r="G269" s="58"/>
-      <c r="H269" s="60"/>
+      <c r="H269" s="63"/>
       <c r="I269" s="56"/>
       <c r="J269" s="56"/>
-      <c r="K269" s="64"/>
+      <c r="K269" s="60"/>
     </row>
     <row r="270" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A270" s="7">
@@ -15732,11 +15732,11 @@
       <c r="D281" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E281" s="65" t="s">
+      <c r="E281" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F281" s="65"/>
-      <c r="G281" s="65"/>
+      <c r="F281" s="64"/>
+      <c r="G281" s="64"/>
       <c r="J281" s="21"/>
       <c r="K281" s="22"/>
     </row>
@@ -15753,16 +15753,16 @@
       <c r="D282" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E282" s="59" t="s">
+      <c r="E282" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F282" s="61" t="s">
+      <c r="F282" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G282" s="62" t="s">
+      <c r="G282" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H282" s="63" t="s">
+      <c r="H282" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I282" s="55" t="s">
@@ -15771,7 +15771,7 @@
       <c r="J282" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K282" s="64" t="s">
+      <c r="K282" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -15780,13 +15780,13 @@
       <c r="B283" s="56"/>
       <c r="C283" s="56"/>
       <c r="D283" s="58"/>
-      <c r="E283" s="60"/>
+      <c r="E283" s="63"/>
       <c r="F283" s="56"/>
       <c r="G283" s="58"/>
-      <c r="H283" s="60"/>
+      <c r="H283" s="63"/>
       <c r="I283" s="56"/>
       <c r="J283" s="56"/>
-      <c r="K283" s="64"/>
+      <c r="K283" s="60"/>
     </row>
     <row r="284" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A284" s="7">
@@ -15999,11 +15999,11 @@
       <c r="D295" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E295" s="65" t="s">
+      <c r="E295" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F295" s="65"/>
-      <c r="G295" s="65"/>
+      <c r="F295" s="64"/>
+      <c r="G295" s="64"/>
       <c r="J295" s="21"/>
       <c r="K295" s="22"/>
     </row>
@@ -16020,16 +16020,16 @@
       <c r="D296" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E296" s="59" t="s">
+      <c r="E296" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F296" s="61" t="s">
+      <c r="F296" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G296" s="62" t="s">
+      <c r="G296" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H296" s="63" t="s">
+      <c r="H296" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I296" s="55" t="s">
@@ -16038,7 +16038,7 @@
       <c r="J296" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K296" s="64" t="s">
+      <c r="K296" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -16047,13 +16047,13 @@
       <c r="B297" s="56"/>
       <c r="C297" s="56"/>
       <c r="D297" s="58"/>
-      <c r="E297" s="60"/>
+      <c r="E297" s="63"/>
       <c r="F297" s="56"/>
       <c r="G297" s="58"/>
-      <c r="H297" s="60"/>
+      <c r="H297" s="63"/>
       <c r="I297" s="56"/>
       <c r="J297" s="56"/>
-      <c r="K297" s="64"/>
+      <c r="K297" s="60"/>
     </row>
     <row r="298" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A298" s="7">
@@ -16266,11 +16266,11 @@
       <c r="D309" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E309" s="65" t="s">
+      <c r="E309" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F309" s="65"/>
-      <c r="G309" s="65"/>
+      <c r="F309" s="64"/>
+      <c r="G309" s="64"/>
       <c r="J309" s="21"/>
       <c r="K309" s="22"/>
     </row>
@@ -16287,16 +16287,16 @@
       <c r="D310" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E310" s="59" t="s">
+      <c r="E310" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F310" s="61" t="s">
+      <c r="F310" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G310" s="62" t="s">
+      <c r="G310" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H310" s="63" t="s">
+      <c r="H310" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I310" s="55" t="s">
@@ -16305,7 +16305,7 @@
       <c r="J310" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K310" s="64" t="s">
+      <c r="K310" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -16314,13 +16314,13 @@
       <c r="B311" s="56"/>
       <c r="C311" s="56"/>
       <c r="D311" s="58"/>
-      <c r="E311" s="60"/>
+      <c r="E311" s="63"/>
       <c r="F311" s="56"/>
       <c r="G311" s="58"/>
-      <c r="H311" s="60"/>
+      <c r="H311" s="63"/>
       <c r="I311" s="56"/>
       <c r="J311" s="56"/>
-      <c r="K311" s="64"/>
+      <c r="K311" s="60"/>
     </row>
     <row r="312" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A312" s="7">
@@ -16533,11 +16533,11 @@
       <c r="D323" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E323" s="65" t="s">
+      <c r="E323" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F323" s="65"/>
-      <c r="G323" s="65"/>
+      <c r="F323" s="64"/>
+      <c r="G323" s="64"/>
       <c r="J323" s="21"/>
       <c r="K323" s="22"/>
     </row>
@@ -16554,16 +16554,16 @@
       <c r="D324" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E324" s="59" t="s">
+      <c r="E324" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F324" s="61" t="s">
+      <c r="F324" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G324" s="62" t="s">
+      <c r="G324" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H324" s="63" t="s">
+      <c r="H324" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I324" s="55" t="s">
@@ -16572,7 +16572,7 @@
       <c r="J324" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K324" s="64" t="s">
+      <c r="K324" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -16581,13 +16581,13 @@
       <c r="B325" s="56"/>
       <c r="C325" s="56"/>
       <c r="D325" s="58"/>
-      <c r="E325" s="60"/>
+      <c r="E325" s="63"/>
       <c r="F325" s="56"/>
       <c r="G325" s="58"/>
-      <c r="H325" s="60"/>
+      <c r="H325" s="63"/>
       <c r="I325" s="56"/>
       <c r="J325" s="56"/>
-      <c r="K325" s="64"/>
+      <c r="K325" s="60"/>
     </row>
     <row r="326" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A326" s="7">
@@ -16800,11 +16800,11 @@
       <c r="D337" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E337" s="65" t="s">
+      <c r="E337" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F337" s="65"/>
-      <c r="G337" s="65"/>
+      <c r="F337" s="64"/>
+      <c r="G337" s="64"/>
       <c r="J337" s="21"/>
       <c r="K337" s="22"/>
     </row>
@@ -16821,16 +16821,16 @@
       <c r="D338" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E338" s="59" t="s">
+      <c r="E338" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F338" s="61" t="s">
+      <c r="F338" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G338" s="62" t="s">
+      <c r="G338" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H338" s="63" t="s">
+      <c r="H338" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I338" s="55" t="s">
@@ -16839,7 +16839,7 @@
       <c r="J338" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K338" s="64" t="s">
+      <c r="K338" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -16848,13 +16848,13 @@
       <c r="B339" s="56"/>
       <c r="C339" s="56"/>
       <c r="D339" s="58"/>
-      <c r="E339" s="60"/>
+      <c r="E339" s="63"/>
       <c r="F339" s="56"/>
       <c r="G339" s="58"/>
-      <c r="H339" s="60"/>
+      <c r="H339" s="63"/>
       <c r="I339" s="56"/>
       <c r="J339" s="56"/>
-      <c r="K339" s="64"/>
+      <c r="K339" s="60"/>
     </row>
     <row r="340" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A340" s="7">
@@ -17059,11 +17059,11 @@
       <c r="D351" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E351" s="65" t="s">
+      <c r="E351" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F351" s="65"/>
-      <c r="G351" s="65"/>
+      <c r="F351" s="64"/>
+      <c r="G351" s="64"/>
       <c r="J351" s="21"/>
       <c r="K351" s="22"/>
     </row>
@@ -17080,16 +17080,16 @@
       <c r="D352" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E352" s="59" t="s">
+      <c r="E352" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F352" s="61" t="s">
+      <c r="F352" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G352" s="62" t="s">
+      <c r="G352" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H352" s="63" t="s">
+      <c r="H352" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I352" s="55" t="s">
@@ -17098,7 +17098,7 @@
       <c r="J352" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K352" s="64" t="s">
+      <c r="K352" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -17107,13 +17107,13 @@
       <c r="B353" s="56"/>
       <c r="C353" s="56"/>
       <c r="D353" s="58"/>
-      <c r="E353" s="60"/>
+      <c r="E353" s="63"/>
       <c r="F353" s="56"/>
       <c r="G353" s="58"/>
-      <c r="H353" s="60"/>
+      <c r="H353" s="63"/>
       <c r="I353" s="56"/>
       <c r="J353" s="56"/>
-      <c r="K353" s="64"/>
+      <c r="K353" s="60"/>
     </row>
     <row r="354" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A354" s="7">
@@ -17318,11 +17318,11 @@
       <c r="D365" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E365" s="65" t="s">
+      <c r="E365" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F365" s="65"/>
-      <c r="G365" s="65"/>
+      <c r="F365" s="64"/>
+      <c r="G365" s="64"/>
       <c r="J365" s="21"/>
       <c r="K365" s="22"/>
     </row>
@@ -17339,16 +17339,16 @@
       <c r="D366" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E366" s="59" t="s">
+      <c r="E366" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F366" s="61" t="s">
+      <c r="F366" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G366" s="62" t="s">
+      <c r="G366" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H366" s="63" t="s">
+      <c r="H366" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I366" s="55" t="s">
@@ -17357,7 +17357,7 @@
       <c r="J366" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K366" s="64" t="s">
+      <c r="K366" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -17366,13 +17366,13 @@
       <c r="B367" s="56"/>
       <c r="C367" s="56"/>
       <c r="D367" s="58"/>
-      <c r="E367" s="60"/>
+      <c r="E367" s="63"/>
       <c r="F367" s="56"/>
       <c r="G367" s="58"/>
-      <c r="H367" s="60"/>
+      <c r="H367" s="63"/>
       <c r="I367" s="56"/>
       <c r="J367" s="56"/>
-      <c r="K367" s="64"/>
+      <c r="K367" s="60"/>
     </row>
     <row r="368" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A368" s="7">
@@ -17577,11 +17577,11 @@
       <c r="D379" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E379" s="65" t="s">
+      <c r="E379" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F379" s="65"/>
-      <c r="G379" s="65"/>
+      <c r="F379" s="64"/>
+      <c r="G379" s="64"/>
       <c r="J379" s="21"/>
       <c r="K379" s="22"/>
     </row>
@@ -17598,16 +17598,16 @@
       <c r="D380" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E380" s="59" t="s">
+      <c r="E380" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F380" s="61" t="s">
+      <c r="F380" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G380" s="62" t="s">
+      <c r="G380" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H380" s="63" t="s">
+      <c r="H380" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I380" s="55" t="s">
@@ -17616,7 +17616,7 @@
       <c r="J380" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K380" s="64" t="s">
+      <c r="K380" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -17625,13 +17625,13 @@
       <c r="B381" s="56"/>
       <c r="C381" s="56"/>
       <c r="D381" s="58"/>
-      <c r="E381" s="60"/>
+      <c r="E381" s="63"/>
       <c r="F381" s="56"/>
       <c r="G381" s="58"/>
-      <c r="H381" s="60"/>
+      <c r="H381" s="63"/>
       <c r="I381" s="56"/>
       <c r="J381" s="56"/>
-      <c r="K381" s="64"/>
+      <c r="K381" s="60"/>
     </row>
     <row r="382" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A382" s="7">
@@ -17836,11 +17836,11 @@
       <c r="D393" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E393" s="65" t="s">
+      <c r="E393" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F393" s="65"/>
-      <c r="G393" s="65"/>
+      <c r="F393" s="64"/>
+      <c r="G393" s="64"/>
       <c r="J393" s="21"/>
       <c r="K393" s="22"/>
     </row>
@@ -17857,16 +17857,16 @@
       <c r="D394" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E394" s="59" t="s">
+      <c r="E394" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F394" s="61" t="s">
+      <c r="F394" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G394" s="62" t="s">
+      <c r="G394" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H394" s="63" t="s">
+      <c r="H394" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I394" s="55" t="s">
@@ -17875,7 +17875,7 @@
       <c r="J394" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K394" s="64" t="s">
+      <c r="K394" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -17884,13 +17884,13 @@
       <c r="B395" s="56"/>
       <c r="C395" s="56"/>
       <c r="D395" s="58"/>
-      <c r="E395" s="60"/>
+      <c r="E395" s="63"/>
       <c r="F395" s="56"/>
       <c r="G395" s="58"/>
-      <c r="H395" s="60"/>
+      <c r="H395" s="63"/>
       <c r="I395" s="56"/>
       <c r="J395" s="56"/>
-      <c r="K395" s="64"/>
+      <c r="K395" s="60"/>
     </row>
     <row r="396" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A396" s="7">
@@ -18095,11 +18095,11 @@
       <c r="D407" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E407" s="65" t="s">
+      <c r="E407" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F407" s="65"/>
-      <c r="G407" s="65"/>
+      <c r="F407" s="64"/>
+      <c r="G407" s="64"/>
       <c r="J407" s="21"/>
       <c r="K407" s="22"/>
     </row>
@@ -18116,16 +18116,16 @@
       <c r="D408" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E408" s="59" t="s">
+      <c r="E408" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F408" s="61" t="s">
+      <c r="F408" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G408" s="62" t="s">
+      <c r="G408" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H408" s="63" t="s">
+      <c r="H408" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I408" s="55" t="s">
@@ -18134,7 +18134,7 @@
       <c r="J408" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K408" s="64" t="s">
+      <c r="K408" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -18143,13 +18143,13 @@
       <c r="B409" s="56"/>
       <c r="C409" s="56"/>
       <c r="D409" s="58"/>
-      <c r="E409" s="60"/>
+      <c r="E409" s="63"/>
       <c r="F409" s="56"/>
       <c r="G409" s="58"/>
-      <c r="H409" s="60"/>
+      <c r="H409" s="63"/>
       <c r="I409" s="56"/>
       <c r="J409" s="56"/>
-      <c r="K409" s="64"/>
+      <c r="K409" s="60"/>
     </row>
     <row r="410" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A410" s="7">
@@ -18354,11 +18354,11 @@
       <c r="D421" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E421" s="65" t="s">
+      <c r="E421" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F421" s="65"/>
-      <c r="G421" s="65"/>
+      <c r="F421" s="64"/>
+      <c r="G421" s="64"/>
       <c r="J421" s="21"/>
       <c r="K421" s="22"/>
     </row>
@@ -18375,16 +18375,16 @@
       <c r="D422" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E422" s="59" t="s">
+      <c r="E422" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F422" s="61" t="s">
+      <c r="F422" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G422" s="62" t="s">
+      <c r="G422" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H422" s="63" t="s">
+      <c r="H422" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I422" s="55" t="s">
@@ -18393,7 +18393,7 @@
       <c r="J422" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K422" s="64" t="s">
+      <c r="K422" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -18402,13 +18402,13 @@
       <c r="B423" s="56"/>
       <c r="C423" s="56"/>
       <c r="D423" s="58"/>
-      <c r="E423" s="60"/>
+      <c r="E423" s="63"/>
       <c r="F423" s="56"/>
       <c r="G423" s="58"/>
-      <c r="H423" s="60"/>
+      <c r="H423" s="63"/>
       <c r="I423" s="56"/>
       <c r="J423" s="56"/>
-      <c r="K423" s="64"/>
+      <c r="K423" s="60"/>
     </row>
     <row r="424" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A424" s="7">
@@ -18613,11 +18613,11 @@
       <c r="D435" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E435" s="65" t="s">
+      <c r="E435" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F435" s="65"/>
-      <c r="G435" s="65"/>
+      <c r="F435" s="64"/>
+      <c r="G435" s="64"/>
       <c r="J435" s="21"/>
       <c r="K435" s="22"/>
     </row>
@@ -18634,16 +18634,16 @@
       <c r="D436" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E436" s="59" t="s">
+      <c r="E436" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F436" s="61" t="s">
+      <c r="F436" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G436" s="62" t="s">
+      <c r="G436" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H436" s="63" t="s">
+      <c r="H436" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I436" s="55" t="s">
@@ -18652,7 +18652,7 @@
       <c r="J436" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K436" s="64" t="s">
+      <c r="K436" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -18661,13 +18661,13 @@
       <c r="B437" s="56"/>
       <c r="C437" s="56"/>
       <c r="D437" s="58"/>
-      <c r="E437" s="60"/>
+      <c r="E437" s="63"/>
       <c r="F437" s="56"/>
       <c r="G437" s="58"/>
-      <c r="H437" s="60"/>
+      <c r="H437" s="63"/>
       <c r="I437" s="56"/>
       <c r="J437" s="56"/>
-      <c r="K437" s="64"/>
+      <c r="K437" s="60"/>
     </row>
     <row r="438" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A438" s="7">
@@ -18872,11 +18872,11 @@
       <c r="D449" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E449" s="65" t="s">
+      <c r="E449" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F449" s="65"/>
-      <c r="G449" s="65"/>
+      <c r="F449" s="64"/>
+      <c r="G449" s="64"/>
       <c r="J449" s="21"/>
       <c r="K449" s="22"/>
     </row>
@@ -18893,16 +18893,16 @@
       <c r="D450" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E450" s="59" t="s">
+      <c r="E450" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F450" s="61" t="s">
+      <c r="F450" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G450" s="62" t="s">
+      <c r="G450" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H450" s="63" t="s">
+      <c r="H450" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I450" s="55" t="s">
@@ -18911,7 +18911,7 @@
       <c r="J450" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K450" s="64" t="s">
+      <c r="K450" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -18920,13 +18920,13 @@
       <c r="B451" s="56"/>
       <c r="C451" s="56"/>
       <c r="D451" s="58"/>
-      <c r="E451" s="60"/>
+      <c r="E451" s="63"/>
       <c r="F451" s="56"/>
       <c r="G451" s="58"/>
-      <c r="H451" s="60"/>
+      <c r="H451" s="63"/>
       <c r="I451" s="56"/>
       <c r="J451" s="56"/>
-      <c r="K451" s="64"/>
+      <c r="K451" s="60"/>
     </row>
     <row r="452" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A452" s="7">
@@ -19131,11 +19131,11 @@
       <c r="D463" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E463" s="65" t="s">
+      <c r="E463" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F463" s="65"/>
-      <c r="G463" s="65"/>
+      <c r="F463" s="64"/>
+      <c r="G463" s="64"/>
       <c r="J463" s="21"/>
       <c r="K463" s="22"/>
     </row>
@@ -19152,16 +19152,16 @@
       <c r="D464" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E464" s="59" t="s">
+      <c r="E464" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F464" s="61" t="s">
+      <c r="F464" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G464" s="62" t="s">
+      <c r="G464" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H464" s="63" t="s">
+      <c r="H464" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I464" s="55" t="s">
@@ -19170,7 +19170,7 @@
       <c r="J464" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K464" s="64" t="s">
+      <c r="K464" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -19179,13 +19179,13 @@
       <c r="B465" s="56"/>
       <c r="C465" s="56"/>
       <c r="D465" s="58"/>
-      <c r="E465" s="60"/>
+      <c r="E465" s="63"/>
       <c r="F465" s="56"/>
       <c r="G465" s="58"/>
-      <c r="H465" s="60"/>
+      <c r="H465" s="63"/>
       <c r="I465" s="56"/>
       <c r="J465" s="56"/>
-      <c r="K465" s="64"/>
+      <c r="K465" s="60"/>
     </row>
     <row r="466" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A466" s="7">
@@ -19390,11 +19390,11 @@
       <c r="D477" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E477" s="65" t="s">
+      <c r="E477" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F477" s="65"/>
-      <c r="G477" s="65"/>
+      <c r="F477" s="64"/>
+      <c r="G477" s="64"/>
       <c r="J477" s="21"/>
       <c r="K477" s="22"/>
     </row>
@@ -19411,16 +19411,16 @@
       <c r="D478" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E478" s="59" t="s">
+      <c r="E478" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F478" s="61" t="s">
+      <c r="F478" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G478" s="62" t="s">
+      <c r="G478" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H478" s="63" t="s">
+      <c r="H478" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I478" s="55" t="s">
@@ -19429,7 +19429,7 @@
       <c r="J478" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K478" s="64" t="s">
+      <c r="K478" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -19438,13 +19438,13 @@
       <c r="B479" s="56"/>
       <c r="C479" s="56"/>
       <c r="D479" s="58"/>
-      <c r="E479" s="60"/>
+      <c r="E479" s="63"/>
       <c r="F479" s="56"/>
       <c r="G479" s="58"/>
-      <c r="H479" s="60"/>
+      <c r="H479" s="63"/>
       <c r="I479" s="56"/>
       <c r="J479" s="56"/>
-      <c r="K479" s="64"/>
+      <c r="K479" s="60"/>
     </row>
     <row r="480" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A480" s="7">
@@ -19644,28 +19644,380 @@
     </row>
   </sheetData>
   <mergeCells count="420">
-    <mergeCell ref="B226:B227"/>
-    <mergeCell ref="C226:C227"/>
-    <mergeCell ref="D226:D227"/>
-    <mergeCell ref="C240:C241"/>
-    <mergeCell ref="F268:F269"/>
-    <mergeCell ref="K240:K241"/>
-    <mergeCell ref="G268:G269"/>
-    <mergeCell ref="G254:G255"/>
-    <mergeCell ref="H240:H241"/>
-    <mergeCell ref="E267:G267"/>
-    <mergeCell ref="H268:H269"/>
-    <mergeCell ref="H254:H255"/>
-    <mergeCell ref="E240:E241"/>
-    <mergeCell ref="I268:I269"/>
-    <mergeCell ref="E254:E255"/>
-    <mergeCell ref="K254:K255"/>
-    <mergeCell ref="I254:I255"/>
-    <mergeCell ref="E268:E269"/>
-    <mergeCell ref="F254:F255"/>
-    <mergeCell ref="K268:K269"/>
-    <mergeCell ref="E253:G253"/>
-    <mergeCell ref="B240:B241"/>
+    <mergeCell ref="A478:A479"/>
+    <mergeCell ref="B478:B479"/>
+    <mergeCell ref="C478:C479"/>
+    <mergeCell ref="D478:D479"/>
+    <mergeCell ref="E478:E479"/>
+    <mergeCell ref="F478:F479"/>
+    <mergeCell ref="G478:G479"/>
+    <mergeCell ref="H478:H479"/>
+    <mergeCell ref="I478:I479"/>
+    <mergeCell ref="J478:J479"/>
+    <mergeCell ref="K478:K479"/>
+    <mergeCell ref="H464:H465"/>
+    <mergeCell ref="I464:I465"/>
+    <mergeCell ref="J464:J465"/>
+    <mergeCell ref="K464:K465"/>
+    <mergeCell ref="E477:G477"/>
+    <mergeCell ref="A450:A451"/>
+    <mergeCell ref="B450:B451"/>
+    <mergeCell ref="C450:C451"/>
+    <mergeCell ref="D450:D451"/>
+    <mergeCell ref="E450:E451"/>
+    <mergeCell ref="F450:F451"/>
+    <mergeCell ref="G450:G451"/>
+    <mergeCell ref="E463:G463"/>
+    <mergeCell ref="A464:A465"/>
+    <mergeCell ref="B464:B465"/>
+    <mergeCell ref="C464:C465"/>
+    <mergeCell ref="D464:D465"/>
+    <mergeCell ref="E464:E465"/>
+    <mergeCell ref="F464:F465"/>
+    <mergeCell ref="G464:G465"/>
+    <mergeCell ref="H450:H451"/>
+    <mergeCell ref="I450:I451"/>
+    <mergeCell ref="J450:J451"/>
+    <mergeCell ref="K450:K451"/>
+    <mergeCell ref="H436:H437"/>
+    <mergeCell ref="I436:I437"/>
+    <mergeCell ref="J436:J437"/>
+    <mergeCell ref="K436:K437"/>
+    <mergeCell ref="E449:G449"/>
+    <mergeCell ref="A422:A423"/>
+    <mergeCell ref="B422:B423"/>
+    <mergeCell ref="C422:C423"/>
+    <mergeCell ref="D422:D423"/>
+    <mergeCell ref="E422:E423"/>
+    <mergeCell ref="F422:F423"/>
+    <mergeCell ref="G422:G423"/>
+    <mergeCell ref="E435:G435"/>
+    <mergeCell ref="A436:A437"/>
+    <mergeCell ref="B436:B437"/>
+    <mergeCell ref="C436:C437"/>
+    <mergeCell ref="D436:D437"/>
+    <mergeCell ref="E436:E437"/>
+    <mergeCell ref="F436:F437"/>
+    <mergeCell ref="G436:G437"/>
+    <mergeCell ref="H422:H423"/>
+    <mergeCell ref="I422:I423"/>
+    <mergeCell ref="J422:J423"/>
+    <mergeCell ref="K422:K423"/>
+    <mergeCell ref="H408:H409"/>
+    <mergeCell ref="I408:I409"/>
+    <mergeCell ref="J408:J409"/>
+    <mergeCell ref="K408:K409"/>
+    <mergeCell ref="E421:G421"/>
+    <mergeCell ref="A394:A395"/>
+    <mergeCell ref="B394:B395"/>
+    <mergeCell ref="C394:C395"/>
+    <mergeCell ref="D394:D395"/>
+    <mergeCell ref="E394:E395"/>
+    <mergeCell ref="F394:F395"/>
+    <mergeCell ref="G394:G395"/>
+    <mergeCell ref="E407:G407"/>
+    <mergeCell ref="A408:A409"/>
+    <mergeCell ref="B408:B409"/>
+    <mergeCell ref="C408:C409"/>
+    <mergeCell ref="D408:D409"/>
+    <mergeCell ref="E408:E409"/>
+    <mergeCell ref="F408:F409"/>
+    <mergeCell ref="G408:G409"/>
+    <mergeCell ref="H394:H395"/>
+    <mergeCell ref="I394:I395"/>
+    <mergeCell ref="J394:J395"/>
+    <mergeCell ref="K394:K395"/>
+    <mergeCell ref="H380:H381"/>
+    <mergeCell ref="I380:I381"/>
+    <mergeCell ref="J380:J381"/>
+    <mergeCell ref="K380:K381"/>
+    <mergeCell ref="E393:G393"/>
+    <mergeCell ref="A366:A367"/>
+    <mergeCell ref="B366:B367"/>
+    <mergeCell ref="C366:C367"/>
+    <mergeCell ref="D366:D367"/>
+    <mergeCell ref="E366:E367"/>
+    <mergeCell ref="F366:F367"/>
+    <mergeCell ref="G366:G367"/>
+    <mergeCell ref="E379:G379"/>
+    <mergeCell ref="A380:A381"/>
+    <mergeCell ref="B380:B381"/>
+    <mergeCell ref="C380:C381"/>
+    <mergeCell ref="D380:D381"/>
+    <mergeCell ref="E380:E381"/>
+    <mergeCell ref="F380:F381"/>
+    <mergeCell ref="G380:G381"/>
+    <mergeCell ref="H366:H367"/>
+    <mergeCell ref="I366:I367"/>
+    <mergeCell ref="J366:J367"/>
+    <mergeCell ref="K366:K367"/>
+    <mergeCell ref="H352:H353"/>
+    <mergeCell ref="I352:I353"/>
+    <mergeCell ref="J352:J353"/>
+    <mergeCell ref="K352:K353"/>
+    <mergeCell ref="E365:G365"/>
+    <mergeCell ref="A338:A339"/>
+    <mergeCell ref="B338:B339"/>
+    <mergeCell ref="C338:C339"/>
+    <mergeCell ref="D338:D339"/>
+    <mergeCell ref="E351:G351"/>
+    <mergeCell ref="A352:A353"/>
+    <mergeCell ref="B352:B353"/>
+    <mergeCell ref="C352:C353"/>
+    <mergeCell ref="D352:D353"/>
+    <mergeCell ref="E352:E353"/>
+    <mergeCell ref="F352:F353"/>
+    <mergeCell ref="G352:G353"/>
+    <mergeCell ref="J338:J339"/>
+    <mergeCell ref="K338:K339"/>
+    <mergeCell ref="H338:H339"/>
+    <mergeCell ref="E337:G337"/>
+    <mergeCell ref="J324:J325"/>
+    <mergeCell ref="K324:K325"/>
+    <mergeCell ref="H324:H325"/>
+    <mergeCell ref="I324:I325"/>
+    <mergeCell ref="F338:F339"/>
+    <mergeCell ref="G338:G339"/>
+    <mergeCell ref="E338:E339"/>
+    <mergeCell ref="I338:I339"/>
+    <mergeCell ref="G324:G325"/>
+    <mergeCell ref="E323:G323"/>
+    <mergeCell ref="E324:E325"/>
+    <mergeCell ref="E309:G309"/>
+    <mergeCell ref="F310:F311"/>
+    <mergeCell ref="G310:G311"/>
+    <mergeCell ref="A324:A325"/>
+    <mergeCell ref="B324:B325"/>
+    <mergeCell ref="C324:C325"/>
+    <mergeCell ref="D324:D325"/>
+    <mergeCell ref="C310:C311"/>
+    <mergeCell ref="D310:D311"/>
+    <mergeCell ref="E310:E311"/>
+    <mergeCell ref="F324:F325"/>
+    <mergeCell ref="A226:A227"/>
+    <mergeCell ref="A240:A241"/>
+    <mergeCell ref="A268:A269"/>
+    <mergeCell ref="J310:J311"/>
+    <mergeCell ref="K310:K311"/>
+    <mergeCell ref="J296:J297"/>
+    <mergeCell ref="K296:K297"/>
+    <mergeCell ref="J282:J283"/>
+    <mergeCell ref="K282:K283"/>
+    <mergeCell ref="D296:D297"/>
+    <mergeCell ref="E296:E297"/>
+    <mergeCell ref="F296:F297"/>
+    <mergeCell ref="H310:H311"/>
+    <mergeCell ref="I310:I311"/>
+    <mergeCell ref="A296:A297"/>
+    <mergeCell ref="A310:A311"/>
+    <mergeCell ref="B310:B311"/>
+    <mergeCell ref="B296:B297"/>
+    <mergeCell ref="C296:C297"/>
+    <mergeCell ref="E225:G225"/>
+    <mergeCell ref="G226:G227"/>
+    <mergeCell ref="E226:E227"/>
+    <mergeCell ref="E239:G239"/>
+    <mergeCell ref="A282:A283"/>
+    <mergeCell ref="B282:B283"/>
+    <mergeCell ref="C282:C283"/>
+    <mergeCell ref="D282:D283"/>
+    <mergeCell ref="K198:K199"/>
+    <mergeCell ref="I198:I199"/>
+    <mergeCell ref="J198:J199"/>
+    <mergeCell ref="J268:J269"/>
+    <mergeCell ref="J254:J255"/>
+    <mergeCell ref="K226:K227"/>
+    <mergeCell ref="J226:J227"/>
+    <mergeCell ref="J240:J241"/>
+    <mergeCell ref="I226:I227"/>
+    <mergeCell ref="I240:I241"/>
+    <mergeCell ref="F226:F227"/>
+    <mergeCell ref="G240:G241"/>
+    <mergeCell ref="F240:F241"/>
+    <mergeCell ref="A212:A213"/>
+    <mergeCell ref="B212:B213"/>
+    <mergeCell ref="C212:C213"/>
+    <mergeCell ref="I296:I297"/>
+    <mergeCell ref="E295:G295"/>
+    <mergeCell ref="G296:G297"/>
+    <mergeCell ref="H282:H283"/>
+    <mergeCell ref="H296:H297"/>
+    <mergeCell ref="E281:G281"/>
+    <mergeCell ref="E282:E283"/>
+    <mergeCell ref="F282:F283"/>
+    <mergeCell ref="G282:G283"/>
+    <mergeCell ref="I282:I283"/>
+    <mergeCell ref="J100:J101"/>
+    <mergeCell ref="I114:I115"/>
+    <mergeCell ref="H114:H115"/>
+    <mergeCell ref="F86:F87"/>
+    <mergeCell ref="D86:D87"/>
+    <mergeCell ref="F114:F115"/>
+    <mergeCell ref="C100:C101"/>
+    <mergeCell ref="D100:D101"/>
+    <mergeCell ref="E100:E101"/>
+    <mergeCell ref="F100:F101"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="G100:G101"/>
+    <mergeCell ref="E114:E115"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="K72:K73"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="J72:J73"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="K30:K31"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="H72:H73"/>
+    <mergeCell ref="I72:I73"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="E71:G71"/>
+    <mergeCell ref="F72:F73"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="G72:G73"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="B156:B157"/>
+    <mergeCell ref="B114:B115"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="A184:A185"/>
+    <mergeCell ref="A114:A115"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="A142:A143"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="C170:C171"/>
+    <mergeCell ref="C184:C185"/>
+    <mergeCell ref="E85:G85"/>
+    <mergeCell ref="E86:E87"/>
+    <mergeCell ref="E169:G169"/>
+    <mergeCell ref="E99:G99"/>
+    <mergeCell ref="G114:G115"/>
+    <mergeCell ref="E127:G127"/>
+    <mergeCell ref="E128:E129"/>
+    <mergeCell ref="F128:F129"/>
+    <mergeCell ref="E113:G113"/>
+    <mergeCell ref="G128:G129"/>
+    <mergeCell ref="G156:G157"/>
+    <mergeCell ref="E141:G141"/>
+    <mergeCell ref="E142:E143"/>
+    <mergeCell ref="F142:F143"/>
+    <mergeCell ref="G142:G143"/>
+    <mergeCell ref="F156:F157"/>
+    <mergeCell ref="E156:E157"/>
+    <mergeCell ref="E155:G155"/>
+    <mergeCell ref="K86:K87"/>
+    <mergeCell ref="J86:J87"/>
+    <mergeCell ref="G86:G87"/>
+    <mergeCell ref="I212:I213"/>
+    <mergeCell ref="J212:J213"/>
+    <mergeCell ref="K212:K213"/>
+    <mergeCell ref="H86:H87"/>
+    <mergeCell ref="I86:I87"/>
+    <mergeCell ref="D198:D199"/>
+    <mergeCell ref="D156:D157"/>
+    <mergeCell ref="D128:D129"/>
+    <mergeCell ref="K142:K143"/>
+    <mergeCell ref="J156:J157"/>
+    <mergeCell ref="K156:K157"/>
+    <mergeCell ref="K128:K129"/>
+    <mergeCell ref="D142:D143"/>
+    <mergeCell ref="I128:I129"/>
+    <mergeCell ref="I156:I157"/>
+    <mergeCell ref="J128:J129"/>
+    <mergeCell ref="H142:H143"/>
+    <mergeCell ref="H128:H129"/>
+    <mergeCell ref="K184:K185"/>
+    <mergeCell ref="J170:J171"/>
+    <mergeCell ref="K170:K171"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="A198:A199"/>
+    <mergeCell ref="C142:C143"/>
+    <mergeCell ref="A156:A157"/>
+    <mergeCell ref="B170:B171"/>
+    <mergeCell ref="B184:B185"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="C198:C199"/>
+    <mergeCell ref="D170:D171"/>
+    <mergeCell ref="D184:D185"/>
+    <mergeCell ref="E184:E185"/>
+    <mergeCell ref="F184:F185"/>
+    <mergeCell ref="G184:G185"/>
+    <mergeCell ref="F212:F213"/>
+    <mergeCell ref="I100:I101"/>
+    <mergeCell ref="C156:C157"/>
+    <mergeCell ref="C128:C129"/>
+    <mergeCell ref="D114:D115"/>
+    <mergeCell ref="B198:B199"/>
+    <mergeCell ref="E170:E171"/>
+    <mergeCell ref="H170:H171"/>
+    <mergeCell ref="I170:I171"/>
+    <mergeCell ref="F170:F171"/>
+    <mergeCell ref="I184:I185"/>
+    <mergeCell ref="E197:G197"/>
+    <mergeCell ref="F198:F199"/>
+    <mergeCell ref="G198:G199"/>
+    <mergeCell ref="H198:H199"/>
+    <mergeCell ref="G212:G213"/>
+    <mergeCell ref="D212:D213"/>
     <mergeCell ref="A254:A255"/>
     <mergeCell ref="B254:B255"/>
     <mergeCell ref="B268:B269"/>
@@ -19690,394 +20042,42 @@
     <mergeCell ref="E211:G211"/>
     <mergeCell ref="E212:E213"/>
     <mergeCell ref="E183:G183"/>
-    <mergeCell ref="E184:E185"/>
-    <mergeCell ref="F184:F185"/>
-    <mergeCell ref="G184:G185"/>
-    <mergeCell ref="F212:F213"/>
-    <mergeCell ref="I100:I101"/>
-    <mergeCell ref="C156:C157"/>
-    <mergeCell ref="C128:C129"/>
-    <mergeCell ref="D114:D115"/>
-    <mergeCell ref="B198:B199"/>
-    <mergeCell ref="E170:E171"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="A198:A199"/>
-    <mergeCell ref="C142:C143"/>
-    <mergeCell ref="A156:A157"/>
-    <mergeCell ref="B170:B171"/>
-    <mergeCell ref="B184:B185"/>
-    <mergeCell ref="B100:B101"/>
-    <mergeCell ref="C198:C199"/>
-    <mergeCell ref="D170:D171"/>
-    <mergeCell ref="D184:D185"/>
-    <mergeCell ref="H170:H171"/>
-    <mergeCell ref="I170:I171"/>
-    <mergeCell ref="F170:F171"/>
-    <mergeCell ref="K86:K87"/>
-    <mergeCell ref="J86:J87"/>
-    <mergeCell ref="G86:G87"/>
-    <mergeCell ref="I212:I213"/>
-    <mergeCell ref="J212:J213"/>
-    <mergeCell ref="K212:K213"/>
-    <mergeCell ref="H86:H87"/>
-    <mergeCell ref="I86:I87"/>
-    <mergeCell ref="D198:D199"/>
-    <mergeCell ref="D156:D157"/>
-    <mergeCell ref="D128:D129"/>
-    <mergeCell ref="K142:K143"/>
-    <mergeCell ref="J156:J157"/>
-    <mergeCell ref="K156:K157"/>
-    <mergeCell ref="K128:K129"/>
-    <mergeCell ref="D142:D143"/>
-    <mergeCell ref="I128:I129"/>
-    <mergeCell ref="I156:I157"/>
-    <mergeCell ref="J128:J129"/>
-    <mergeCell ref="H142:H143"/>
-    <mergeCell ref="H128:H129"/>
-    <mergeCell ref="K184:K185"/>
-    <mergeCell ref="J170:J171"/>
-    <mergeCell ref="K170:K171"/>
-    <mergeCell ref="E85:G85"/>
-    <mergeCell ref="E86:E87"/>
-    <mergeCell ref="E169:G169"/>
-    <mergeCell ref="E99:G99"/>
-    <mergeCell ref="G114:G115"/>
-    <mergeCell ref="E127:G127"/>
-    <mergeCell ref="E128:E129"/>
-    <mergeCell ref="F128:F129"/>
-    <mergeCell ref="E113:G113"/>
-    <mergeCell ref="G128:G129"/>
-    <mergeCell ref="G156:G157"/>
-    <mergeCell ref="E141:G141"/>
-    <mergeCell ref="E142:E143"/>
-    <mergeCell ref="F142:F143"/>
-    <mergeCell ref="G142:G143"/>
-    <mergeCell ref="F156:F157"/>
-    <mergeCell ref="E156:E157"/>
-    <mergeCell ref="E155:G155"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="B156:B157"/>
-    <mergeCell ref="B114:B115"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="A184:A185"/>
-    <mergeCell ref="A114:A115"/>
-    <mergeCell ref="A100:A101"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="C170:C171"/>
-    <mergeCell ref="C184:C185"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="E71:G71"/>
-    <mergeCell ref="F72:F73"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="G72:G73"/>
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="K72:K73"/>
-    <mergeCell ref="K44:K45"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="J72:J73"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="K30:K31"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="H72:H73"/>
-    <mergeCell ref="I72:I73"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="G100:G101"/>
-    <mergeCell ref="E114:E115"/>
-    <mergeCell ref="J100:J101"/>
-    <mergeCell ref="I114:I115"/>
-    <mergeCell ref="H114:H115"/>
-    <mergeCell ref="F86:F87"/>
-    <mergeCell ref="D86:D87"/>
-    <mergeCell ref="F114:F115"/>
-    <mergeCell ref="C100:C101"/>
-    <mergeCell ref="D100:D101"/>
-    <mergeCell ref="E100:E101"/>
-    <mergeCell ref="F100:F101"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="I184:I185"/>
-    <mergeCell ref="E197:G197"/>
-    <mergeCell ref="F198:F199"/>
-    <mergeCell ref="G198:G199"/>
-    <mergeCell ref="H198:H199"/>
-    <mergeCell ref="I296:I297"/>
-    <mergeCell ref="E295:G295"/>
-    <mergeCell ref="G296:G297"/>
-    <mergeCell ref="H282:H283"/>
-    <mergeCell ref="H296:H297"/>
-    <mergeCell ref="E281:G281"/>
-    <mergeCell ref="E282:E283"/>
-    <mergeCell ref="F282:F283"/>
-    <mergeCell ref="G282:G283"/>
-    <mergeCell ref="I282:I283"/>
-    <mergeCell ref="G212:G213"/>
-    <mergeCell ref="E225:G225"/>
-    <mergeCell ref="G226:G227"/>
-    <mergeCell ref="E226:E227"/>
-    <mergeCell ref="E239:G239"/>
-    <mergeCell ref="A282:A283"/>
-    <mergeCell ref="B282:B283"/>
-    <mergeCell ref="C282:C283"/>
-    <mergeCell ref="D282:D283"/>
-    <mergeCell ref="K198:K199"/>
-    <mergeCell ref="I198:I199"/>
-    <mergeCell ref="J198:J199"/>
-    <mergeCell ref="J268:J269"/>
-    <mergeCell ref="J254:J255"/>
-    <mergeCell ref="K226:K227"/>
-    <mergeCell ref="J226:J227"/>
-    <mergeCell ref="J240:J241"/>
-    <mergeCell ref="I226:I227"/>
-    <mergeCell ref="I240:I241"/>
-    <mergeCell ref="F226:F227"/>
-    <mergeCell ref="G240:G241"/>
-    <mergeCell ref="F240:F241"/>
-    <mergeCell ref="A212:A213"/>
-    <mergeCell ref="B212:B213"/>
-    <mergeCell ref="C212:C213"/>
-    <mergeCell ref="D212:D213"/>
-    <mergeCell ref="A226:A227"/>
-    <mergeCell ref="A240:A241"/>
-    <mergeCell ref="A268:A269"/>
-    <mergeCell ref="J310:J311"/>
-    <mergeCell ref="K310:K311"/>
-    <mergeCell ref="J296:J297"/>
-    <mergeCell ref="K296:K297"/>
-    <mergeCell ref="J282:J283"/>
-    <mergeCell ref="K282:K283"/>
-    <mergeCell ref="D296:D297"/>
-    <mergeCell ref="E296:E297"/>
-    <mergeCell ref="F296:F297"/>
-    <mergeCell ref="H310:H311"/>
-    <mergeCell ref="I310:I311"/>
-    <mergeCell ref="A296:A297"/>
-    <mergeCell ref="A310:A311"/>
-    <mergeCell ref="B310:B311"/>
-    <mergeCell ref="B296:B297"/>
-    <mergeCell ref="C296:C297"/>
-    <mergeCell ref="G324:G325"/>
-    <mergeCell ref="E323:G323"/>
-    <mergeCell ref="E324:E325"/>
-    <mergeCell ref="E309:G309"/>
-    <mergeCell ref="F310:F311"/>
-    <mergeCell ref="G310:G311"/>
-    <mergeCell ref="A324:A325"/>
-    <mergeCell ref="B324:B325"/>
-    <mergeCell ref="C324:C325"/>
-    <mergeCell ref="D324:D325"/>
-    <mergeCell ref="C310:C311"/>
-    <mergeCell ref="D310:D311"/>
-    <mergeCell ref="E310:E311"/>
-    <mergeCell ref="F324:F325"/>
-    <mergeCell ref="E337:G337"/>
-    <mergeCell ref="J324:J325"/>
-    <mergeCell ref="K324:K325"/>
-    <mergeCell ref="H324:H325"/>
-    <mergeCell ref="I324:I325"/>
-    <mergeCell ref="F338:F339"/>
-    <mergeCell ref="G338:G339"/>
-    <mergeCell ref="E338:E339"/>
-    <mergeCell ref="I338:I339"/>
-    <mergeCell ref="J366:J367"/>
-    <mergeCell ref="K366:K367"/>
-    <mergeCell ref="H352:H353"/>
-    <mergeCell ref="I352:I353"/>
-    <mergeCell ref="J352:J353"/>
-    <mergeCell ref="K352:K353"/>
-    <mergeCell ref="E365:G365"/>
-    <mergeCell ref="A338:A339"/>
-    <mergeCell ref="B338:B339"/>
-    <mergeCell ref="C338:C339"/>
-    <mergeCell ref="D338:D339"/>
-    <mergeCell ref="E351:G351"/>
-    <mergeCell ref="A352:A353"/>
-    <mergeCell ref="B352:B353"/>
-    <mergeCell ref="C352:C353"/>
-    <mergeCell ref="D352:D353"/>
-    <mergeCell ref="E352:E353"/>
-    <mergeCell ref="F352:F353"/>
-    <mergeCell ref="G352:G353"/>
-    <mergeCell ref="J338:J339"/>
-    <mergeCell ref="K338:K339"/>
-    <mergeCell ref="H338:H339"/>
-    <mergeCell ref="J394:J395"/>
-    <mergeCell ref="K394:K395"/>
-    <mergeCell ref="H380:H381"/>
-    <mergeCell ref="I380:I381"/>
-    <mergeCell ref="J380:J381"/>
-    <mergeCell ref="K380:K381"/>
-    <mergeCell ref="E393:G393"/>
-    <mergeCell ref="A366:A367"/>
-    <mergeCell ref="B366:B367"/>
-    <mergeCell ref="C366:C367"/>
-    <mergeCell ref="D366:D367"/>
-    <mergeCell ref="E366:E367"/>
-    <mergeCell ref="F366:F367"/>
-    <mergeCell ref="G366:G367"/>
-    <mergeCell ref="E379:G379"/>
-    <mergeCell ref="A380:A381"/>
-    <mergeCell ref="B380:B381"/>
-    <mergeCell ref="C380:C381"/>
-    <mergeCell ref="D380:D381"/>
-    <mergeCell ref="E380:E381"/>
-    <mergeCell ref="F380:F381"/>
-    <mergeCell ref="G380:G381"/>
-    <mergeCell ref="H366:H367"/>
-    <mergeCell ref="I366:I367"/>
-    <mergeCell ref="J422:J423"/>
-    <mergeCell ref="K422:K423"/>
-    <mergeCell ref="H408:H409"/>
-    <mergeCell ref="I408:I409"/>
-    <mergeCell ref="J408:J409"/>
-    <mergeCell ref="K408:K409"/>
-    <mergeCell ref="E421:G421"/>
-    <mergeCell ref="A394:A395"/>
-    <mergeCell ref="B394:B395"/>
-    <mergeCell ref="C394:C395"/>
-    <mergeCell ref="D394:D395"/>
-    <mergeCell ref="E394:E395"/>
-    <mergeCell ref="F394:F395"/>
-    <mergeCell ref="G394:G395"/>
-    <mergeCell ref="E407:G407"/>
-    <mergeCell ref="A408:A409"/>
-    <mergeCell ref="B408:B409"/>
-    <mergeCell ref="C408:C409"/>
-    <mergeCell ref="D408:D409"/>
-    <mergeCell ref="E408:E409"/>
-    <mergeCell ref="F408:F409"/>
-    <mergeCell ref="G408:G409"/>
-    <mergeCell ref="H394:H395"/>
-    <mergeCell ref="I394:I395"/>
-    <mergeCell ref="J450:J451"/>
-    <mergeCell ref="K450:K451"/>
-    <mergeCell ref="H436:H437"/>
-    <mergeCell ref="I436:I437"/>
-    <mergeCell ref="J436:J437"/>
-    <mergeCell ref="K436:K437"/>
-    <mergeCell ref="E449:G449"/>
-    <mergeCell ref="A422:A423"/>
-    <mergeCell ref="B422:B423"/>
-    <mergeCell ref="C422:C423"/>
-    <mergeCell ref="D422:D423"/>
-    <mergeCell ref="E422:E423"/>
-    <mergeCell ref="F422:F423"/>
-    <mergeCell ref="G422:G423"/>
-    <mergeCell ref="E435:G435"/>
-    <mergeCell ref="A436:A437"/>
-    <mergeCell ref="B436:B437"/>
-    <mergeCell ref="C436:C437"/>
-    <mergeCell ref="D436:D437"/>
-    <mergeCell ref="E436:E437"/>
-    <mergeCell ref="F436:F437"/>
-    <mergeCell ref="G436:G437"/>
-    <mergeCell ref="H422:H423"/>
-    <mergeCell ref="I422:I423"/>
-    <mergeCell ref="J478:J479"/>
-    <mergeCell ref="K478:K479"/>
-    <mergeCell ref="H464:H465"/>
-    <mergeCell ref="I464:I465"/>
-    <mergeCell ref="J464:J465"/>
-    <mergeCell ref="K464:K465"/>
-    <mergeCell ref="E477:G477"/>
-    <mergeCell ref="A450:A451"/>
-    <mergeCell ref="B450:B451"/>
-    <mergeCell ref="C450:C451"/>
-    <mergeCell ref="D450:D451"/>
-    <mergeCell ref="E450:E451"/>
-    <mergeCell ref="F450:F451"/>
-    <mergeCell ref="G450:G451"/>
-    <mergeCell ref="E463:G463"/>
-    <mergeCell ref="A464:A465"/>
-    <mergeCell ref="B464:B465"/>
-    <mergeCell ref="C464:C465"/>
-    <mergeCell ref="D464:D465"/>
-    <mergeCell ref="E464:E465"/>
-    <mergeCell ref="F464:F465"/>
-    <mergeCell ref="G464:G465"/>
-    <mergeCell ref="H450:H451"/>
-    <mergeCell ref="I450:I451"/>
-    <mergeCell ref="A478:A479"/>
-    <mergeCell ref="B478:B479"/>
-    <mergeCell ref="C478:C479"/>
-    <mergeCell ref="D478:D479"/>
-    <mergeCell ref="E478:E479"/>
-    <mergeCell ref="F478:F479"/>
-    <mergeCell ref="G478:G479"/>
-    <mergeCell ref="H478:H479"/>
-    <mergeCell ref="I478:I479"/>
+    <mergeCell ref="B226:B227"/>
+    <mergeCell ref="C226:C227"/>
+    <mergeCell ref="D226:D227"/>
+    <mergeCell ref="C240:C241"/>
+    <mergeCell ref="F268:F269"/>
+    <mergeCell ref="K240:K241"/>
+    <mergeCell ref="G268:G269"/>
+    <mergeCell ref="G254:G255"/>
+    <mergeCell ref="H240:H241"/>
+    <mergeCell ref="E267:G267"/>
+    <mergeCell ref="H268:H269"/>
+    <mergeCell ref="H254:H255"/>
+    <mergeCell ref="E240:E241"/>
+    <mergeCell ref="I268:I269"/>
+    <mergeCell ref="E254:E255"/>
+    <mergeCell ref="K254:K255"/>
+    <mergeCell ref="I254:I255"/>
+    <mergeCell ref="E268:E269"/>
+    <mergeCell ref="F254:F255"/>
+    <mergeCell ref="K268:K269"/>
+    <mergeCell ref="E253:G253"/>
+    <mergeCell ref="B240:B241"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations xWindow="401" yWindow="629" count="6">
     <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E18:J27 A116:B125 A424:B433 A4:B13 A32:B41 A228:B237 E214:J223 A480:B489 E4:J13 A60:B69 A88:B97 A186:B195 A46:B55 A172:B181 E74:J83 E46:J55 A102:B111 E60:J69 A74:B83 E102:J111 A130:B139 E88:J97 A158:B167 E116:J125 E130:J139 E144:J153 E32:J41 A144:B153 E158:J167 A200:B209 A326:B335 E186:J195 E200:J209 A242:B251 A18:B27 A256:B265 E228:J237 E172:J181 A284:B293 A214:B223 A298:B307 E242:J251 A312:B321 E270:J279 E326:J335 E284:J293 E340:J349 E256:J265 E480:J489 E298:J307 E354:J363 E368:J377 A368:B377 E382:J391 A382:B391 E396:J405 A396:B405 E410:J419 A410:B419 E424:J433 A354:B363 E438:J447 A438:B447 E452:J461 A452:B461 E466:J475 A466:B475 A340:B349 A270:B279 E312:J321" xr:uid="{A2E9CFEE-2B0F-4548-84A2-35A78D79EA82}"/>
-    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K13 K18:K27 C4:C6 K214:K223 K158:K167 K32:K41 K172:K181 K46:K55 K74:K83 K354:K363 K60:K69 K88:K97 K102:K111 K116:K125 K130:K139 K144:K153 C358 K186:K195 K200:K209 K466:K475 K228:K237 K242:K251 K340:K349 K270:K279 K284:K293 K298:K307 K326:K335 K256:K265 K480:K489 K368:K377 K382:K391 K396:K405 K410:K419 K424:K433 K438:K447 K452:K461 K312:K321" xr:uid="{0FE6C353-CEF9-4A19-8837-1F8D00BDBC7F}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C284:C293 C32:C41 C18:C27 C158:C167 C46:C55 C74:C83 C60:C69 C88:C97 C116:C125 C130:C139 C102:C111 C214:C223 C172:C181 C340:C349 C144:C153 C228:C237 C200:C209 C186:C195 C242:C251 C256:C265 C270:C279 C298:C307 C480:C489 C326:C335 C359:C363 C382:C391 C396:C405 C410:C419 C368:C377 C424:C433 C452:C461 C466:C475 C354:C357 C438:C447 C7:C13 C312:C321" xr:uid="{78DD0EF1-0896-446A-A8CB-00320A7D98AC}">
-      <formula1>"鴛　泊,沓　形,鬼　脇,仙法志"</formula1>
-    </dataValidation>
+    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K13 K18:K27 K312:K321 K214:K223 K158:K167 K32:K41 K172:K181 K46:K55 K74:K83 K354:K363 K60:K69 K88:K97 K102:K111 K116:K125 K130:K139 K144:K153 K452:K461 K186:K195 K200:K209 K466:K475 K228:K237 K242:K251 K340:K349 K270:K279 K284:K293 K298:K307 K326:K335 K256:K265 K480:K489 K368:K377 K382:K391 K396:K405 K410:K419 K424:K433 K438:K447" xr:uid="{0FE6C353-CEF9-4A19-8837-1F8D00BDBC7F}"/>
     <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D1:D3" xr:uid="{FBC42288-9CA0-4C34-971F-0FC3C00868FC}"/>
     <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D308:D311 D14:D17 D252:D255 D70:D73 D56:D59 D42:D45 D140:D143 D126:D129 D112:D115 D224:D227 D238:D241 D266:D269 D28:D31 D84:D87 D98:D101 D154:D157 D168:D171 D182:D185 D196:D199 D210:D213 D280:D283 D294:D297 D322:D325 D336:D339 D350:D353 D364:D367 D378:D381 D392:D395 D406:D409 D420:D423 D434:D437 D448:D451 D462:D465 D476:D479 D490:D868" xr:uid="{409488D5-CE0F-452A-ABE4-BCBC197406DD}">
       <formula1>"国保中央病院,福士水産㈱,高橋水産㈱"</formula1>
     </dataValidation>
     <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D4:D13 D18:D27 D32:D41 D46:D55 D60:D69 D74:D83 D88:D97 D102:D111 D116:D125 D130:D139 D144:D153 D158:D167 D172:D181 D186:D195 D200:D209 D214:D223 D228:D237 D242:D251 D256:D265 D270:D279 D284:D293 D298:D307 D312:D321 D326:D335 D340:D349 D354:D363 D368:D377 D382:D391 D396:D405 D410:D419 D424:D433 D438:D447 D452:D461 D466:D475 D480:D489" xr:uid="{3203905E-E1B9-4E90-8FE3-17A1CEA62B86}">
       <formula1>"国保中央病院,道立鬼脇診療所,カムイウィスキー,福士水産㈱,糀谷商店,米田商店"</formula1>
+    </dataValidation>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C13 C18:C27 C32:C41 C46:C55 C60:C69 C74:C83 C88:C97 C102:C111 C116:C125 C130:C139 C144:C153 C158:C167 C172:C181 C186:C195 C200:C209 C214:C223 C228:C237 C242:C251 C256:C265 C270:C279 C284:C293 C298:C307 C312:C321 C326:C335 C340:C349 C354:C363 C368:C377 C382:C391 C396:C405 C410:C419 C424:C433 C438:C447 C452:C461 C466:C475 C480:C489" xr:uid="{B980D593-B3D9-4872-9E24-4DD0B2E2A15C}">
+      <formula1>"鴛 泊,鬼 脇,沓 形,仙法志"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -20112,11 +20112,11 @@
       <c r="D1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="65" t="s">
+      <c r="E1" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
       <c r="J1" s="21"/>
       <c r="K1" s="22"/>
     </row>
@@ -20133,16 +20133,16 @@
       <c r="D2" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="59" t="s">
+      <c r="E2" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="61" t="s">
+      <c r="F2" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="62" t="s">
+      <c r="G2" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="63" t="s">
+      <c r="H2" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="55" t="s">
@@ -20151,7 +20151,7 @@
       <c r="J2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="64" t="s">
+      <c r="K2" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -20160,13 +20160,13 @@
       <c r="B3" s="56"/>
       <c r="C3" s="56"/>
       <c r="D3" s="58"/>
-      <c r="E3" s="60"/>
+      <c r="E3" s="63"/>
       <c r="F3" s="56"/>
       <c r="G3" s="58"/>
-      <c r="H3" s="60"/>
+      <c r="H3" s="63"/>
       <c r="I3" s="56"/>
       <c r="J3" s="56"/>
-      <c r="K3" s="64"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="7"/>
@@ -20351,11 +20351,11 @@
       <c r="D15" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="65" t="s">
+      <c r="E15" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="65"/>
-      <c r="G15" s="65"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="64"/>
       <c r="J15" s="21"/>
       <c r="K15" s="22"/>
     </row>
@@ -20372,16 +20372,16 @@
       <c r="D16" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="59" t="s">
+      <c r="E16" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="61" t="s">
+      <c r="F16" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="62" t="s">
+      <c r="G16" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="63" t="s">
+      <c r="H16" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I16" s="55" t="s">
@@ -20390,7 +20390,7 @@
       <c r="J16" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="64" t="s">
+      <c r="K16" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -20399,13 +20399,13 @@
       <c r="B17" s="56"/>
       <c r="C17" s="56"/>
       <c r="D17" s="58"/>
-      <c r="E17" s="60"/>
+      <c r="E17" s="63"/>
       <c r="F17" s="56"/>
       <c r="G17" s="58"/>
-      <c r="H17" s="60"/>
+      <c r="H17" s="63"/>
       <c r="I17" s="56"/>
       <c r="J17" s="56"/>
-      <c r="K17" s="64"/>
+      <c r="K17" s="60"/>
     </row>
     <row r="18" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7"/>
@@ -20590,11 +20590,11 @@
       <c r="D29" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="65" t="s">
+      <c r="E29" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="65"/>
-      <c r="G29" s="65"/>
+      <c r="F29" s="64"/>
+      <c r="G29" s="64"/>
       <c r="J29" s="21"/>
       <c r="K29" s="22"/>
     </row>
@@ -20611,16 +20611,16 @@
       <c r="D30" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E30" s="59" t="s">
+      <c r="E30" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F30" s="61" t="s">
+      <c r="F30" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G30" s="62" t="s">
+      <c r="G30" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="63" t="s">
+      <c r="H30" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I30" s="55" t="s">
@@ -20629,7 +20629,7 @@
       <c r="J30" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K30" s="64" t="s">
+      <c r="K30" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -20638,13 +20638,13 @@
       <c r="B31" s="56"/>
       <c r="C31" s="56"/>
       <c r="D31" s="58"/>
-      <c r="E31" s="60"/>
+      <c r="E31" s="63"/>
       <c r="F31" s="56"/>
       <c r="G31" s="58"/>
-      <c r="H31" s="60"/>
+      <c r="H31" s="63"/>
       <c r="I31" s="56"/>
       <c r="J31" s="56"/>
-      <c r="K31" s="64"/>
+      <c r="K31" s="60"/>
     </row>
     <row r="32" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7"/>
@@ -20829,11 +20829,11 @@
       <c r="D43" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="65" t="s">
+      <c r="E43" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="65"/>
-      <c r="G43" s="65"/>
+      <c r="F43" s="64"/>
+      <c r="G43" s="64"/>
       <c r="J43" s="21"/>
       <c r="K43" s="22"/>
     </row>
@@ -20850,16 +20850,16 @@
       <c r="D44" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="59" t="s">
+      <c r="E44" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="61" t="s">
+      <c r="F44" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G44" s="62" t="s">
+      <c r="G44" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H44" s="63" t="s">
+      <c r="H44" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I44" s="55" t="s">
@@ -20868,7 +20868,7 @@
       <c r="J44" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="64" t="s">
+      <c r="K44" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -20877,13 +20877,13 @@
       <c r="B45" s="56"/>
       <c r="C45" s="56"/>
       <c r="D45" s="58"/>
-      <c r="E45" s="60"/>
+      <c r="E45" s="63"/>
       <c r="F45" s="56"/>
       <c r="G45" s="58"/>
-      <c r="H45" s="60"/>
+      <c r="H45" s="63"/>
       <c r="I45" s="56"/>
       <c r="J45" s="56"/>
-      <c r="K45" s="64"/>
+      <c r="K45" s="60"/>
     </row>
     <row r="46" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7"/>
@@ -21068,11 +21068,11 @@
       <c r="D57" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E57" s="65" t="s">
+      <c r="E57" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="65"/>
-      <c r="G57" s="65"/>
+      <c r="F57" s="64"/>
+      <c r="G57" s="64"/>
       <c r="J57" s="21"/>
       <c r="K57" s="22"/>
     </row>
@@ -21089,16 +21089,16 @@
       <c r="D58" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="59" t="s">
+      <c r="E58" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F58" s="61" t="s">
+      <c r="F58" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G58" s="62" t="s">
+      <c r="G58" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H58" s="63" t="s">
+      <c r="H58" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I58" s="55" t="s">
@@ -21107,7 +21107,7 @@
       <c r="J58" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K58" s="64" t="s">
+      <c r="K58" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -21116,13 +21116,13 @@
       <c r="B59" s="56"/>
       <c r="C59" s="56"/>
       <c r="D59" s="58"/>
-      <c r="E59" s="60"/>
+      <c r="E59" s="63"/>
       <c r="F59" s="56"/>
       <c r="G59" s="58"/>
-      <c r="H59" s="60"/>
+      <c r="H59" s="63"/>
       <c r="I59" s="56"/>
       <c r="J59" s="56"/>
-      <c r="K59" s="64"/>
+      <c r="K59" s="60"/>
     </row>
     <row r="60" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="7"/>
@@ -21309,27 +21309,29 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
     <mergeCell ref="E57:G57"/>
     <mergeCell ref="J16:J17"/>
     <mergeCell ref="K16:K17"/>
@@ -21346,43 +21348,41 @@
     <mergeCell ref="H16:H17"/>
     <mergeCell ref="E43:G43"/>
     <mergeCell ref="G30:G31"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="K44:K45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B2:B3"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="6">
     <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E46:J55 E32:J41 E60:J69 E18:J27 A60:B69 A4:B13 A18:B27 A32:B41 A46:B55 E4:J13" xr:uid="{6E5B312D-12B2-4E48-B8FC-E77197A975F6}"/>
-    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K13 K32:K41 K60:K69 K18:K27 C4:C6 K46:K55" xr:uid="{7F210DE2-4951-4963-BE0D-5F11ACF3936E}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C32:C41 C60:C69 C7:C13 C18:C27 C46:C55" xr:uid="{34DC81E4-AAE3-44D8-9310-9CFB85BBFE25}">
-      <formula1>"鴛　泊,沓　形,鬼　脇,仙法志"</formula1>
-    </dataValidation>
+    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K13 K32:K41 K60:K69 K18:K27 K46:K55" xr:uid="{7F210DE2-4951-4963-BE0D-5F11ACF3936E}"/>
     <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D1:D3 D15 D29 D43 D57" xr:uid="{42938F0F-076F-40EA-BFD9-E1982A6B78CD}"/>
     <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D56 D42 D16:D17 D30:D31 D14 D28 D44:D45 D58:D59 D70:D341" xr:uid="{96817405-941A-41D6-B619-E0307AD1FBC8}">
       <formula1>"国保中央病院,福士水産㈱,高橋水産㈱"</formula1>
     </dataValidation>
     <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D4:D13 D18:D27 D32:D41 D46:D55 D60:D69" xr:uid="{5923DAAC-ED61-4B97-819B-82F0A141C587}">
       <formula1>"国保中央病院,道立鬼脇診療所,カムイウィスキー,福士水産㈱,糀谷商店,米田商店"</formula1>
+    </dataValidation>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C13 C18:C27 C32:C41 C46:C55 C60:C69" xr:uid="{DFCF292D-BEE8-4A9D-BF82-4382295D480D}">
+      <formula1>"鴛 泊,鬼 脇,沓 形,仙法志"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -21416,11 +21416,11 @@
       <c r="D1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="65" t="s">
+      <c r="E1" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
       <c r="J1" s="21"/>
       <c r="K1" s="22"/>
     </row>
@@ -21437,16 +21437,16 @@
       <c r="D2" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="59" t="s">
+      <c r="E2" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="61" t="s">
+      <c r="F2" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="62" t="s">
+      <c r="G2" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="63" t="s">
+      <c r="H2" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="55" t="s">
@@ -21455,7 +21455,7 @@
       <c r="J2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="64" t="s">
+      <c r="K2" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -21464,13 +21464,13 @@
       <c r="B3" s="56"/>
       <c r="C3" s="56"/>
       <c r="D3" s="58"/>
-      <c r="E3" s="60"/>
+      <c r="E3" s="63"/>
       <c r="F3" s="56"/>
       <c r="G3" s="58"/>
-      <c r="H3" s="60"/>
+      <c r="H3" s="63"/>
       <c r="I3" s="56"/>
       <c r="J3" s="56"/>
-      <c r="K3" s="64"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="7"/>
@@ -21655,11 +21655,11 @@
       <c r="D15" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="65" t="s">
+      <c r="E15" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="65"/>
-      <c r="G15" s="65"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="64"/>
       <c r="J15" s="21"/>
       <c r="K15" s="22"/>
     </row>
@@ -21676,16 +21676,16 @@
       <c r="D16" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="59" t="s">
+      <c r="E16" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="61" t="s">
+      <c r="F16" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="62" t="s">
+      <c r="G16" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="63" t="s">
+      <c r="H16" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I16" s="55" t="s">
@@ -21694,7 +21694,7 @@
       <c r="J16" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="64" t="s">
+      <c r="K16" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -21703,13 +21703,13 @@
       <c r="B17" s="56"/>
       <c r="C17" s="56"/>
       <c r="D17" s="58"/>
-      <c r="E17" s="60"/>
+      <c r="E17" s="63"/>
       <c r="F17" s="56"/>
       <c r="G17" s="58"/>
-      <c r="H17" s="60"/>
+      <c r="H17" s="63"/>
       <c r="I17" s="56"/>
       <c r="J17" s="56"/>
-      <c r="K17" s="64"/>
+      <c r="K17" s="60"/>
     </row>
     <row r="18" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7"/>
@@ -21894,11 +21894,11 @@
       <c r="D29" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="65" t="s">
+      <c r="E29" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="65"/>
-      <c r="G29" s="65"/>
+      <c r="F29" s="64"/>
+      <c r="G29" s="64"/>
       <c r="J29" s="21"/>
       <c r="K29" s="22"/>
     </row>
@@ -21915,16 +21915,16 @@
       <c r="D30" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E30" s="59" t="s">
+      <c r="E30" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F30" s="61" t="s">
+      <c r="F30" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G30" s="62" t="s">
+      <c r="G30" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="63" t="s">
+      <c r="H30" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I30" s="55" t="s">
@@ -21933,7 +21933,7 @@
       <c r="J30" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K30" s="64" t="s">
+      <c r="K30" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -21942,13 +21942,13 @@
       <c r="B31" s="56"/>
       <c r="C31" s="56"/>
       <c r="D31" s="58"/>
-      <c r="E31" s="60"/>
+      <c r="E31" s="63"/>
       <c r="F31" s="56"/>
       <c r="G31" s="58"/>
-      <c r="H31" s="60"/>
+      <c r="H31" s="63"/>
       <c r="I31" s="56"/>
       <c r="J31" s="56"/>
-      <c r="K31" s="64"/>
+      <c r="K31" s="60"/>
     </row>
     <row r="32" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7"/>
@@ -22133,11 +22133,11 @@
       <c r="D43" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="65" t="s">
+      <c r="E43" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="65"/>
-      <c r="G43" s="65"/>
+      <c r="F43" s="64"/>
+      <c r="G43" s="64"/>
       <c r="J43" s="21"/>
       <c r="K43" s="22"/>
     </row>
@@ -22154,16 +22154,16 @@
       <c r="D44" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="59" t="s">
+      <c r="E44" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="61" t="s">
+      <c r="F44" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G44" s="62" t="s">
+      <c r="G44" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H44" s="63" t="s">
+      <c r="H44" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I44" s="55" t="s">
@@ -22172,7 +22172,7 @@
       <c r="J44" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="64" t="s">
+      <c r="K44" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -22181,13 +22181,13 @@
       <c r="B45" s="56"/>
       <c r="C45" s="56"/>
       <c r="D45" s="58"/>
-      <c r="E45" s="60"/>
+      <c r="E45" s="63"/>
       <c r="F45" s="56"/>
       <c r="G45" s="58"/>
-      <c r="H45" s="60"/>
+      <c r="H45" s="63"/>
       <c r="I45" s="56"/>
       <c r="J45" s="56"/>
-      <c r="K45" s="64"/>
+      <c r="K45" s="60"/>
     </row>
     <row r="46" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7"/>
@@ -22372,11 +22372,11 @@
       <c r="D57" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E57" s="65" t="s">
+      <c r="E57" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="65"/>
-      <c r="G57" s="65"/>
+      <c r="F57" s="64"/>
+      <c r="G57" s="64"/>
       <c r="J57" s="21"/>
       <c r="K57" s="22"/>
     </row>
@@ -22393,16 +22393,16 @@
       <c r="D58" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="59" t="s">
+      <c r="E58" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F58" s="61" t="s">
+      <c r="F58" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G58" s="62" t="s">
+      <c r="G58" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H58" s="63" t="s">
+      <c r="H58" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I58" s="55" t="s">
@@ -22411,7 +22411,7 @@
       <c r="J58" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K58" s="64" t="s">
+      <c r="K58" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -22420,13 +22420,13 @@
       <c r="B59" s="56"/>
       <c r="C59" s="56"/>
       <c r="D59" s="58"/>
-      <c r="E59" s="60"/>
+      <c r="E59" s="63"/>
       <c r="F59" s="56"/>
       <c r="G59" s="58"/>
-      <c r="H59" s="60"/>
+      <c r="H59" s="63"/>
       <c r="I59" s="56"/>
       <c r="J59" s="56"/>
-      <c r="K59" s="64"/>
+      <c r="K59" s="60"/>
     </row>
     <row r="60" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="7"/>
@@ -22613,27 +22613,29 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
     <mergeCell ref="E57:G57"/>
     <mergeCell ref="J16:J17"/>
     <mergeCell ref="K16:K17"/>
@@ -22650,43 +22652,41 @@
     <mergeCell ref="H16:H17"/>
     <mergeCell ref="E43:G43"/>
     <mergeCell ref="G30:G31"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="K44:K45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B2:B3"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="6">
-    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E46:J55 E32:J41 E60:J69 E18:J27 A60:B69 A4:B13 A18:B27 A32:B41 A46:B55 E4:J13" xr:uid="{6A7031DD-B0E9-428F-AA65-461874A532B1}"/>
-    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K13 K32:K41 K60:K69 K18:K27 C4:C6 K46:K55" xr:uid="{2856CD24-8CB0-46EC-A58E-DAD9C97468EF}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C32:C41 C60:C69 C7:C13 C18:C27 C46:C55" xr:uid="{5A555D96-6CF0-42EA-9540-D53780AF66DC}">
-      <formula1>"鴛　泊,沓　形,鬼　脇,仙法志"</formula1>
-    </dataValidation>
-    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D1:D3 D15 D29 D43 D57" xr:uid="{A580724A-C463-4CD9-B3ED-B1315ECE5266}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D56 D42 D16:D17 D30:D31 D14 D28 D44:D45 D58:D59 D70:D341" xr:uid="{B6157F60-8FD2-4050-AD83-16B9C26C79B7}">
+    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E46:J55 E32:J41 E60:J69 E18:J27 A60:B69 A4:B13 A18:B27 A32:B41 A46:B55 E4:J13" xr:uid="{477AD3C8-354D-47DF-9FFD-32F79FC2EF0C}"/>
+    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K13 K32:K41 K60:K69 K18:K27 K46:K55" xr:uid="{FA3F6AAE-448B-4E0A-AE86-FAEC6ED80C9D}"/>
+    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D1:D3 D15 D29 D43 D57" xr:uid="{CE0C0FCD-30AD-4F4F-ADDD-C0959EAF5CA1}"/>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D56 D42 D16:D17 D30:D31 D14 D28 D44:D45 D58:D59 D70:D341" xr:uid="{D8256A2D-0636-4632-BF1E-B7F3D76D7135}">
       <formula1>"国保中央病院,福士水産㈱,高橋水産㈱"</formula1>
     </dataValidation>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D4:D13 D18:D27 D32:D41 D46:D55 D60:D69" xr:uid="{717A7D07-02CB-46D4-882F-90787EDBB406}">
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D4:D13 D18:D27 D32:D41 D46:D55 D60:D69" xr:uid="{ABBF72AA-EE67-4021-B64A-9826E53BA84A}">
       <formula1>"国保中央病院,道立鬼脇診療所,カムイウィスキー,福士水産㈱,糀谷商店,米田商店"</formula1>
+    </dataValidation>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C13 C18:C27 C32:C41 C46:C55 C60:C69" xr:uid="{43D4C2A0-ADC3-4EA2-BF4D-8B3E5FD12EA7}">
+      <formula1>"鴛 泊,鬼 脇,沓 形,仙法志"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -22720,11 +22720,11 @@
       <c r="D1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="65" t="s">
+      <c r="E1" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
       <c r="J1" s="21"/>
       <c r="K1" s="22"/>
     </row>
@@ -22741,16 +22741,16 @@
       <c r="D2" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="59" t="s">
+      <c r="E2" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="61" t="s">
+      <c r="F2" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="62" t="s">
+      <c r="G2" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="63" t="s">
+      <c r="H2" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="55" t="s">
@@ -22759,7 +22759,7 @@
       <c r="J2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="64" t="s">
+      <c r="K2" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -22768,13 +22768,13 @@
       <c r="B3" s="56"/>
       <c r="C3" s="56"/>
       <c r="D3" s="58"/>
-      <c r="E3" s="60"/>
+      <c r="E3" s="63"/>
       <c r="F3" s="56"/>
       <c r="G3" s="58"/>
-      <c r="H3" s="60"/>
+      <c r="H3" s="63"/>
       <c r="I3" s="56"/>
       <c r="J3" s="56"/>
-      <c r="K3" s="64"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="7"/>
@@ -22959,11 +22959,11 @@
       <c r="D15" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="65" t="s">
+      <c r="E15" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="65"/>
-      <c r="G15" s="65"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="64"/>
       <c r="J15" s="21"/>
       <c r="K15" s="22"/>
     </row>
@@ -22980,16 +22980,16 @@
       <c r="D16" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="59" t="s">
+      <c r="E16" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="61" t="s">
+      <c r="F16" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="62" t="s">
+      <c r="G16" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="63" t="s">
+      <c r="H16" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I16" s="55" t="s">
@@ -22998,7 +22998,7 @@
       <c r="J16" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="64" t="s">
+      <c r="K16" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -23007,13 +23007,13 @@
       <c r="B17" s="56"/>
       <c r="C17" s="56"/>
       <c r="D17" s="58"/>
-      <c r="E17" s="60"/>
+      <c r="E17" s="63"/>
       <c r="F17" s="56"/>
       <c r="G17" s="58"/>
-      <c r="H17" s="60"/>
+      <c r="H17" s="63"/>
       <c r="I17" s="56"/>
       <c r="J17" s="56"/>
-      <c r="K17" s="64"/>
+      <c r="K17" s="60"/>
     </row>
     <row r="18" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7"/>
@@ -23198,11 +23198,11 @@
       <c r="D29" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="65" t="s">
+      <c r="E29" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="65"/>
-      <c r="G29" s="65"/>
+      <c r="F29" s="64"/>
+      <c r="G29" s="64"/>
       <c r="J29" s="21"/>
       <c r="K29" s="22"/>
     </row>
@@ -23219,16 +23219,16 @@
       <c r="D30" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E30" s="59" t="s">
+      <c r="E30" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F30" s="61" t="s">
+      <c r="F30" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G30" s="62" t="s">
+      <c r="G30" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="63" t="s">
+      <c r="H30" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I30" s="55" t="s">
@@ -23237,7 +23237,7 @@
       <c r="J30" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K30" s="64" t="s">
+      <c r="K30" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -23246,13 +23246,13 @@
       <c r="B31" s="56"/>
       <c r="C31" s="56"/>
       <c r="D31" s="58"/>
-      <c r="E31" s="60"/>
+      <c r="E31" s="63"/>
       <c r="F31" s="56"/>
       <c r="G31" s="58"/>
-      <c r="H31" s="60"/>
+      <c r="H31" s="63"/>
       <c r="I31" s="56"/>
       <c r="J31" s="56"/>
-      <c r="K31" s="64"/>
+      <c r="K31" s="60"/>
     </row>
     <row r="32" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7"/>
@@ -23437,11 +23437,11 @@
       <c r="D43" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="65" t="s">
+      <c r="E43" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="65"/>
-      <c r="G43" s="65"/>
+      <c r="F43" s="64"/>
+      <c r="G43" s="64"/>
       <c r="J43" s="21"/>
       <c r="K43" s="22"/>
     </row>
@@ -23458,16 +23458,16 @@
       <c r="D44" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="59" t="s">
+      <c r="E44" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="61" t="s">
+      <c r="F44" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G44" s="62" t="s">
+      <c r="G44" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H44" s="63" t="s">
+      <c r="H44" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I44" s="55" t="s">
@@ -23476,7 +23476,7 @@
       <c r="J44" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="64" t="s">
+      <c r="K44" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -23485,13 +23485,13 @@
       <c r="B45" s="56"/>
       <c r="C45" s="56"/>
       <c r="D45" s="58"/>
-      <c r="E45" s="60"/>
+      <c r="E45" s="63"/>
       <c r="F45" s="56"/>
       <c r="G45" s="58"/>
-      <c r="H45" s="60"/>
+      <c r="H45" s="63"/>
       <c r="I45" s="56"/>
       <c r="J45" s="56"/>
-      <c r="K45" s="64"/>
+      <c r="K45" s="60"/>
     </row>
     <row r="46" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7"/>
@@ -23676,11 +23676,11 @@
       <c r="D57" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E57" s="65" t="s">
+      <c r="E57" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="65"/>
-      <c r="G57" s="65"/>
+      <c r="F57" s="64"/>
+      <c r="G57" s="64"/>
       <c r="J57" s="21"/>
       <c r="K57" s="22"/>
     </row>
@@ -23697,16 +23697,16 @@
       <c r="D58" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="59" t="s">
+      <c r="E58" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F58" s="61" t="s">
+      <c r="F58" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G58" s="62" t="s">
+      <c r="G58" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H58" s="63" t="s">
+      <c r="H58" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I58" s="55" t="s">
@@ -23715,7 +23715,7 @@
       <c r="J58" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K58" s="64" t="s">
+      <c r="K58" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -23724,13 +23724,13 @@
       <c r="B59" s="56"/>
       <c r="C59" s="56"/>
       <c r="D59" s="58"/>
-      <c r="E59" s="60"/>
+      <c r="E59" s="63"/>
       <c r="F59" s="56"/>
       <c r="G59" s="58"/>
-      <c r="H59" s="60"/>
+      <c r="H59" s="63"/>
       <c r="I59" s="56"/>
       <c r="J59" s="56"/>
-      <c r="K59" s="64"/>
+      <c r="K59" s="60"/>
     </row>
     <row r="60" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="7"/>
@@ -23917,25 +23917,35 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="K44:K45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="K30:K31"/>
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="C30:C31"/>
@@ -23948,49 +23958,39 @@
     <mergeCell ref="E44:E45"/>
     <mergeCell ref="F44:F45"/>
     <mergeCell ref="G44:G45"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="K30:K31"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="6">
-    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E46:J55 E32:J41 E60:J69 E18:J27 A60:B69 A4:B13 A18:B27 A32:B41 A46:B55 E4:J13" xr:uid="{E565C334-7B1E-4F3C-A689-9575D82165E7}"/>
-    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K13 K32:K41 K60:K69 K18:K27 C4:C6 K46:K55" xr:uid="{1DBC47AC-2DE0-471F-8B2E-E68FE40C71AF}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C32:C41 C60:C69 C7:C13 C18:C27 C46:C55" xr:uid="{B28CB0B2-A1D1-421C-AED3-39F7AA35EFD2}">
-      <formula1>"鴛　泊,沓　形,鬼　脇,仙法志"</formula1>
-    </dataValidation>
-    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D1:D3 D15 D29 D43 D57" xr:uid="{990DCC30-9DF6-47DC-8B35-11244BDB8256}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D56 D42 D16:D17 D30:D31 D14 D28 D44:D45 D58:D59 D70:D341" xr:uid="{A88400CB-F622-42A3-A807-14CF99285D2F}">
+    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E46:J55 E32:J41 E60:J69 E18:J27 A60:B69 A4:B13 A18:B27 A32:B41 A46:B55 E4:J13" xr:uid="{E8F85296-B43F-4D46-8EE9-0630EB3DF98B}"/>
+    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K13 K32:K41 K60:K69 K18:K27 K46:K55" xr:uid="{6540E148-0A91-4587-9F17-CAF1DD07CD29}"/>
+    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D1:D3 D15 D29 D43 D57" xr:uid="{5AA2E9B0-DD15-4B3B-A7C9-60BBF94E0CEC}"/>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D56 D42 D16:D17 D30:D31 D14 D28 D44:D45 D58:D59 D70:D341" xr:uid="{5A7DA553-FCFC-4445-92A0-5E621F347A67}">
       <formula1>"国保中央病院,福士水産㈱,高橋水産㈱"</formula1>
     </dataValidation>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D4:D13 D18:D27 D32:D41 D46:D55 D60:D69" xr:uid="{51E06B70-53D7-45A9-B41D-D24893A2A96C}">
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D4:D13 D18:D27 D32:D41 D46:D55 D60:D69" xr:uid="{3576D791-1371-4F09-9F5B-2D4117D17D68}">
       <formula1>"国保中央病院,道立鬼脇診療所,カムイウィスキー,福士水産㈱,糀谷商店,米田商店"</formula1>
+    </dataValidation>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C13 C18:C27 C32:C41 C46:C55 C60:C69" xr:uid="{0F9A8A56-C49E-4DC7-AD42-9A8B8157AC14}">
+      <formula1>"鴛 泊,鬼 脇,沓 形,仙法志"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -24024,11 +24024,11 @@
       <c r="D1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="65" t="s">
+      <c r="E1" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
       <c r="J1" s="21"/>
       <c r="K1" s="22"/>
     </row>
@@ -24045,16 +24045,16 @@
       <c r="D2" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="59" t="s">
+      <c r="E2" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="61" t="s">
+      <c r="F2" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="62" t="s">
+      <c r="G2" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="63" t="s">
+      <c r="H2" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="55" t="s">
@@ -24063,7 +24063,7 @@
       <c r="J2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="64" t="s">
+      <c r="K2" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -24072,13 +24072,13 @@
       <c r="B3" s="56"/>
       <c r="C3" s="56"/>
       <c r="D3" s="58"/>
-      <c r="E3" s="60"/>
+      <c r="E3" s="63"/>
       <c r="F3" s="56"/>
       <c r="G3" s="58"/>
-      <c r="H3" s="60"/>
+      <c r="H3" s="63"/>
       <c r="I3" s="56"/>
       <c r="J3" s="56"/>
-      <c r="K3" s="64"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="7"/>
@@ -24263,11 +24263,11 @@
       <c r="D15" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="65" t="s">
+      <c r="E15" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="65"/>
-      <c r="G15" s="65"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="64"/>
       <c r="J15" s="21"/>
       <c r="K15" s="22"/>
     </row>
@@ -24284,16 +24284,16 @@
       <c r="D16" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="59" t="s">
+      <c r="E16" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="61" t="s">
+      <c r="F16" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="62" t="s">
+      <c r="G16" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="63" t="s">
+      <c r="H16" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I16" s="55" t="s">
@@ -24302,7 +24302,7 @@
       <c r="J16" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="64" t="s">
+      <c r="K16" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -24311,13 +24311,13 @@
       <c r="B17" s="56"/>
       <c r="C17" s="56"/>
       <c r="D17" s="58"/>
-      <c r="E17" s="60"/>
+      <c r="E17" s="63"/>
       <c r="F17" s="56"/>
       <c r="G17" s="58"/>
-      <c r="H17" s="60"/>
+      <c r="H17" s="63"/>
       <c r="I17" s="56"/>
       <c r="J17" s="56"/>
-      <c r="K17" s="64"/>
+      <c r="K17" s="60"/>
     </row>
     <row r="18" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7"/>
@@ -24502,11 +24502,11 @@
       <c r="D29" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="65" t="s">
+      <c r="E29" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="65"/>
-      <c r="G29" s="65"/>
+      <c r="F29" s="64"/>
+      <c r="G29" s="64"/>
       <c r="J29" s="21"/>
       <c r="K29" s="22"/>
     </row>
@@ -24523,16 +24523,16 @@
       <c r="D30" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E30" s="59" t="s">
+      <c r="E30" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F30" s="61" t="s">
+      <c r="F30" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G30" s="62" t="s">
+      <c r="G30" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="63" t="s">
+      <c r="H30" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I30" s="55" t="s">
@@ -24541,7 +24541,7 @@
       <c r="J30" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K30" s="64" t="s">
+      <c r="K30" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -24550,13 +24550,13 @@
       <c r="B31" s="56"/>
       <c r="C31" s="56"/>
       <c r="D31" s="58"/>
-      <c r="E31" s="60"/>
+      <c r="E31" s="63"/>
       <c r="F31" s="56"/>
       <c r="G31" s="58"/>
-      <c r="H31" s="60"/>
+      <c r="H31" s="63"/>
       <c r="I31" s="56"/>
       <c r="J31" s="56"/>
-      <c r="K31" s="64"/>
+      <c r="K31" s="60"/>
     </row>
     <row r="32" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7"/>
@@ -24741,11 +24741,11 @@
       <c r="D43" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="65" t="s">
+      <c r="E43" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="65"/>
-      <c r="G43" s="65"/>
+      <c r="F43" s="64"/>
+      <c r="G43" s="64"/>
       <c r="J43" s="21"/>
       <c r="K43" s="22"/>
     </row>
@@ -24762,16 +24762,16 @@
       <c r="D44" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="59" t="s">
+      <c r="E44" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="61" t="s">
+      <c r="F44" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G44" s="62" t="s">
+      <c r="G44" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H44" s="63" t="s">
+      <c r="H44" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I44" s="55" t="s">
@@ -24780,7 +24780,7 @@
       <c r="J44" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="64" t="s">
+      <c r="K44" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -24789,13 +24789,13 @@
       <c r="B45" s="56"/>
       <c r="C45" s="56"/>
       <c r="D45" s="58"/>
-      <c r="E45" s="60"/>
+      <c r="E45" s="63"/>
       <c r="F45" s="56"/>
       <c r="G45" s="58"/>
-      <c r="H45" s="60"/>
+      <c r="H45" s="63"/>
       <c r="I45" s="56"/>
       <c r="J45" s="56"/>
-      <c r="K45" s="64"/>
+      <c r="K45" s="60"/>
     </row>
     <row r="46" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7"/>
@@ -24980,11 +24980,11 @@
       <c r="D57" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E57" s="65" t="s">
+      <c r="E57" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="65"/>
-      <c r="G57" s="65"/>
+      <c r="F57" s="64"/>
+      <c r="G57" s="64"/>
       <c r="J57" s="21"/>
       <c r="K57" s="22"/>
     </row>
@@ -25001,16 +25001,16 @@
       <c r="D58" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="59" t="s">
+      <c r="E58" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F58" s="61" t="s">
+      <c r="F58" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G58" s="62" t="s">
+      <c r="G58" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H58" s="63" t="s">
+      <c r="H58" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I58" s="55" t="s">
@@ -25019,7 +25019,7 @@
       <c r="J58" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K58" s="64" t="s">
+      <c r="K58" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -25028,13 +25028,13 @@
       <c r="B59" s="56"/>
       <c r="C59" s="56"/>
       <c r="D59" s="58"/>
-      <c r="E59" s="60"/>
+      <c r="E59" s="63"/>
       <c r="F59" s="56"/>
       <c r="G59" s="58"/>
-      <c r="H59" s="60"/>
+      <c r="H59" s="63"/>
       <c r="I59" s="56"/>
       <c r="J59" s="56"/>
-      <c r="K59" s="64"/>
+      <c r="K59" s="60"/>
     </row>
     <row r="60" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="7"/>
@@ -25221,25 +25221,35 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="K44:K45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="K30:K31"/>
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="C30:C31"/>
@@ -25252,49 +25262,39 @@
     <mergeCell ref="E44:E45"/>
     <mergeCell ref="F44:F45"/>
     <mergeCell ref="G44:G45"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="K30:K31"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="6">
-    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E46:J55 E32:J41 E60:J69 E18:J27 A60:B69 A4:B13 A18:B27 A32:B41 A46:B55 E4:J13" xr:uid="{AC025C52-5D59-4089-822C-D31ED178187F}"/>
-    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K13 K32:K41 K60:K69 K18:K27 C4:C6 K46:K55" xr:uid="{17A56ED4-EF1F-443C-A2B5-4F3A7090E050}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C32:C41 C60:C69 C7:C13 C18:C27 C46:C55" xr:uid="{74AF2C51-3531-42E2-B8CB-91319A030F81}">
-      <formula1>"鴛　泊,沓　形,鬼　脇,仙法志"</formula1>
-    </dataValidation>
-    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D1:D3 D15 D29 D43 D57" xr:uid="{17F24833-C5BB-47FD-924A-32EDB641CE04}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D56 D42 D16:D17 D30:D31 D14 D28 D44:D45 D58:D59 D70:D341" xr:uid="{C44E50ED-12B1-4AE5-BCB2-C1DA65DF23CC}">
+    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E46:J55 E32:J41 E60:J69 E18:J27 A60:B69 A4:B13 A18:B27 A32:B41 A46:B55 E4:J13" xr:uid="{CFC4F041-3E55-473F-B578-8A79998EEAFC}"/>
+    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K13 K32:K41 K60:K69 K18:K27 K46:K55" xr:uid="{2BE643CC-BA86-4FB3-8F22-FD93B6FB6A59}"/>
+    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D1:D3 D15 D29 D43 D57" xr:uid="{CA8A04C6-9F31-4DDB-A9E9-F534D9EDDF0B}"/>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D56 D42 D16:D17 D30:D31 D14 D28 D44:D45 D58:D59 D70:D341" xr:uid="{AEE4FBF6-9B5F-4429-8008-C5FA66C33E0D}">
       <formula1>"国保中央病院,福士水産㈱,高橋水産㈱"</formula1>
     </dataValidation>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D4:D13 D18:D27 D32:D41 D46:D55 D60:D69" xr:uid="{177A9EE6-B126-4E95-A6D6-DDAE64ACBDD0}">
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D4:D13 D18:D27 D32:D41 D46:D55 D60:D69" xr:uid="{285D9136-69F9-4D70-AF75-2263B453513B}">
       <formula1>"国保中央病院,道立鬼脇診療所,カムイウィスキー,福士水産㈱,糀谷商店,米田商店"</formula1>
+    </dataValidation>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C13 C18:C27 C32:C41 C46:C55 C60:C69" xr:uid="{511EE8EB-8027-4127-8E9F-31C16F38FE33}">
+      <formula1>"鴛 泊,鬼 脇,沓 形,仙法志"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -25328,11 +25328,11 @@
       <c r="D1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="65" t="s">
+      <c r="E1" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
       <c r="J1" s="21"/>
       <c r="K1" s="22"/>
     </row>
@@ -25349,16 +25349,16 @@
       <c r="D2" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="59" t="s">
+      <c r="E2" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="61" t="s">
+      <c r="F2" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="62" t="s">
+      <c r="G2" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="63" t="s">
+      <c r="H2" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="55" t="s">
@@ -25367,7 +25367,7 @@
       <c r="J2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="64" t="s">
+      <c r="K2" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -25376,13 +25376,13 @@
       <c r="B3" s="56"/>
       <c r="C3" s="56"/>
       <c r="D3" s="58"/>
-      <c r="E3" s="60"/>
+      <c r="E3" s="63"/>
       <c r="F3" s="56"/>
       <c r="G3" s="58"/>
-      <c r="H3" s="60"/>
+      <c r="H3" s="63"/>
       <c r="I3" s="56"/>
       <c r="J3" s="56"/>
-      <c r="K3" s="64"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="7"/>
@@ -25567,11 +25567,11 @@
       <c r="D15" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="65" t="s">
+      <c r="E15" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="65"/>
-      <c r="G15" s="65"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="64"/>
       <c r="J15" s="21"/>
       <c r="K15" s="22"/>
     </row>
@@ -25588,16 +25588,16 @@
       <c r="D16" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="59" t="s">
+      <c r="E16" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="61" t="s">
+      <c r="F16" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="62" t="s">
+      <c r="G16" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="63" t="s">
+      <c r="H16" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I16" s="55" t="s">
@@ -25606,7 +25606,7 @@
       <c r="J16" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="64" t="s">
+      <c r="K16" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -25615,13 +25615,13 @@
       <c r="B17" s="56"/>
       <c r="C17" s="56"/>
       <c r="D17" s="58"/>
-      <c r="E17" s="60"/>
+      <c r="E17" s="63"/>
       <c r="F17" s="56"/>
       <c r="G17" s="58"/>
-      <c r="H17" s="60"/>
+      <c r="H17" s="63"/>
       <c r="I17" s="56"/>
       <c r="J17" s="56"/>
-      <c r="K17" s="64"/>
+      <c r="K17" s="60"/>
     </row>
     <row r="18" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7"/>
@@ -25806,11 +25806,11 @@
       <c r="D29" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="65" t="s">
+      <c r="E29" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="65"/>
-      <c r="G29" s="65"/>
+      <c r="F29" s="64"/>
+      <c r="G29" s="64"/>
       <c r="J29" s="21"/>
       <c r="K29" s="22"/>
     </row>
@@ -25827,16 +25827,16 @@
       <c r="D30" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E30" s="59" t="s">
+      <c r="E30" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F30" s="61" t="s">
+      <c r="F30" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G30" s="62" t="s">
+      <c r="G30" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="63" t="s">
+      <c r="H30" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I30" s="55" t="s">
@@ -25845,7 +25845,7 @@
       <c r="J30" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K30" s="64" t="s">
+      <c r="K30" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -25854,13 +25854,13 @@
       <c r="B31" s="56"/>
       <c r="C31" s="56"/>
       <c r="D31" s="58"/>
-      <c r="E31" s="60"/>
+      <c r="E31" s="63"/>
       <c r="F31" s="56"/>
       <c r="G31" s="58"/>
-      <c r="H31" s="60"/>
+      <c r="H31" s="63"/>
       <c r="I31" s="56"/>
       <c r="J31" s="56"/>
-      <c r="K31" s="64"/>
+      <c r="K31" s="60"/>
     </row>
     <row r="32" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7"/>
@@ -26045,11 +26045,11 @@
       <c r="D43" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="65" t="s">
+      <c r="E43" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="65"/>
-      <c r="G43" s="65"/>
+      <c r="F43" s="64"/>
+      <c r="G43" s="64"/>
       <c r="J43" s="21"/>
       <c r="K43" s="22"/>
     </row>
@@ -26066,16 +26066,16 @@
       <c r="D44" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="59" t="s">
+      <c r="E44" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="61" t="s">
+      <c r="F44" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G44" s="62" t="s">
+      <c r="G44" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H44" s="63" t="s">
+      <c r="H44" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I44" s="55" t="s">
@@ -26084,7 +26084,7 @@
       <c r="J44" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="64" t="s">
+      <c r="K44" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -26093,13 +26093,13 @@
       <c r="B45" s="56"/>
       <c r="C45" s="56"/>
       <c r="D45" s="58"/>
-      <c r="E45" s="60"/>
+      <c r="E45" s="63"/>
       <c r="F45" s="56"/>
       <c r="G45" s="58"/>
-      <c r="H45" s="60"/>
+      <c r="H45" s="63"/>
       <c r="I45" s="56"/>
       <c r="J45" s="56"/>
-      <c r="K45" s="64"/>
+      <c r="K45" s="60"/>
     </row>
     <row r="46" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7"/>
@@ -26284,11 +26284,11 @@
       <c r="D57" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E57" s="65" t="s">
+      <c r="E57" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="65"/>
-      <c r="G57" s="65"/>
+      <c r="F57" s="64"/>
+      <c r="G57" s="64"/>
       <c r="J57" s="21"/>
       <c r="K57" s="22"/>
     </row>
@@ -26305,16 +26305,16 @@
       <c r="D58" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="59" t="s">
+      <c r="E58" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F58" s="61" t="s">
+      <c r="F58" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G58" s="62" t="s">
+      <c r="G58" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H58" s="63" t="s">
+      <c r="H58" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I58" s="55" t="s">
@@ -26323,7 +26323,7 @@
       <c r="J58" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K58" s="64" t="s">
+      <c r="K58" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -26332,13 +26332,13 @@
       <c r="B59" s="56"/>
       <c r="C59" s="56"/>
       <c r="D59" s="58"/>
-      <c r="E59" s="60"/>
+      <c r="E59" s="63"/>
       <c r="F59" s="56"/>
       <c r="G59" s="58"/>
-      <c r="H59" s="60"/>
+      <c r="H59" s="63"/>
       <c r="I59" s="56"/>
       <c r="J59" s="56"/>
-      <c r="K59" s="64"/>
+      <c r="K59" s="60"/>
     </row>
     <row r="60" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="7"/>
@@ -26525,27 +26525,29 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
     <mergeCell ref="E57:G57"/>
     <mergeCell ref="J16:J17"/>
     <mergeCell ref="K16:K17"/>
@@ -26562,43 +26564,41 @@
     <mergeCell ref="H16:H17"/>
     <mergeCell ref="E43:G43"/>
     <mergeCell ref="G30:G31"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="K44:K45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B2:B3"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="6">
-    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E46:J55 E32:J41 E60:J69 E18:J27 A60:B69 A4:B13 A18:B27 A32:B41 A46:B55 E4:J13" xr:uid="{F0BD45DF-C49C-4ED2-8E32-DD4E55E0C53D}"/>
-    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K13 K32:K41 K60:K69 K18:K27 C4:C6 K46:K55" xr:uid="{F351DD2B-3A26-42F5-8983-787B7296808C}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C32:C41 C60:C69 C7:C13 C18:C27 C46:C55" xr:uid="{824541A2-4AEA-4478-8D21-D83C2698EF5F}">
-      <formula1>"鴛　泊,沓　形,鬼　脇,仙法志"</formula1>
-    </dataValidation>
-    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D1:D3 D15 D29 D43 D57" xr:uid="{82E85D2D-19FC-4EF7-AFB6-C3F33BE4A9D7}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D56 D42 D16:D17 D30:D31 D14 D28 D44:D45 D58:D59 D70:D341" xr:uid="{6FB028BA-CFD6-4479-A9A0-BDF35F47BB25}">
+    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E46:J55 E32:J41 E60:J69 E18:J27 A60:B69 A4:B13 A18:B27 A32:B41 A46:B55 E4:J13" xr:uid="{68DFC828-DF15-46C1-BACE-1E03C736E910}"/>
+    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K13 K32:K41 K60:K69 K18:K27 K46:K55" xr:uid="{9AD781C6-77E4-4534-900D-E4F01FC2573B}"/>
+    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D1:D3 D15 D29 D43 D57" xr:uid="{127CD1A0-04A5-4CF5-8D9C-BA5E3A1FB692}"/>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D56 D42 D16:D17 D30:D31 D14 D28 D44:D45 D58:D59 D70:D341" xr:uid="{54F5C0E4-D49D-435B-BBFB-E60AEDEC7D76}">
       <formula1>"国保中央病院,福士水産㈱,高橋水産㈱"</formula1>
     </dataValidation>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D4:D13 D18:D27 D32:D41 D46:D55 D60:D69" xr:uid="{F40EFA6B-4B86-4153-ADF9-BC16685CBB1E}">
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D4:D13 D18:D27 D32:D41 D46:D55 D60:D69" xr:uid="{AD42AD07-CE21-4387-8DE0-31B17B663DEF}">
       <formula1>"国保中央病院,道立鬼脇診療所,カムイウィスキー,福士水産㈱,糀谷商店,米田商店"</formula1>
+    </dataValidation>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C13 C18:C27 C32:C41 C46:C55 C60:C69" xr:uid="{D498DAD0-9DCB-4182-97E3-CE2A0DF2CD3C}">
+      <formula1>"鴛 泊,鬼 脇,沓 形,仙法志"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -26632,11 +26632,11 @@
       <c r="D1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="65" t="s">
+      <c r="E1" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
       <c r="J1" s="21"/>
       <c r="K1" s="22"/>
     </row>
@@ -26653,16 +26653,16 @@
       <c r="D2" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="59" t="s">
+      <c r="E2" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="61" t="s">
+      <c r="F2" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="62" t="s">
+      <c r="G2" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="63" t="s">
+      <c r="H2" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="55" t="s">
@@ -26671,7 +26671,7 @@
       <c r="J2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="64" t="s">
+      <c r="K2" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -26680,13 +26680,13 @@
       <c r="B3" s="56"/>
       <c r="C3" s="56"/>
       <c r="D3" s="58"/>
-      <c r="E3" s="60"/>
+      <c r="E3" s="63"/>
       <c r="F3" s="56"/>
       <c r="G3" s="58"/>
-      <c r="H3" s="60"/>
+      <c r="H3" s="63"/>
       <c r="I3" s="56"/>
       <c r="J3" s="56"/>
-      <c r="K3" s="64"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="7"/>
@@ -26871,11 +26871,11 @@
       <c r="D15" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="65" t="s">
+      <c r="E15" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="65"/>
-      <c r="G15" s="65"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="64"/>
       <c r="J15" s="21"/>
       <c r="K15" s="22"/>
     </row>
@@ -26892,16 +26892,16 @@
       <c r="D16" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="59" t="s">
+      <c r="E16" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="61" t="s">
+      <c r="F16" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="62" t="s">
+      <c r="G16" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="63" t="s">
+      <c r="H16" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I16" s="55" t="s">
@@ -26910,7 +26910,7 @@
       <c r="J16" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="64" t="s">
+      <c r="K16" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -26919,13 +26919,13 @@
       <c r="B17" s="56"/>
       <c r="C17" s="56"/>
       <c r="D17" s="58"/>
-      <c r="E17" s="60"/>
+      <c r="E17" s="63"/>
       <c r="F17" s="56"/>
       <c r="G17" s="58"/>
-      <c r="H17" s="60"/>
+      <c r="H17" s="63"/>
       <c r="I17" s="56"/>
       <c r="J17" s="56"/>
-      <c r="K17" s="64"/>
+      <c r="K17" s="60"/>
     </row>
     <row r="18" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7"/>
@@ -27110,11 +27110,11 @@
       <c r="D29" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="65" t="s">
+      <c r="E29" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="65"/>
-      <c r="G29" s="65"/>
+      <c r="F29" s="64"/>
+      <c r="G29" s="64"/>
       <c r="J29" s="21"/>
       <c r="K29" s="22"/>
     </row>
@@ -27131,16 +27131,16 @@
       <c r="D30" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E30" s="59" t="s">
+      <c r="E30" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F30" s="61" t="s">
+      <c r="F30" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G30" s="62" t="s">
+      <c r="G30" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="63" t="s">
+      <c r="H30" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I30" s="55" t="s">
@@ -27149,7 +27149,7 @@
       <c r="J30" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K30" s="64" t="s">
+      <c r="K30" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -27158,13 +27158,13 @@
       <c r="B31" s="56"/>
       <c r="C31" s="56"/>
       <c r="D31" s="58"/>
-      <c r="E31" s="60"/>
+      <c r="E31" s="63"/>
       <c r="F31" s="56"/>
       <c r="G31" s="58"/>
-      <c r="H31" s="60"/>
+      <c r="H31" s="63"/>
       <c r="I31" s="56"/>
       <c r="J31" s="56"/>
-      <c r="K31" s="64"/>
+      <c r="K31" s="60"/>
     </row>
     <row r="32" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7"/>
@@ -27349,11 +27349,11 @@
       <c r="D43" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="65" t="s">
+      <c r="E43" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="65"/>
-      <c r="G43" s="65"/>
+      <c r="F43" s="64"/>
+      <c r="G43" s="64"/>
       <c r="J43" s="21"/>
       <c r="K43" s="22"/>
     </row>
@@ -27370,16 +27370,16 @@
       <c r="D44" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="59" t="s">
+      <c r="E44" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="61" t="s">
+      <c r="F44" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G44" s="62" t="s">
+      <c r="G44" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H44" s="63" t="s">
+      <c r="H44" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I44" s="55" t="s">
@@ -27388,7 +27388,7 @@
       <c r="J44" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="64" t="s">
+      <c r="K44" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -27397,13 +27397,13 @@
       <c r="B45" s="56"/>
       <c r="C45" s="56"/>
       <c r="D45" s="58"/>
-      <c r="E45" s="60"/>
+      <c r="E45" s="63"/>
       <c r="F45" s="56"/>
       <c r="G45" s="58"/>
-      <c r="H45" s="60"/>
+      <c r="H45" s="63"/>
       <c r="I45" s="56"/>
       <c r="J45" s="56"/>
-      <c r="K45" s="64"/>
+      <c r="K45" s="60"/>
     </row>
     <row r="46" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7"/>
@@ -27588,11 +27588,11 @@
       <c r="D57" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E57" s="65" t="s">
+      <c r="E57" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="65"/>
-      <c r="G57" s="65"/>
+      <c r="F57" s="64"/>
+      <c r="G57" s="64"/>
       <c r="J57" s="21"/>
       <c r="K57" s="22"/>
     </row>
@@ -27609,16 +27609,16 @@
       <c r="D58" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="59" t="s">
+      <c r="E58" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F58" s="61" t="s">
+      <c r="F58" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G58" s="62" t="s">
+      <c r="G58" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H58" s="63" t="s">
+      <c r="H58" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I58" s="55" t="s">
@@ -27627,7 +27627,7 @@
       <c r="J58" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K58" s="64" t="s">
+      <c r="K58" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -27636,13 +27636,13 @@
       <c r="B59" s="56"/>
       <c r="C59" s="56"/>
       <c r="D59" s="58"/>
-      <c r="E59" s="60"/>
+      <c r="E59" s="63"/>
       <c r="F59" s="56"/>
       <c r="G59" s="58"/>
-      <c r="H59" s="60"/>
+      <c r="H59" s="63"/>
       <c r="I59" s="56"/>
       <c r="J59" s="56"/>
-      <c r="K59" s="64"/>
+      <c r="K59" s="60"/>
     </row>
     <row r="60" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="7"/>
@@ -27829,25 +27829,35 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="K44:K45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="K30:K31"/>
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="C30:C31"/>
@@ -27860,49 +27870,39 @@
     <mergeCell ref="E44:E45"/>
     <mergeCell ref="F44:F45"/>
     <mergeCell ref="G44:G45"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="K30:K31"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="6">
-    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E46:J55 E32:J41 E60:J69 E18:J27 A60:B69 A4:B13 A18:B27 A32:B41 A46:B55 E4:J13" xr:uid="{436C2026-31B8-4047-A29F-F8D458E8BF31}"/>
-    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K13 K32:K41 K60:K69 K18:K27 C4:C6 K46:K55" xr:uid="{775A41CB-A2BF-4DDB-9EA4-BBE0FE5CFA2A}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C32:C41 C60:C69 C7:C13 C18:C27 C46:C55" xr:uid="{B35C0FD4-464C-4B83-B3DC-AD86FF5C52B0}">
-      <formula1>"鴛　泊,沓　形,鬼　脇,仙法志"</formula1>
-    </dataValidation>
-    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D1:D3 D15 D29 D43 D57" xr:uid="{226A4771-8D1F-4A8A-8BC9-67102018F4BF}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D56 D42 D16:D17 D30:D31 D14 D28 D44:D45 D58:D59 D70:D341" xr:uid="{66D28365-710B-4222-B706-EA4723B3D7A9}">
+    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E46:J55 E32:J41 E60:J69 E18:J27 A60:B69 A4:B13 A18:B27 A32:B41 A46:B55 E4:J13" xr:uid="{019E84E0-321E-4738-AC5E-FCD8EE4BF162}"/>
+    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K13 K32:K41 K60:K69 K18:K27 K46:K55" xr:uid="{8CF5DBF0-7672-4805-ADDF-307827F68006}"/>
+    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D1:D3 D15 D29 D43 D57" xr:uid="{8E4E3C4C-861B-414C-80B3-42E24095F1E7}"/>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D56 D42 D16:D17 D30:D31 D14 D28 D44:D45 D58:D59 D70:D341" xr:uid="{31E908D9-C6DF-49E8-BA13-4066ED606994}">
       <formula1>"国保中央病院,福士水産㈱,高橋水産㈱"</formula1>
     </dataValidation>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D4:D13 D18:D27 D32:D41 D46:D55 D60:D69" xr:uid="{F048D338-6C9F-431C-84F4-4725C7735543}">
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D4:D13 D18:D27 D32:D41 D46:D55 D60:D69" xr:uid="{A700E6F7-BA2D-4612-BB15-4EC550A246B1}">
       <formula1>"国保中央病院,道立鬼脇診療所,カムイウィスキー,福士水産㈱,糀谷商店,米田商店"</formula1>
+    </dataValidation>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C13 C18:C27 C32:C41 C46:C55 C60:C69" xr:uid="{D6841794-3992-4DAF-B98D-036AB13C1D97}">
+      <formula1>"鴛 泊,鬼 脇,沓 形,仙法志"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -28013,7 +28013,7 @@
       <c r="I4" s="25"/>
       <c r="J4" s="25"/>
       <c r="K4" s="25" t="str">
-        <f t="shared" ref="K4:K43" si="2">IF(E4="","",IF(E4="国保中央病院","医療","水産"))</f>
+        <f>IF(E4="","",IF(E4="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -28037,7 +28037,7 @@
       <c r="I5" s="25"/>
       <c r="J5" s="25"/>
       <c r="K5" s="25" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="K5:K43" si="2">IF(E5="","",IF(E5="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -29060,7 +29060,7 @@
       <c r="I48" s="25"/>
       <c r="J48" s="25"/>
       <c r="K48" s="25" t="str">
-        <f t="shared" ref="K48:K87" si="5">IF(E48="","",IF(E48="国保中央病院","医療","水産"))</f>
+        <f>IF(E48="","",IF(E48="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -29084,7 +29084,7 @@
       <c r="I49" s="25"/>
       <c r="J49" s="25"/>
       <c r="K49" s="25" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="K49:K87" si="5">IF(E49="","",IF(E49="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -29977,25 +29977,25 @@
       </c>
     </row>
     <row r="87" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="25">
+      <c r="A87" s="36">
         <v>80</v>
       </c>
-      <c r="B87" s="27"/>
-      <c r="C87" s="25"/>
-      <c r="D87" s="26"/>
+      <c r="B87" s="37"/>
+      <c r="C87" s="36"/>
+      <c r="D87" s="38"/>
       <c r="E87" s="39"/>
-      <c r="F87" s="29"/>
-      <c r="G87" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="H87" s="25" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="I87" s="25"/>
-      <c r="J87" s="25"/>
-      <c r="K87" s="25" t="str">
+      <c r="F87" s="40"/>
+      <c r="G87" s="40" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H87" s="36" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="I87" s="36"/>
+      <c r="J87" s="36"/>
+      <c r="K87" s="36" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -30022,19 +30022,19 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="5">
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="K4:K43 K48:K87" xr:uid="{A2D0BA34-FB05-4505-8C6A-0ABC29D901E2}">
-      <formula1>"医療,水産,木くず"</formula1>
-    </dataValidation>
-    <dataValidation type="whole" imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I48:J87 I4:J43" xr:uid="{56C01CDE-3FE3-490A-9166-D87EDFEC4E36}">
+    <dataValidation type="whole" imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I48:J87 I4:J43" xr:uid="{235D4EEF-25C4-4118-AD13-210A69121757}">
       <formula1>1</formula1>
       <formula2>99999</formula2>
     </dataValidation>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C48:C87 C4:C43" xr:uid="{C6F55B8D-B4BA-4E62-AB77-9232EEDD30F7}">
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C48:C87 C4:C43" xr:uid="{F5B7876B-D743-42F4-945C-0236CF9B2479}">
       <formula1>"鴛 泊,鬼 脇,沓 形,仙法志"</formula1>
     </dataValidation>
-    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:G43 B48:B87 F48:G87 B4:B43" xr:uid="{6D139645-7489-4D7A-AA37-FA5849B7A6EF}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="E4:E43 E48:E87" xr:uid="{8D027F36-2EB4-4275-8CAD-AF9EA1D73020}">
+    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:G43 B48:B87 F48:G87 B4:B43" xr:uid="{934639CD-3904-46DE-93DB-83AF315B4CDC}"/>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="E4:E43 E48:E87" xr:uid="{1AD18821-E45F-41C3-8DF1-58D986A904FB}">
       <formula1>"国保中央病院,道立鬼脇診療所,カムイウイスキー,福士水産㈱,糀谷商店,米田商店"</formula1>
+    </dataValidation>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="K4:K43 K48:K87" xr:uid="{7D9BBA35-2740-45D5-A65E-1905EE0EB3EF}">
+      <formula1>"医療,動植"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -30068,11 +30068,11 @@
       <c r="D1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="65" t="s">
+      <c r="E1" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
       <c r="J1" s="21"/>
       <c r="K1" s="22"/>
     </row>
@@ -30089,16 +30089,16 @@
       <c r="D2" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="59" t="s">
+      <c r="E2" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="61" t="s">
+      <c r="F2" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="62" t="s">
+      <c r="G2" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="63" t="s">
+      <c r="H2" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="55" t="s">
@@ -30107,7 +30107,7 @@
       <c r="J2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="64" t="s">
+      <c r="K2" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -30116,13 +30116,13 @@
       <c r="B3" s="56"/>
       <c r="C3" s="56"/>
       <c r="D3" s="58"/>
-      <c r="E3" s="60"/>
+      <c r="E3" s="63"/>
       <c r="F3" s="56"/>
       <c r="G3" s="58"/>
-      <c r="H3" s="60"/>
+      <c r="H3" s="63"/>
       <c r="I3" s="56"/>
       <c r="J3" s="56"/>
-      <c r="K3" s="64"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="7"/>
@@ -30307,11 +30307,11 @@
       <c r="D15" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="65" t="s">
+      <c r="E15" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="65"/>
-      <c r="G15" s="65"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="64"/>
       <c r="J15" s="21"/>
       <c r="K15" s="22"/>
     </row>
@@ -30328,16 +30328,16 @@
       <c r="D16" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="59" t="s">
+      <c r="E16" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="61" t="s">
+      <c r="F16" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="62" t="s">
+      <c r="G16" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="63" t="s">
+      <c r="H16" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I16" s="55" t="s">
@@ -30346,7 +30346,7 @@
       <c r="J16" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="64" t="s">
+      <c r="K16" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -30355,13 +30355,13 @@
       <c r="B17" s="56"/>
       <c r="C17" s="56"/>
       <c r="D17" s="58"/>
-      <c r="E17" s="60"/>
+      <c r="E17" s="63"/>
       <c r="F17" s="56"/>
       <c r="G17" s="58"/>
-      <c r="H17" s="60"/>
+      <c r="H17" s="63"/>
       <c r="I17" s="56"/>
       <c r="J17" s="56"/>
-      <c r="K17" s="64"/>
+      <c r="K17" s="60"/>
     </row>
     <row r="18" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7"/>
@@ -30546,11 +30546,11 @@
       <c r="D29" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="65" t="s">
+      <c r="E29" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="65"/>
-      <c r="G29" s="65"/>
+      <c r="F29" s="64"/>
+      <c r="G29" s="64"/>
       <c r="J29" s="21"/>
       <c r="K29" s="22"/>
     </row>
@@ -30567,16 +30567,16 @@
       <c r="D30" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E30" s="59" t="s">
+      <c r="E30" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F30" s="61" t="s">
+      <c r="F30" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G30" s="62" t="s">
+      <c r="G30" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="63" t="s">
+      <c r="H30" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I30" s="55" t="s">
@@ -30585,7 +30585,7 @@
       <c r="J30" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K30" s="64" t="s">
+      <c r="K30" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -30594,13 +30594,13 @@
       <c r="B31" s="56"/>
       <c r="C31" s="56"/>
       <c r="D31" s="58"/>
-      <c r="E31" s="60"/>
+      <c r="E31" s="63"/>
       <c r="F31" s="56"/>
       <c r="G31" s="58"/>
-      <c r="H31" s="60"/>
+      <c r="H31" s="63"/>
       <c r="I31" s="56"/>
       <c r="J31" s="56"/>
-      <c r="K31" s="64"/>
+      <c r="K31" s="60"/>
     </row>
     <row r="32" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7"/>
@@ -30785,11 +30785,11 @@
       <c r="D43" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="65" t="s">
+      <c r="E43" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="65"/>
-      <c r="G43" s="65"/>
+      <c r="F43" s="64"/>
+      <c r="G43" s="64"/>
       <c r="J43" s="21"/>
       <c r="K43" s="22"/>
     </row>
@@ -30806,16 +30806,16 @@
       <c r="D44" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="59" t="s">
+      <c r="E44" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="61" t="s">
+      <c r="F44" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G44" s="62" t="s">
+      <c r="G44" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H44" s="63" t="s">
+      <c r="H44" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I44" s="55" t="s">
@@ -30824,7 +30824,7 @@
       <c r="J44" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="64" t="s">
+      <c r="K44" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -30833,13 +30833,13 @@
       <c r="B45" s="56"/>
       <c r="C45" s="56"/>
       <c r="D45" s="58"/>
-      <c r="E45" s="60"/>
+      <c r="E45" s="63"/>
       <c r="F45" s="56"/>
       <c r="G45" s="58"/>
-      <c r="H45" s="60"/>
+      <c r="H45" s="63"/>
       <c r="I45" s="56"/>
       <c r="J45" s="56"/>
-      <c r="K45" s="64"/>
+      <c r="K45" s="60"/>
     </row>
     <row r="46" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7"/>
@@ -31024,11 +31024,11 @@
       <c r="D57" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E57" s="65" t="s">
+      <c r="E57" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="65"/>
-      <c r="G57" s="65"/>
+      <c r="F57" s="64"/>
+      <c r="G57" s="64"/>
       <c r="J57" s="21"/>
       <c r="K57" s="22"/>
     </row>
@@ -31045,16 +31045,16 @@
       <c r="D58" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="59" t="s">
+      <c r="E58" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F58" s="61" t="s">
+      <c r="F58" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G58" s="62" t="s">
+      <c r="G58" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H58" s="63" t="s">
+      <c r="H58" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I58" s="55" t="s">
@@ -31063,7 +31063,7 @@
       <c r="J58" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K58" s="64" t="s">
+      <c r="K58" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -31072,13 +31072,13 @@
       <c r="B59" s="56"/>
       <c r="C59" s="56"/>
       <c r="D59" s="58"/>
-      <c r="E59" s="60"/>
+      <c r="E59" s="63"/>
       <c r="F59" s="56"/>
       <c r="G59" s="58"/>
-      <c r="H59" s="60"/>
+      <c r="H59" s="63"/>
       <c r="I59" s="56"/>
       <c r="J59" s="56"/>
-      <c r="K59" s="64"/>
+      <c r="K59" s="60"/>
     </row>
     <row r="60" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="7"/>
@@ -31265,25 +31265,35 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="K44:K45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="K30:K31"/>
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="C30:C31"/>
@@ -31296,49 +31306,39 @@
     <mergeCell ref="E44:E45"/>
     <mergeCell ref="F44:F45"/>
     <mergeCell ref="G44:G45"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="K30:K31"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="6">
-    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E46:J55 E32:J41 E60:J69 E18:J27 A60:B69 A4:B13 A18:B27 A32:B41 A46:B55 E4:J13" xr:uid="{0A995B77-EB24-48C8-87DE-4A2729CD0DAF}"/>
-    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K13 K32:K41 K60:K69 K18:K27 C4:C6 K46:K55" xr:uid="{4C9BA8A7-FAF9-4ADA-AE66-7905A34A7140}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C32:C41 C60:C69 C7:C13 C18:C27 C46:C55" xr:uid="{D136A7AE-A994-44A9-909A-B6252DD74C22}">
-      <formula1>"鴛　泊,沓　形,鬼　脇,仙法志"</formula1>
-    </dataValidation>
-    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D1:D3 D15 D29 D43 D57" xr:uid="{361976FE-324E-45E6-A53F-0EC2DF05D0F6}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D56 D42 D16:D17 D30:D31 D14 D28 D44:D45 D58:D59 D70:D341" xr:uid="{CBDC3CAC-BC32-4207-A618-D5E53C2CA39B}">
+    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E46:J55 E32:J41 E60:J69 E18:J27 A60:B69 A4:B13 A18:B27 A32:B41 A46:B55 E4:J13" xr:uid="{77E60535-72B2-4047-A085-329A70EA65FA}"/>
+    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K13 K32:K41 K60:K69 K18:K27 K46:K55" xr:uid="{C1C6A836-CB4F-41F9-8F27-3350928A001B}"/>
+    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D1:D3 D15 D29 D43 D57" xr:uid="{A509D222-C45B-4C33-8B38-479EA2A1E149}"/>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D56 D42 D16:D17 D30:D31 D14 D28 D44:D45 D58:D59 D70:D341" xr:uid="{FD166A1F-A78B-4678-B988-47B66F64D77E}">
       <formula1>"国保中央病院,福士水産㈱,高橋水産㈱"</formula1>
     </dataValidation>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D4:D13 D18:D27 D32:D41 D46:D55 D60:D69" xr:uid="{2B5DFEF1-BE79-42EB-BAD0-A7A8209264D0}">
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D4:D13 D18:D27 D32:D41 D46:D55 D60:D69" xr:uid="{3E63D73C-2071-42D5-8133-072709ABF4AF}">
       <formula1>"国保中央病院,道立鬼脇診療所,カムイウィスキー,福士水産㈱,糀谷商店,米田商店"</formula1>
+    </dataValidation>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C13 C18:C27 C32:C41 C46:C55 C60:C69" xr:uid="{A4F4093E-D35E-4B24-BD26-CEBB34D187DC}">
+      <formula1>"鴛 泊,鬼 脇,沓 形,仙法志"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -31372,11 +31372,11 @@
       <c r="D1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="65" t="s">
+      <c r="E1" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
       <c r="J1" s="21"/>
       <c r="K1" s="22"/>
     </row>
@@ -31393,16 +31393,16 @@
       <c r="D2" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="59" t="s">
+      <c r="E2" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="61" t="s">
+      <c r="F2" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="62" t="s">
+      <c r="G2" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="63" t="s">
+      <c r="H2" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="55" t="s">
@@ -31411,7 +31411,7 @@
       <c r="J2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="64" t="s">
+      <c r="K2" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -31420,13 +31420,13 @@
       <c r="B3" s="56"/>
       <c r="C3" s="56"/>
       <c r="D3" s="58"/>
-      <c r="E3" s="60"/>
+      <c r="E3" s="63"/>
       <c r="F3" s="56"/>
       <c r="G3" s="58"/>
-      <c r="H3" s="60"/>
+      <c r="H3" s="63"/>
       <c r="I3" s="56"/>
       <c r="J3" s="56"/>
-      <c r="K3" s="64"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="7"/>
@@ -31611,11 +31611,11 @@
       <c r="D15" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="65" t="s">
+      <c r="E15" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="65"/>
-      <c r="G15" s="65"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="64"/>
       <c r="J15" s="21"/>
       <c r="K15" s="22"/>
     </row>
@@ -31632,16 +31632,16 @@
       <c r="D16" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="59" t="s">
+      <c r="E16" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="61" t="s">
+      <c r="F16" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="62" t="s">
+      <c r="G16" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="63" t="s">
+      <c r="H16" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I16" s="55" t="s">
@@ -31650,7 +31650,7 @@
       <c r="J16" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="64" t="s">
+      <c r="K16" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -31659,13 +31659,13 @@
       <c r="B17" s="56"/>
       <c r="C17" s="56"/>
       <c r="D17" s="58"/>
-      <c r="E17" s="60"/>
+      <c r="E17" s="63"/>
       <c r="F17" s="56"/>
       <c r="G17" s="58"/>
-      <c r="H17" s="60"/>
+      <c r="H17" s="63"/>
       <c r="I17" s="56"/>
       <c r="J17" s="56"/>
-      <c r="K17" s="64"/>
+      <c r="K17" s="60"/>
     </row>
     <row r="18" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7"/>
@@ -31850,11 +31850,11 @@
       <c r="D29" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="65" t="s">
+      <c r="E29" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="65"/>
-      <c r="G29" s="65"/>
+      <c r="F29" s="64"/>
+      <c r="G29" s="64"/>
       <c r="J29" s="21"/>
       <c r="K29" s="22"/>
     </row>
@@ -31871,16 +31871,16 @@
       <c r="D30" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E30" s="59" t="s">
+      <c r="E30" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F30" s="61" t="s">
+      <c r="F30" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G30" s="62" t="s">
+      <c r="G30" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="63" t="s">
+      <c r="H30" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I30" s="55" t="s">
@@ -31889,7 +31889,7 @@
       <c r="J30" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K30" s="64" t="s">
+      <c r="K30" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -31898,13 +31898,13 @@
       <c r="B31" s="56"/>
       <c r="C31" s="56"/>
       <c r="D31" s="58"/>
-      <c r="E31" s="60"/>
+      <c r="E31" s="63"/>
       <c r="F31" s="56"/>
       <c r="G31" s="58"/>
-      <c r="H31" s="60"/>
+      <c r="H31" s="63"/>
       <c r="I31" s="56"/>
       <c r="J31" s="56"/>
-      <c r="K31" s="64"/>
+      <c r="K31" s="60"/>
     </row>
     <row r="32" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7"/>
@@ -32089,11 +32089,11 @@
       <c r="D43" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="65" t="s">
+      <c r="E43" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="65"/>
-      <c r="G43" s="65"/>
+      <c r="F43" s="64"/>
+      <c r="G43" s="64"/>
       <c r="J43" s="21"/>
       <c r="K43" s="22"/>
     </row>
@@ -32110,16 +32110,16 @@
       <c r="D44" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="59" t="s">
+      <c r="E44" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="61" t="s">
+      <c r="F44" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G44" s="62" t="s">
+      <c r="G44" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H44" s="63" t="s">
+      <c r="H44" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I44" s="55" t="s">
@@ -32128,7 +32128,7 @@
       <c r="J44" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="64" t="s">
+      <c r="K44" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -32137,13 +32137,13 @@
       <c r="B45" s="56"/>
       <c r="C45" s="56"/>
       <c r="D45" s="58"/>
-      <c r="E45" s="60"/>
+      <c r="E45" s="63"/>
       <c r="F45" s="56"/>
       <c r="G45" s="58"/>
-      <c r="H45" s="60"/>
+      <c r="H45" s="63"/>
       <c r="I45" s="56"/>
       <c r="J45" s="56"/>
-      <c r="K45" s="64"/>
+      <c r="K45" s="60"/>
     </row>
     <row r="46" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7"/>
@@ -32328,11 +32328,11 @@
       <c r="D57" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E57" s="65" t="s">
+      <c r="E57" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="65"/>
-      <c r="G57" s="65"/>
+      <c r="F57" s="64"/>
+      <c r="G57" s="64"/>
       <c r="J57" s="21"/>
       <c r="K57" s="22"/>
     </row>
@@ -32349,16 +32349,16 @@
       <c r="D58" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="59" t="s">
+      <c r="E58" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F58" s="61" t="s">
+      <c r="F58" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G58" s="62" t="s">
+      <c r="G58" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H58" s="63" t="s">
+      <c r="H58" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I58" s="55" t="s">
@@ -32367,7 +32367,7 @@
       <c r="J58" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K58" s="64" t="s">
+      <c r="K58" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -32376,13 +32376,13 @@
       <c r="B59" s="56"/>
       <c r="C59" s="56"/>
       <c r="D59" s="58"/>
-      <c r="E59" s="60"/>
+      <c r="E59" s="63"/>
       <c r="F59" s="56"/>
       <c r="G59" s="58"/>
-      <c r="H59" s="60"/>
+      <c r="H59" s="63"/>
       <c r="I59" s="56"/>
       <c r="J59" s="56"/>
-      <c r="K59" s="64"/>
+      <c r="K59" s="60"/>
     </row>
     <row r="60" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="7"/>
@@ -32569,25 +32569,35 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="K44:K45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="K30:K31"/>
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="C30:C31"/>
@@ -32600,49 +32610,39 @@
     <mergeCell ref="E44:E45"/>
     <mergeCell ref="F44:F45"/>
     <mergeCell ref="G44:G45"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="K30:K31"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="6">
-    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E46:J55 E32:J41 E60:J69 E18:J27 A60:B69 A4:B13 A18:B27 A32:B41 A46:B55 E4:J13" xr:uid="{A4A96E8C-81EE-4BDE-BBC1-AA356F6A89D9}"/>
-    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K13 K32:K41 K60:K69 K18:K27 C4:C6 K46:K55" xr:uid="{0CE9A54F-65CB-4FE8-9BA4-17F7A9417B96}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C32:C41 C60:C69 C7:C13 C18:C27 C46:C55" xr:uid="{0E581C66-26FA-4CBE-87B7-E1D7CD8E01C5}">
-      <formula1>"鴛　泊,沓　形,鬼　脇,仙法志"</formula1>
-    </dataValidation>
-    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D1:D3 D15 D29 D43 D57" xr:uid="{7B2378AA-AC1F-40B4-9048-6F59E0A48386}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D56 D42 D16:D17 D30:D31 D14 D28 D44:D45 D58:D59 D70:D341" xr:uid="{147C8F58-87FD-47B3-A27E-D4F07DCE7279}">
+    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E46:J55 E32:J41 E60:J69 E18:J27 A60:B69 A4:B13 A18:B27 A32:B41 A46:B55 E4:J13" xr:uid="{02731A2E-2DBC-4709-AA6E-36CE97492D82}"/>
+    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K13 K32:K41 K60:K69 K18:K27 K46:K55" xr:uid="{B06A7517-D765-4826-A5DA-C47A31F7B792}"/>
+    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D1:D3 D15 D29 D43 D57" xr:uid="{B269088D-EC00-4EB9-A1E1-7EE6C3C8491E}"/>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D56 D42 D16:D17 D30:D31 D14 D28 D44:D45 D58:D59 D70:D341" xr:uid="{1A914D5D-0DC0-444B-B16E-B245A891EA0D}">
       <formula1>"国保中央病院,福士水産㈱,高橋水産㈱"</formula1>
     </dataValidation>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D4:D13 D18:D27 D32:D41 D46:D55 D60:D69" xr:uid="{148FF10A-6C6E-43CD-A5C5-10C41DB8E771}">
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D4:D13 D18:D27 D32:D41 D46:D55 D60:D69" xr:uid="{EF9EEE9A-11E8-494D-9778-ED3E146DA678}">
       <formula1>"国保中央病院,道立鬼脇診療所,カムイウィスキー,福士水産㈱,糀谷商店,米田商店"</formula1>
+    </dataValidation>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C13 C18:C27 C32:C41 C46:C55 C60:C69" xr:uid="{C8020FCB-60BD-41E0-9BF5-ACBB08169F84}">
+      <formula1>"鴛 泊,鬼 脇,沓 形,仙法志"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -32676,11 +32676,11 @@
       <c r="D1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="65" t="s">
+      <c r="E1" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
       <c r="J1" s="21"/>
       <c r="K1" s="22"/>
     </row>
@@ -32697,16 +32697,16 @@
       <c r="D2" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="59" t="s">
+      <c r="E2" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="61" t="s">
+      <c r="F2" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="62" t="s">
+      <c r="G2" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="63" t="s">
+      <c r="H2" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="55" t="s">
@@ -32715,7 +32715,7 @@
       <c r="J2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="64" t="s">
+      <c r="K2" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -32724,13 +32724,13 @@
       <c r="B3" s="56"/>
       <c r="C3" s="56"/>
       <c r="D3" s="58"/>
-      <c r="E3" s="60"/>
+      <c r="E3" s="63"/>
       <c r="F3" s="56"/>
       <c r="G3" s="58"/>
-      <c r="H3" s="60"/>
+      <c r="H3" s="63"/>
       <c r="I3" s="56"/>
       <c r="J3" s="56"/>
-      <c r="K3" s="64"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="7"/>
@@ -32915,11 +32915,11 @@
       <c r="D15" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="65" t="s">
+      <c r="E15" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="65"/>
-      <c r="G15" s="65"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="64"/>
       <c r="J15" s="21"/>
       <c r="K15" s="22"/>
     </row>
@@ -32936,16 +32936,16 @@
       <c r="D16" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="59" t="s">
+      <c r="E16" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="61" t="s">
+      <c r="F16" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="62" t="s">
+      <c r="G16" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="63" t="s">
+      <c r="H16" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I16" s="55" t="s">
@@ -32954,7 +32954,7 @@
       <c r="J16" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="64" t="s">
+      <c r="K16" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -32963,13 +32963,13 @@
       <c r="B17" s="56"/>
       <c r="C17" s="56"/>
       <c r="D17" s="58"/>
-      <c r="E17" s="60"/>
+      <c r="E17" s="63"/>
       <c r="F17" s="56"/>
       <c r="G17" s="58"/>
-      <c r="H17" s="60"/>
+      <c r="H17" s="63"/>
       <c r="I17" s="56"/>
       <c r="J17" s="56"/>
-      <c r="K17" s="64"/>
+      <c r="K17" s="60"/>
     </row>
     <row r="18" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7"/>
@@ -33154,11 +33154,11 @@
       <c r="D29" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="65" t="s">
+      <c r="E29" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="65"/>
-      <c r="G29" s="65"/>
+      <c r="F29" s="64"/>
+      <c r="G29" s="64"/>
       <c r="J29" s="21"/>
       <c r="K29" s="22"/>
     </row>
@@ -33175,16 +33175,16 @@
       <c r="D30" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E30" s="59" t="s">
+      <c r="E30" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F30" s="61" t="s">
+      <c r="F30" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G30" s="62" t="s">
+      <c r="G30" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="63" t="s">
+      <c r="H30" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I30" s="55" t="s">
@@ -33193,7 +33193,7 @@
       <c r="J30" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K30" s="64" t="s">
+      <c r="K30" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -33202,13 +33202,13 @@
       <c r="B31" s="56"/>
       <c r="C31" s="56"/>
       <c r="D31" s="58"/>
-      <c r="E31" s="60"/>
+      <c r="E31" s="63"/>
       <c r="F31" s="56"/>
       <c r="G31" s="58"/>
-      <c r="H31" s="60"/>
+      <c r="H31" s="63"/>
       <c r="I31" s="56"/>
       <c r="J31" s="56"/>
-      <c r="K31" s="64"/>
+      <c r="K31" s="60"/>
     </row>
     <row r="32" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7"/>
@@ -33393,11 +33393,11 @@
       <c r="D43" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="65" t="s">
+      <c r="E43" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="65"/>
-      <c r="G43" s="65"/>
+      <c r="F43" s="64"/>
+      <c r="G43" s="64"/>
       <c r="J43" s="21"/>
       <c r="K43" s="22"/>
     </row>
@@ -33414,16 +33414,16 @@
       <c r="D44" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="59" t="s">
+      <c r="E44" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="61" t="s">
+      <c r="F44" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G44" s="62" t="s">
+      <c r="G44" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H44" s="63" t="s">
+      <c r="H44" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I44" s="55" t="s">
@@ -33432,7 +33432,7 @@
       <c r="J44" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="64" t="s">
+      <c r="K44" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -33441,13 +33441,13 @@
       <c r="B45" s="56"/>
       <c r="C45" s="56"/>
       <c r="D45" s="58"/>
-      <c r="E45" s="60"/>
+      <c r="E45" s="63"/>
       <c r="F45" s="56"/>
       <c r="G45" s="58"/>
-      <c r="H45" s="60"/>
+      <c r="H45" s="63"/>
       <c r="I45" s="56"/>
       <c r="J45" s="56"/>
-      <c r="K45" s="64"/>
+      <c r="K45" s="60"/>
     </row>
     <row r="46" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7"/>
@@ -33632,11 +33632,11 @@
       <c r="D57" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E57" s="65" t="s">
+      <c r="E57" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="65"/>
-      <c r="G57" s="65"/>
+      <c r="F57" s="64"/>
+      <c r="G57" s="64"/>
       <c r="J57" s="21"/>
       <c r="K57" s="22"/>
     </row>
@@ -33653,16 +33653,16 @@
       <c r="D58" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="59" t="s">
+      <c r="E58" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F58" s="61" t="s">
+      <c r="F58" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G58" s="62" t="s">
+      <c r="G58" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H58" s="63" t="s">
+      <c r="H58" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I58" s="55" t="s">
@@ -33671,7 +33671,7 @@
       <c r="J58" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K58" s="64" t="s">
+      <c r="K58" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -33680,13 +33680,13 @@
       <c r="B59" s="56"/>
       <c r="C59" s="56"/>
       <c r="D59" s="58"/>
-      <c r="E59" s="60"/>
+      <c r="E59" s="63"/>
       <c r="F59" s="56"/>
       <c r="G59" s="58"/>
-      <c r="H59" s="60"/>
+      <c r="H59" s="63"/>
       <c r="I59" s="56"/>
       <c r="J59" s="56"/>
-      <c r="K59" s="64"/>
+      <c r="K59" s="60"/>
     </row>
     <row r="60" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="7"/>
@@ -33873,27 +33873,29 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
     <mergeCell ref="E57:G57"/>
     <mergeCell ref="J16:J17"/>
     <mergeCell ref="K16:K17"/>
@@ -33910,43 +33912,41 @@
     <mergeCell ref="H16:H17"/>
     <mergeCell ref="E43:G43"/>
     <mergeCell ref="G30:G31"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="K44:K45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B2:B3"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="6">
-    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E46:J55 E32:J41 E60:J69 E18:J27 A60:B69 A4:B13 A18:B27 A32:B41 A46:B55 E4:J13" xr:uid="{38EF1155-5475-42F1-BB50-AA57B06E91CF}"/>
-    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K13 K32:K41 K60:K69 K18:K27 C4:C6 K46:K55" xr:uid="{363045F1-4420-4DCD-A102-197AFA5972D3}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C32:C41 C60:C69 C7:C13 C18:C27 C46:C55" xr:uid="{16312BA0-BD0C-4127-8E35-2C295BEFF4AA}">
-      <formula1>"鴛　泊,沓　形,鬼　脇,仙法志"</formula1>
-    </dataValidation>
-    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D1:D3 D15 D29 D43 D57" xr:uid="{AA534B07-F830-484E-B27A-614B2A58DA99}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D56 D42 D16:D17 D30:D31 D14 D28 D44:D45 D58:D59 D70:D341" xr:uid="{F1F5D771-66DA-4686-9725-2B1D630E89AE}">
+    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E46:J55 E32:J41 E60:J69 E18:J27 A60:B69 A4:B13 A18:B27 A32:B41 A46:B55 E4:J13" xr:uid="{B58059FA-3D28-4C58-8EB7-09EA47D7A4A3}"/>
+    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K13 K32:K41 K60:K69 K18:K27 K46:K55" xr:uid="{165810CD-CDD6-4C37-87BE-68F6746AA219}"/>
+    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D1:D3 D15 D29 D43 D57" xr:uid="{78380FB5-E94F-4EAF-BBF4-B7C7417C2CD4}"/>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D56 D42 D16:D17 D30:D31 D14 D28 D44:D45 D58:D59 D70:D341" xr:uid="{6CE411A1-17A2-45C9-9CFF-E68D96BCD245}">
       <formula1>"国保中央病院,福士水産㈱,高橋水産㈱"</formula1>
     </dataValidation>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D4:D13 D18:D27 D32:D41 D46:D55 D60:D69" xr:uid="{75BA3A56-4CD2-415F-A720-22BD40D4AB35}">
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D4:D13 D18:D27 D32:D41 D46:D55 D60:D69" xr:uid="{2237DDE8-2181-4463-8DBC-CF1C9ED2BAE9}">
       <formula1>"国保中央病院,道立鬼脇診療所,カムイウィスキー,福士水産㈱,糀谷商店,米田商店"</formula1>
+    </dataValidation>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C13 C18:C27 C32:C41 C46:C55 C60:C69" xr:uid="{4597190A-75E0-455F-AB37-AF5D6E36FB57}">
+      <formula1>"鴛 泊,鬼 脇,沓 形,仙法志"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -33980,11 +33980,11 @@
       <c r="D1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="65" t="s">
+      <c r="E1" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
       <c r="J1" s="21"/>
       <c r="K1" s="22"/>
     </row>
@@ -34001,16 +34001,16 @@
       <c r="D2" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="59" t="s">
+      <c r="E2" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="61" t="s">
+      <c r="F2" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="62" t="s">
+      <c r="G2" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="63" t="s">
+      <c r="H2" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="55" t="s">
@@ -34019,7 +34019,7 @@
       <c r="J2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="64" t="s">
+      <c r="K2" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -34028,13 +34028,13 @@
       <c r="B3" s="56"/>
       <c r="C3" s="56"/>
       <c r="D3" s="58"/>
-      <c r="E3" s="60"/>
+      <c r="E3" s="63"/>
       <c r="F3" s="56"/>
       <c r="G3" s="58"/>
-      <c r="H3" s="60"/>
+      <c r="H3" s="63"/>
       <c r="I3" s="56"/>
       <c r="J3" s="56"/>
-      <c r="K3" s="64"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="7"/>
@@ -34219,11 +34219,11 @@
       <c r="D15" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="65" t="s">
+      <c r="E15" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="65"/>
-      <c r="G15" s="65"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="64"/>
       <c r="J15" s="21"/>
       <c r="K15" s="22"/>
     </row>
@@ -34240,16 +34240,16 @@
       <c r="D16" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="59" t="s">
+      <c r="E16" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="61" t="s">
+      <c r="F16" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="62" t="s">
+      <c r="G16" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="63" t="s">
+      <c r="H16" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I16" s="55" t="s">
@@ -34258,7 +34258,7 @@
       <c r="J16" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="64" t="s">
+      <c r="K16" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -34267,13 +34267,13 @@
       <c r="B17" s="56"/>
       <c r="C17" s="56"/>
       <c r="D17" s="58"/>
-      <c r="E17" s="60"/>
+      <c r="E17" s="63"/>
       <c r="F17" s="56"/>
       <c r="G17" s="58"/>
-      <c r="H17" s="60"/>
+      <c r="H17" s="63"/>
       <c r="I17" s="56"/>
       <c r="J17" s="56"/>
-      <c r="K17" s="64"/>
+      <c r="K17" s="60"/>
     </row>
     <row r="18" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7"/>
@@ -34458,11 +34458,11 @@
       <c r="D29" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="65" t="s">
+      <c r="E29" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="65"/>
-      <c r="G29" s="65"/>
+      <c r="F29" s="64"/>
+      <c r="G29" s="64"/>
       <c r="J29" s="21"/>
       <c r="K29" s="22"/>
     </row>
@@ -34479,16 +34479,16 @@
       <c r="D30" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E30" s="59" t="s">
+      <c r="E30" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F30" s="61" t="s">
+      <c r="F30" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G30" s="62" t="s">
+      <c r="G30" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="63" t="s">
+      <c r="H30" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I30" s="55" t="s">
@@ -34497,7 +34497,7 @@
       <c r="J30" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K30" s="64" t="s">
+      <c r="K30" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -34506,13 +34506,13 @@
       <c r="B31" s="56"/>
       <c r="C31" s="56"/>
       <c r="D31" s="58"/>
-      <c r="E31" s="60"/>
+      <c r="E31" s="63"/>
       <c r="F31" s="56"/>
       <c r="G31" s="58"/>
-      <c r="H31" s="60"/>
+      <c r="H31" s="63"/>
       <c r="I31" s="56"/>
       <c r="J31" s="56"/>
-      <c r="K31" s="64"/>
+      <c r="K31" s="60"/>
     </row>
     <row r="32" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7"/>
@@ -34697,11 +34697,11 @@
       <c r="D43" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="65" t="s">
+      <c r="E43" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="65"/>
-      <c r="G43" s="65"/>
+      <c r="F43" s="64"/>
+      <c r="G43" s="64"/>
       <c r="J43" s="21"/>
       <c r="K43" s="22"/>
     </row>
@@ -34718,16 +34718,16 @@
       <c r="D44" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="59" t="s">
+      <c r="E44" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="61" t="s">
+      <c r="F44" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G44" s="62" t="s">
+      <c r="G44" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H44" s="63" t="s">
+      <c r="H44" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I44" s="55" t="s">
@@ -34736,7 +34736,7 @@
       <c r="J44" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="64" t="s">
+      <c r="K44" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -34745,13 +34745,13 @@
       <c r="B45" s="56"/>
       <c r="C45" s="56"/>
       <c r="D45" s="58"/>
-      <c r="E45" s="60"/>
+      <c r="E45" s="63"/>
       <c r="F45" s="56"/>
       <c r="G45" s="58"/>
-      <c r="H45" s="60"/>
+      <c r="H45" s="63"/>
       <c r="I45" s="56"/>
       <c r="J45" s="56"/>
-      <c r="K45" s="64"/>
+      <c r="K45" s="60"/>
     </row>
     <row r="46" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7"/>
@@ -34936,11 +34936,11 @@
       <c r="D57" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E57" s="65" t="s">
+      <c r="E57" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="65"/>
-      <c r="G57" s="65"/>
+      <c r="F57" s="64"/>
+      <c r="G57" s="64"/>
       <c r="J57" s="21"/>
       <c r="K57" s="22"/>
     </row>
@@ -34957,16 +34957,16 @@
       <c r="D58" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="59" t="s">
+      <c r="E58" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F58" s="61" t="s">
+      <c r="F58" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G58" s="62" t="s">
+      <c r="G58" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H58" s="63" t="s">
+      <c r="H58" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I58" s="55" t="s">
@@ -34975,7 +34975,7 @@
       <c r="J58" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K58" s="64" t="s">
+      <c r="K58" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -34984,13 +34984,13 @@
       <c r="B59" s="56"/>
       <c r="C59" s="56"/>
       <c r="D59" s="58"/>
-      <c r="E59" s="60"/>
+      <c r="E59" s="63"/>
       <c r="F59" s="56"/>
       <c r="G59" s="58"/>
-      <c r="H59" s="60"/>
+      <c r="H59" s="63"/>
       <c r="I59" s="56"/>
       <c r="J59" s="56"/>
-      <c r="K59" s="64"/>
+      <c r="K59" s="60"/>
     </row>
     <row r="60" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="7"/>
@@ -35177,25 +35177,35 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="K44:K45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="K30:K31"/>
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="C30:C31"/>
@@ -35208,49 +35218,39 @@
     <mergeCell ref="E44:E45"/>
     <mergeCell ref="F44:F45"/>
     <mergeCell ref="G44:G45"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="K30:K31"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="6">
-    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E46:J55 E32:J41 E60:J69 E18:J27 A60:B69 A4:B13 A18:B27 A32:B41 A46:B55 E4:J13" xr:uid="{75C8C9D3-AEDC-4AB9-9A88-87DAEE2611E3}"/>
-    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K13 K32:K41 K60:K69 K18:K27 C4:C6 K46:K55" xr:uid="{845CC03B-FDA5-4E5A-9315-70798DFE962C}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C32:C41 C60:C69 C7:C13 C18:C27 C46:C55" xr:uid="{61541A9F-ACDF-469A-B346-7C80AB3445F7}">
-      <formula1>"鴛　泊,沓　形,鬼　脇,仙法志"</formula1>
-    </dataValidation>
-    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D1:D3 D15 D29 D43 D57" xr:uid="{4BFABC3F-4B0C-4D22-AF92-EA250AEEEF7A}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D56 D42 D16:D17 D30:D31 D14 D28 D44:D45 D58:D59 D70:D341" xr:uid="{E77C527A-12A1-4A40-8371-074A84F672DF}">
+    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E46:J55 E32:J41 E60:J69 E18:J27 A60:B69 A4:B13 A18:B27 A32:B41 A46:B55 E4:J13" xr:uid="{CF387215-1F9C-4204-AB6F-2B5920655653}"/>
+    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K13 K32:K41 K60:K69 K18:K27 K46:K55" xr:uid="{23C772E4-E8DB-4F91-A75F-2379A5259460}"/>
+    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D1:D3 D15 D29 D43 D57" xr:uid="{A0CCDA27-28BB-4D16-B590-17F41F21ECBF}"/>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D56 D42 D16:D17 D30:D31 D14 D28 D44:D45 D58:D59 D70:D341" xr:uid="{15C03151-9475-4F7F-9D19-DE4BE002D1FB}">
       <formula1>"国保中央病院,福士水産㈱,高橋水産㈱"</formula1>
     </dataValidation>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D4:D13 D18:D27 D32:D41 D46:D55 D60:D69" xr:uid="{8A5E0467-6E8E-44EB-8070-553C8FF6847D}">
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D4:D13 D18:D27 D32:D41 D46:D55 D60:D69" xr:uid="{29611AEE-1C8B-46BA-A223-2FC0C9B87E72}">
       <formula1>"国保中央病院,道立鬼脇診療所,カムイウィスキー,福士水産㈱,糀谷商店,米田商店"</formula1>
+    </dataValidation>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C13 C18:C27 C32:C41 C46:C55 C60:C69" xr:uid="{BC9121E2-4ECD-4606-983D-6B59613A86C5}">
+      <formula1>"鴛 泊,鬼 脇,沓 形,仙法志"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -35284,11 +35284,11 @@
       <c r="D1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="65" t="s">
+      <c r="E1" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
       <c r="J1" s="21"/>
       <c r="K1" s="22"/>
     </row>
@@ -35305,16 +35305,16 @@
       <c r="D2" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="59" t="s">
+      <c r="E2" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="61" t="s">
+      <c r="F2" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="62" t="s">
+      <c r="G2" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="63" t="s">
+      <c r="H2" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="55" t="s">
@@ -35323,7 +35323,7 @@
       <c r="J2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="64" t="s">
+      <c r="K2" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -35332,13 +35332,13 @@
       <c r="B3" s="56"/>
       <c r="C3" s="56"/>
       <c r="D3" s="58"/>
-      <c r="E3" s="60"/>
+      <c r="E3" s="63"/>
       <c r="F3" s="56"/>
       <c r="G3" s="58"/>
-      <c r="H3" s="60"/>
+      <c r="H3" s="63"/>
       <c r="I3" s="56"/>
       <c r="J3" s="56"/>
-      <c r="K3" s="64"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="7"/>
@@ -35523,11 +35523,11 @@
       <c r="D15" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="65" t="s">
+      <c r="E15" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="65"/>
-      <c r="G15" s="65"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="64"/>
       <c r="J15" s="21"/>
       <c r="K15" s="22"/>
     </row>
@@ -35544,16 +35544,16 @@
       <c r="D16" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="59" t="s">
+      <c r="E16" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="61" t="s">
+      <c r="F16" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="62" t="s">
+      <c r="G16" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="63" t="s">
+      <c r="H16" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I16" s="55" t="s">
@@ -35562,7 +35562,7 @@
       <c r="J16" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="64" t="s">
+      <c r="K16" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -35571,13 +35571,13 @@
       <c r="B17" s="56"/>
       <c r="C17" s="56"/>
       <c r="D17" s="58"/>
-      <c r="E17" s="60"/>
+      <c r="E17" s="63"/>
       <c r="F17" s="56"/>
       <c r="G17" s="58"/>
-      <c r="H17" s="60"/>
+      <c r="H17" s="63"/>
       <c r="I17" s="56"/>
       <c r="J17" s="56"/>
-      <c r="K17" s="64"/>
+      <c r="K17" s="60"/>
     </row>
     <row r="18" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7"/>
@@ -35762,11 +35762,11 @@
       <c r="D29" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="65" t="s">
+      <c r="E29" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="65"/>
-      <c r="G29" s="65"/>
+      <c r="F29" s="64"/>
+      <c r="G29" s="64"/>
       <c r="J29" s="21"/>
       <c r="K29" s="22"/>
     </row>
@@ -35783,16 +35783,16 @@
       <c r="D30" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E30" s="59" t="s">
+      <c r="E30" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F30" s="61" t="s">
+      <c r="F30" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G30" s="62" t="s">
+      <c r="G30" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="63" t="s">
+      <c r="H30" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I30" s="55" t="s">
@@ -35801,7 +35801,7 @@
       <c r="J30" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K30" s="64" t="s">
+      <c r="K30" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -35810,13 +35810,13 @@
       <c r="B31" s="56"/>
       <c r="C31" s="56"/>
       <c r="D31" s="58"/>
-      <c r="E31" s="60"/>
+      <c r="E31" s="63"/>
       <c r="F31" s="56"/>
       <c r="G31" s="58"/>
-      <c r="H31" s="60"/>
+      <c r="H31" s="63"/>
       <c r="I31" s="56"/>
       <c r="J31" s="56"/>
-      <c r="K31" s="64"/>
+      <c r="K31" s="60"/>
     </row>
     <row r="32" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7"/>
@@ -36001,11 +36001,11 @@
       <c r="D43" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="65" t="s">
+      <c r="E43" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="65"/>
-      <c r="G43" s="65"/>
+      <c r="F43" s="64"/>
+      <c r="G43" s="64"/>
       <c r="J43" s="21"/>
       <c r="K43" s="22"/>
     </row>
@@ -36022,16 +36022,16 @@
       <c r="D44" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="59" t="s">
+      <c r="E44" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="61" t="s">
+      <c r="F44" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G44" s="62" t="s">
+      <c r="G44" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H44" s="63" t="s">
+      <c r="H44" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I44" s="55" t="s">
@@ -36040,7 +36040,7 @@
       <c r="J44" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="64" t="s">
+      <c r="K44" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -36049,13 +36049,13 @@
       <c r="B45" s="56"/>
       <c r="C45" s="56"/>
       <c r="D45" s="58"/>
-      <c r="E45" s="60"/>
+      <c r="E45" s="63"/>
       <c r="F45" s="56"/>
       <c r="G45" s="58"/>
-      <c r="H45" s="60"/>
+      <c r="H45" s="63"/>
       <c r="I45" s="56"/>
       <c r="J45" s="56"/>
-      <c r="K45" s="64"/>
+      <c r="K45" s="60"/>
     </row>
     <row r="46" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7"/>
@@ -36240,11 +36240,11 @@
       <c r="D57" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E57" s="65" t="s">
+      <c r="E57" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="65"/>
-      <c r="G57" s="65"/>
+      <c r="F57" s="64"/>
+      <c r="G57" s="64"/>
       <c r="J57" s="21"/>
       <c r="K57" s="22"/>
     </row>
@@ -36261,16 +36261,16 @@
       <c r="D58" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="59" t="s">
+      <c r="E58" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F58" s="61" t="s">
+      <c r="F58" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G58" s="62" t="s">
+      <c r="G58" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H58" s="63" t="s">
+      <c r="H58" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I58" s="55" t="s">
@@ -36279,7 +36279,7 @@
       <c r="J58" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K58" s="64" t="s">
+      <c r="K58" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -36288,13 +36288,13 @@
       <c r="B59" s="56"/>
       <c r="C59" s="56"/>
       <c r="D59" s="58"/>
-      <c r="E59" s="60"/>
+      <c r="E59" s="63"/>
       <c r="F59" s="56"/>
       <c r="G59" s="58"/>
-      <c r="H59" s="60"/>
+      <c r="H59" s="63"/>
       <c r="I59" s="56"/>
       <c r="J59" s="56"/>
-      <c r="K59" s="64"/>
+      <c r="K59" s="60"/>
     </row>
     <row r="60" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="7"/>
@@ -36481,25 +36481,35 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="K44:K45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="K30:K31"/>
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="C30:C31"/>
@@ -36512,49 +36522,39 @@
     <mergeCell ref="E44:E45"/>
     <mergeCell ref="F44:F45"/>
     <mergeCell ref="G44:G45"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="K30:K31"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="6">
-    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E46:J55 E32:J41 E60:J69 E18:J27 A60:B69 A4:B13 A18:B27 A32:B41 A46:B55 E4:J13" xr:uid="{04EE2E1D-645B-476E-9D5C-46E6173E6E53}"/>
-    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K13 K32:K41 K60:K69 K18:K27 C4:C6 K46:K55" xr:uid="{56A82339-1C09-4B41-8292-54295DD2D44D}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C32:C41 C60:C69 C7:C13 C18:C27 C46:C55" xr:uid="{CBC6E513-9F7D-4B54-8255-28DD38B635B9}">
-      <formula1>"鴛　泊,沓　形,鬼　脇,仙法志"</formula1>
-    </dataValidation>
-    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D1:D3 D15 D29 D43 D57" xr:uid="{A38A5013-0C65-4D7C-A00A-CAFFC9066C87}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D56 D42 D16:D17 D30:D31 D14 D28 D44:D45 D58:D59 D70:D341" xr:uid="{3E846AF1-EEBA-4775-BCD5-719A48654DB6}">
+    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E46:J55 E32:J41 E60:J69 E18:J27 A60:B69 A4:B13 A18:B27 A32:B41 A46:B55 E4:J13" xr:uid="{3AEF5F35-5FB7-4DE1-BC27-0C6C309E62D1}"/>
+    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K13 K32:K41 K60:K69 K18:K27 K46:K55" xr:uid="{C29C5C21-B928-47A6-A021-2918EAD26F92}"/>
+    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D1:D3 D15 D29 D43 D57" xr:uid="{265A7AAB-F199-4A82-9B36-87D5992F6C81}"/>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D56 D42 D16:D17 D30:D31 D14 D28 D44:D45 D58:D59 D70:D341" xr:uid="{1C2DD182-C76C-4812-B0B0-BC15A26A2459}">
       <formula1>"国保中央病院,福士水産㈱,高橋水産㈱"</formula1>
     </dataValidation>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D4:D13 D18:D27 D32:D41 D46:D55 D60:D69" xr:uid="{124EA742-238A-451F-BF04-7D16116C055D}">
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D4:D13 D18:D27 D32:D41 D46:D55 D60:D69" xr:uid="{7040BC20-B94D-40B6-A4E6-516E39DEFFD4}">
       <formula1>"国保中央病院,道立鬼脇診療所,カムイウィスキー,福士水産㈱,糀谷商店,米田商店"</formula1>
+    </dataValidation>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C13 C18:C27 C32:C41 C46:C55 C60:C69" xr:uid="{0D59685A-58E8-4749-836E-61E6CB35994C}">
+      <formula1>"鴛 泊,鬼 脇,沓 形,仙法志"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -36588,11 +36588,11 @@
       <c r="D1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="65" t="s">
+      <c r="E1" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
       <c r="J1" s="21"/>
       <c r="K1" s="22"/>
     </row>
@@ -36609,16 +36609,16 @@
       <c r="D2" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="59" t="s">
+      <c r="E2" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="61" t="s">
+      <c r="F2" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="62" t="s">
+      <c r="G2" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="63" t="s">
+      <c r="H2" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="55" t="s">
@@ -36627,7 +36627,7 @@
       <c r="J2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="64" t="s">
+      <c r="K2" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -36636,13 +36636,13 @@
       <c r="B3" s="56"/>
       <c r="C3" s="56"/>
       <c r="D3" s="58"/>
-      <c r="E3" s="60"/>
+      <c r="E3" s="63"/>
       <c r="F3" s="56"/>
       <c r="G3" s="58"/>
-      <c r="H3" s="60"/>
+      <c r="H3" s="63"/>
       <c r="I3" s="56"/>
       <c r="J3" s="56"/>
-      <c r="K3" s="64"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="7"/>
@@ -36827,11 +36827,11 @@
       <c r="D15" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="65" t="s">
+      <c r="E15" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="65"/>
-      <c r="G15" s="65"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="64"/>
       <c r="J15" s="21"/>
       <c r="K15" s="22"/>
     </row>
@@ -36848,16 +36848,16 @@
       <c r="D16" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="59" t="s">
+      <c r="E16" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="61" t="s">
+      <c r="F16" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="62" t="s">
+      <c r="G16" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="63" t="s">
+      <c r="H16" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I16" s="55" t="s">
@@ -36866,7 +36866,7 @@
       <c r="J16" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="64" t="s">
+      <c r="K16" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -36875,13 +36875,13 @@
       <c r="B17" s="56"/>
       <c r="C17" s="56"/>
       <c r="D17" s="58"/>
-      <c r="E17" s="60"/>
+      <c r="E17" s="63"/>
       <c r="F17" s="56"/>
       <c r="G17" s="58"/>
-      <c r="H17" s="60"/>
+      <c r="H17" s="63"/>
       <c r="I17" s="56"/>
       <c r="J17" s="56"/>
-      <c r="K17" s="64"/>
+      <c r="K17" s="60"/>
     </row>
     <row r="18" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7"/>
@@ -37066,11 +37066,11 @@
       <c r="D29" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="65" t="s">
+      <c r="E29" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="65"/>
-      <c r="G29" s="65"/>
+      <c r="F29" s="64"/>
+      <c r="G29" s="64"/>
       <c r="J29" s="21"/>
       <c r="K29" s="22"/>
     </row>
@@ -37087,16 +37087,16 @@
       <c r="D30" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E30" s="59" t="s">
+      <c r="E30" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F30" s="61" t="s">
+      <c r="F30" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G30" s="62" t="s">
+      <c r="G30" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="63" t="s">
+      <c r="H30" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I30" s="55" t="s">
@@ -37105,7 +37105,7 @@
       <c r="J30" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K30" s="64" t="s">
+      <c r="K30" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -37114,13 +37114,13 @@
       <c r="B31" s="56"/>
       <c r="C31" s="56"/>
       <c r="D31" s="58"/>
-      <c r="E31" s="60"/>
+      <c r="E31" s="63"/>
       <c r="F31" s="56"/>
       <c r="G31" s="58"/>
-      <c r="H31" s="60"/>
+      <c r="H31" s="63"/>
       <c r="I31" s="56"/>
       <c r="J31" s="56"/>
-      <c r="K31" s="64"/>
+      <c r="K31" s="60"/>
     </row>
     <row r="32" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7"/>
@@ -37305,11 +37305,11 @@
       <c r="D43" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="65" t="s">
+      <c r="E43" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="65"/>
-      <c r="G43" s="65"/>
+      <c r="F43" s="64"/>
+      <c r="G43" s="64"/>
       <c r="J43" s="21"/>
       <c r="K43" s="22"/>
     </row>
@@ -37326,16 +37326,16 @@
       <c r="D44" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="59" t="s">
+      <c r="E44" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="61" t="s">
+      <c r="F44" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G44" s="62" t="s">
+      <c r="G44" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H44" s="63" t="s">
+      <c r="H44" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I44" s="55" t="s">
@@ -37344,7 +37344,7 @@
       <c r="J44" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="64" t="s">
+      <c r="K44" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -37353,13 +37353,13 @@
       <c r="B45" s="56"/>
       <c r="C45" s="56"/>
       <c r="D45" s="58"/>
-      <c r="E45" s="60"/>
+      <c r="E45" s="63"/>
       <c r="F45" s="56"/>
       <c r="G45" s="58"/>
-      <c r="H45" s="60"/>
+      <c r="H45" s="63"/>
       <c r="I45" s="56"/>
       <c r="J45" s="56"/>
-      <c r="K45" s="64"/>
+      <c r="K45" s="60"/>
     </row>
     <row r="46" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7"/>
@@ -37544,11 +37544,11 @@
       <c r="D57" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E57" s="65" t="s">
+      <c r="E57" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="65"/>
-      <c r="G57" s="65"/>
+      <c r="F57" s="64"/>
+      <c r="G57" s="64"/>
       <c r="J57" s="21"/>
       <c r="K57" s="22"/>
     </row>
@@ -37565,16 +37565,16 @@
       <c r="D58" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="59" t="s">
+      <c r="E58" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="F58" s="61" t="s">
+      <c r="F58" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="G58" s="62" t="s">
+      <c r="G58" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="H58" s="63" t="s">
+      <c r="H58" s="62" t="s">
         <v>4</v>
       </c>
       <c r="I58" s="55" t="s">
@@ -37583,7 +37583,7 @@
       <c r="J58" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K58" s="64" t="s">
+      <c r="K58" s="60" t="s">
         <v>7</v>
       </c>
     </row>
@@ -37592,13 +37592,13 @@
       <c r="B59" s="56"/>
       <c r="C59" s="56"/>
       <c r="D59" s="58"/>
-      <c r="E59" s="60"/>
+      <c r="E59" s="63"/>
       <c r="F59" s="56"/>
       <c r="G59" s="58"/>
-      <c r="H59" s="60"/>
+      <c r="H59" s="63"/>
       <c r="I59" s="56"/>
       <c r="J59" s="56"/>
-      <c r="K59" s="64"/>
+      <c r="K59" s="60"/>
     </row>
     <row r="60" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="7"/>
@@ -37785,25 +37785,35 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="K44:K45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="K30:K31"/>
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="C30:C31"/>
@@ -37816,49 +37826,39 @@
     <mergeCell ref="E44:E45"/>
     <mergeCell ref="F44:F45"/>
     <mergeCell ref="G44:G45"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="K30:K31"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="6">
-    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E46:J55 E32:J41 E60:J69 E18:J27 A60:B69 A4:B13 A18:B27 A32:B41 A46:B55 E4:J13" xr:uid="{A867E47F-422C-483D-864E-CF9164D1D7CA}"/>
-    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K13 K32:K41 K60:K69 K18:K27 C4:C6 K46:K55" xr:uid="{02EDCD5E-49F6-48E3-A99B-84986F1274EC}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C32:C41 C60:C69 C7:C13 C18:C27 C46:C55" xr:uid="{D222580B-82E9-4970-B22B-6CF26FAC7DBE}">
-      <formula1>"鴛　泊,沓　形,鬼　脇,仙法志"</formula1>
-    </dataValidation>
-    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D1:D3 D15 D29 D43 D57" xr:uid="{F4282099-1A4D-4D8E-99F6-AA848F493E9C}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D56 D42 D16:D17 D30:D31 D14 D28 D44:D45 D58:D59 D70:D341" xr:uid="{364133CA-A105-4E81-A0B2-0DF5E5D1906F}">
+    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E46:J55 E32:J41 E60:J69 E18:J27 A60:B69 A4:B13 A18:B27 A32:B41 A46:B55 E4:J13" xr:uid="{B5B90D8E-A511-49A0-923D-F19C0EB7FB7E}"/>
+    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K13 K32:K41 K60:K69 K18:K27 K46:K55" xr:uid="{13E5B91E-0426-43AF-BF1C-93C2F13763C5}"/>
+    <dataValidation imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D1:D3 D15 D29 D43 D57" xr:uid="{378C3A49-8E23-4683-A913-C769ED0E35F3}"/>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D56 D42 D16:D17 D30:D31 D14 D28 D44:D45 D58:D59 D70:D341" xr:uid="{2B2213C6-3C9B-4E0C-9D9B-061D0035B0DA}">
       <formula1>"国保中央病院,福士水産㈱,高橋水産㈱"</formula1>
     </dataValidation>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D4:D13 D18:D27 D32:D41 D46:D55 D60:D69" xr:uid="{8ABD91F0-EA65-42EE-A569-9EAAE0B7B6F2}">
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" prompt="なければ直接入力" sqref="D4:D13 D18:D27 D32:D41 D46:D55 D60:D69" xr:uid="{BBBB9645-06D9-430C-A3F9-629B1D703B41}">
       <formula1>"国保中央病院,道立鬼脇診療所,カムイウィスキー,福士水産㈱,糀谷商店,米田商店"</formula1>
+    </dataValidation>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C13 C18:C27 C32:C41 C46:C55 C60:C69" xr:uid="{F6A5A250-B77E-4952-A354-2AE32DDFEE85}">
+      <formula1>"鴛 泊,鬼 脇,沓 形,仙法志"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -37969,7 +37969,7 @@
       <c r="I4" s="25"/>
       <c r="J4" s="25"/>
       <c r="K4" s="25" t="str">
-        <f t="shared" ref="K4:K43" si="2">IF(E4="","",IF(E4="国保中央病院","医療","水産"))</f>
+        <f>IF(E4="","",IF(E4="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -37993,7 +37993,7 @@
       <c r="I5" s="25"/>
       <c r="J5" s="25"/>
       <c r="K5" s="25" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="K5:K43" si="2">IF(E5="","",IF(E5="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -39016,7 +39016,7 @@
       <c r="I48" s="25"/>
       <c r="J48" s="25"/>
       <c r="K48" s="25" t="str">
-        <f t="shared" ref="K48:K87" si="5">IF(E48="","",IF(E48="国保中央病院","医療","水産"))</f>
+        <f>IF(E48="","",IF(E48="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -39040,7 +39040,7 @@
       <c r="I49" s="25"/>
       <c r="J49" s="25"/>
       <c r="K49" s="25" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="K49:K87" si="5">IF(E49="","",IF(E49="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -39933,25 +39933,25 @@
       </c>
     </row>
     <row r="87" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="25">
+      <c r="A87" s="36">
         <v>80</v>
       </c>
-      <c r="B87" s="27"/>
-      <c r="C87" s="25"/>
-      <c r="D87" s="26"/>
+      <c r="B87" s="37"/>
+      <c r="C87" s="36"/>
+      <c r="D87" s="38"/>
       <c r="E87" s="39"/>
-      <c r="F87" s="29"/>
-      <c r="G87" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="H87" s="25" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="I87" s="25"/>
-      <c r="J87" s="25"/>
-      <c r="K87" s="25" t="str">
+      <c r="F87" s="40"/>
+      <c r="G87" s="40" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H87" s="36" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="I87" s="36"/>
+      <c r="J87" s="36"/>
+      <c r="K87" s="36" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -39978,19 +39978,19 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="5">
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="K4:K43 K48:K87" xr:uid="{EA61A0F1-085D-47EF-A82A-7AA27A98FAA5}">
-      <formula1>"医療,水産,木くず"</formula1>
-    </dataValidation>
-    <dataValidation type="whole" imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I48:J87 I4:J43" xr:uid="{B95F4CD1-1AB2-46D7-8C77-B1C511ED2FD7}">
+    <dataValidation type="whole" imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I48:J87 I4:J43" xr:uid="{662EFCA3-FFC3-42CE-85D5-0EDA6DFDDA67}">
       <formula1>1</formula1>
       <formula2>99999</formula2>
     </dataValidation>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C48:C87 C4:C43" xr:uid="{88B00511-9BF4-437A-91DB-93188B8A3C9A}">
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C48:C87 C4:C43" xr:uid="{7EB615E0-6CDE-42A5-A5E7-B39D7A26025A}">
       <formula1>"鴛 泊,鬼 脇,沓 形,仙法志"</formula1>
     </dataValidation>
-    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:G43 B48:B87 F48:G87 B4:B43" xr:uid="{25E0F34E-9018-4EAB-909D-D0DA16981A43}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="E4:E43 E48:E87" xr:uid="{D75CF854-DADD-466C-A10D-44200CC28D52}">
+    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:G43 B48:B87 F48:G87 B4:B43" xr:uid="{0B148530-16E0-4D17-8F1D-C3A3FBFCBD93}"/>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="E4:E43 E48:E87" xr:uid="{4FDF9B8C-750F-4466-97E3-443E3F3BBA29}">
       <formula1>"国保中央病院,道立鬼脇診療所,カムイウイスキー,福士水産㈱,糀谷商店,米田商店"</formula1>
+    </dataValidation>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="K4:K43 K48:K87" xr:uid="{97A03E5D-5177-404F-8AFD-095525A29F7A}">
+      <formula1>"医療,動植"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -40101,7 +40101,7 @@
       <c r="I4" s="25"/>
       <c r="J4" s="25"/>
       <c r="K4" s="25" t="str">
-        <f t="shared" ref="K4:K43" si="2">IF(E4="","",IF(E4="国保中央病院","医療","水産"))</f>
+        <f>IF(E4="","",IF(E4="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -40125,7 +40125,7 @@
       <c r="I5" s="25"/>
       <c r="J5" s="25"/>
       <c r="K5" s="25" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="K5:K43" si="2">IF(E5="","",IF(E5="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -41148,7 +41148,7 @@
       <c r="I48" s="25"/>
       <c r="J48" s="25"/>
       <c r="K48" s="25" t="str">
-        <f t="shared" ref="K48:K87" si="5">IF(E48="","",IF(E48="国保中央病院","医療","水産"))</f>
+        <f>IF(E48="","",IF(E48="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -41172,7 +41172,7 @@
       <c r="I49" s="25"/>
       <c r="J49" s="25"/>
       <c r="K49" s="25" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="K49:K87" si="5">IF(E49="","",IF(E49="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -42065,25 +42065,25 @@
       </c>
     </row>
     <row r="87" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="25">
+      <c r="A87" s="36">
         <v>80</v>
       </c>
-      <c r="B87" s="27"/>
-      <c r="C87" s="25"/>
-      <c r="D87" s="26"/>
+      <c r="B87" s="37"/>
+      <c r="C87" s="36"/>
+      <c r="D87" s="38"/>
       <c r="E87" s="39"/>
-      <c r="F87" s="29"/>
-      <c r="G87" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="H87" s="25" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="I87" s="25"/>
-      <c r="J87" s="25"/>
-      <c r="K87" s="25" t="str">
+      <c r="F87" s="40"/>
+      <c r="G87" s="40" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H87" s="36" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="I87" s="36"/>
+      <c r="J87" s="36"/>
+      <c r="K87" s="36" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -42110,19 +42110,19 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="5">
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="K4:K43 K48:K87" xr:uid="{F36A120A-7605-4C59-9EAF-0DF672C8CEE8}">
-      <formula1>"医療,水産,木くず"</formula1>
-    </dataValidation>
-    <dataValidation type="whole" imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I48:J87 I4:J43" xr:uid="{FB119C51-9FA6-4FB4-85A9-C79CEA593CEC}">
+    <dataValidation type="whole" imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I48:J87 I4:J43" xr:uid="{2586E063-18AE-4CCA-B2E0-FFCB808C04D1}">
       <formula1>1</formula1>
       <formula2>99999</formula2>
     </dataValidation>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C48:C87 C4:C43" xr:uid="{48F22EB4-C186-465F-862F-9A23BA45D5A1}">
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C48:C87 C4:C43" xr:uid="{C7E88798-C4D2-479D-B617-FE70E1800E45}">
       <formula1>"鴛 泊,鬼 脇,沓 形,仙法志"</formula1>
     </dataValidation>
-    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:G43 B48:B87 F48:G87 B4:B43" xr:uid="{84548199-B4DA-4792-A5F9-201AEB4B223F}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="E4:E43 E48:E87" xr:uid="{53557BDF-A319-4364-9F23-6D48EF3E36AA}">
+    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:G43 B48:B87 F48:G87 B4:B43" xr:uid="{2E8CFAB2-A346-46FA-97D2-9FFF6B3ABDE5}"/>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="E4:E43 E48:E87" xr:uid="{D4481EB9-11D7-4150-898C-47D50ADF7D48}">
       <formula1>"国保中央病院,道立鬼脇診療所,カムイウイスキー,福士水産㈱,糀谷商店,米田商店"</formula1>
+    </dataValidation>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="K4:K43 K48:K87" xr:uid="{51164718-64B9-4E70-9609-714978DDE872}">
+      <formula1>"医療,動植"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -42233,7 +42233,7 @@
       <c r="I4" s="25"/>
       <c r="J4" s="25"/>
       <c r="K4" s="25" t="str">
-        <f t="shared" ref="K4:K43" si="2">IF(E4="","",IF(E4="国保中央病院","医療","水産"))</f>
+        <f>IF(E4="","",IF(E4="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -42257,7 +42257,7 @@
       <c r="I5" s="25"/>
       <c r="J5" s="25"/>
       <c r="K5" s="25" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="K5:K43" si="2">IF(E5="","",IF(E5="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -43280,7 +43280,7 @@
       <c r="I48" s="25"/>
       <c r="J48" s="25"/>
       <c r="K48" s="25" t="str">
-        <f t="shared" ref="K48:K87" si="5">IF(E48="","",IF(E48="国保中央病院","医療","水産"))</f>
+        <f>IF(E48="","",IF(E48="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -43304,7 +43304,7 @@
       <c r="I49" s="25"/>
       <c r="J49" s="25"/>
       <c r="K49" s="25" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="K49:K87" si="5">IF(E49="","",IF(E49="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -44197,25 +44197,25 @@
       </c>
     </row>
     <row r="87" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="25">
+      <c r="A87" s="36">
         <v>80</v>
       </c>
-      <c r="B87" s="27"/>
-      <c r="C87" s="25"/>
-      <c r="D87" s="26"/>
+      <c r="B87" s="37"/>
+      <c r="C87" s="36"/>
+      <c r="D87" s="38"/>
       <c r="E87" s="39"/>
-      <c r="F87" s="29"/>
-      <c r="G87" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="H87" s="25" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="I87" s="25"/>
-      <c r="J87" s="25"/>
-      <c r="K87" s="25" t="str">
+      <c r="F87" s="40"/>
+      <c r="G87" s="40" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H87" s="36" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="I87" s="36"/>
+      <c r="J87" s="36"/>
+      <c r="K87" s="36" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -44242,19 +44242,19 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="5">
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="K4:K43 K48:K87" xr:uid="{0B87807C-1D91-4386-A238-F52101974002}">
-      <formula1>"医療,水産,木くず"</formula1>
-    </dataValidation>
-    <dataValidation type="whole" imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I48:J87 I4:J43" xr:uid="{73B54449-025E-4624-830E-90A1762F28AF}">
+    <dataValidation type="whole" imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I48:J87 I4:J43" xr:uid="{23634BA4-ED4E-4A68-A36E-FE649D6243E7}">
       <formula1>1</formula1>
       <formula2>99999</formula2>
     </dataValidation>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C48:C87 C4:C43" xr:uid="{13EE5120-726E-4A40-8002-23CF0E678BE7}">
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C48:C87 C4:C43" xr:uid="{3AB898DE-EDEF-4888-AE99-850EAB3DD6D6}">
       <formula1>"鴛 泊,鬼 脇,沓 形,仙法志"</formula1>
     </dataValidation>
-    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:G43 B48:B87 F48:G87 B4:B43" xr:uid="{AE66EF92-BC0B-4D88-B333-0A6921BBD4FA}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="E4:E43 E48:E87" xr:uid="{E5BEE3FD-2912-402F-8FFE-F611407D4679}">
+    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:G43 B48:B87 F48:G87 B4:B43" xr:uid="{FAD49A7A-3487-43BC-8E8F-60B2D474EF6D}"/>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="E4:E43 E48:E87" xr:uid="{C12E670C-0D90-4A0C-B7FA-8204CF9B691E}">
       <formula1>"国保中央病院,道立鬼脇診療所,カムイウイスキー,福士水産㈱,糀谷商店,米田商店"</formula1>
+    </dataValidation>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="K4:K43 K48:K87" xr:uid="{8FF10005-7434-4FC4-B4C2-47C96A160782}">
+      <formula1>"医療,動植"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -44365,7 +44365,7 @@
       <c r="I4" s="25"/>
       <c r="J4" s="25"/>
       <c r="K4" s="25" t="str">
-        <f t="shared" ref="K4:K43" si="2">IF(E4="","",IF(E4="国保中央病院","医療","水産"))</f>
+        <f>IF(E4="","",IF(E4="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -44389,7 +44389,7 @@
       <c r="I5" s="25"/>
       <c r="J5" s="25"/>
       <c r="K5" s="25" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="K5:K43" si="2">IF(E5="","",IF(E5="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -45412,7 +45412,7 @@
       <c r="I48" s="25"/>
       <c r="J48" s="25"/>
       <c r="K48" s="25" t="str">
-        <f t="shared" ref="K48:K87" si="5">IF(E48="","",IF(E48="国保中央病院","医療","水産"))</f>
+        <f>IF(E48="","",IF(E48="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -45436,7 +45436,7 @@
       <c r="I49" s="25"/>
       <c r="J49" s="25"/>
       <c r="K49" s="25" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="K49:K87" si="5">IF(E49="","",IF(E49="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -46329,25 +46329,25 @@
       </c>
     </row>
     <row r="87" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="25">
+      <c r="A87" s="36">
         <v>80</v>
       </c>
-      <c r="B87" s="27"/>
-      <c r="C87" s="25"/>
-      <c r="D87" s="26"/>
+      <c r="B87" s="37"/>
+      <c r="C87" s="36"/>
+      <c r="D87" s="38"/>
       <c r="E87" s="39"/>
-      <c r="F87" s="29"/>
-      <c r="G87" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="H87" s="25" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="I87" s="25"/>
-      <c r="J87" s="25"/>
-      <c r="K87" s="25" t="str">
+      <c r="F87" s="40"/>
+      <c r="G87" s="40" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H87" s="36" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="I87" s="36"/>
+      <c r="J87" s="36"/>
+      <c r="K87" s="36" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -46374,19 +46374,19 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="5">
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="K4:K43 K48:K87" xr:uid="{49FD4ECF-11D5-4427-853E-70B87273286A}">
-      <formula1>"医療,水産,木くず"</formula1>
-    </dataValidation>
-    <dataValidation type="whole" imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I48:J87 I4:J43" xr:uid="{66744D22-8ADC-4B40-BD61-F6D11EDB95DD}">
+    <dataValidation type="whole" imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I48:J87 I4:J43" xr:uid="{B1892A76-BE10-4072-86D9-2C71812BF0A8}">
       <formula1>1</formula1>
       <formula2>99999</formula2>
     </dataValidation>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C48:C87 C4:C43" xr:uid="{D7D37BC4-08CB-4A14-B294-88D81B8DF036}">
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C48:C87 C4:C43" xr:uid="{0790781A-F6C3-4B10-9B2C-18A6CB6FBD2C}">
       <formula1>"鴛 泊,鬼 脇,沓 形,仙法志"</formula1>
     </dataValidation>
-    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:G43 B48:B87 F48:G87 B4:B43" xr:uid="{B0173C76-3578-47B1-BF3E-E50D3F523F15}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="E4:E43 E48:E87" xr:uid="{F9839F94-3CFF-4DFE-BB7A-1C7B4A92775C}">
+    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:G43 B48:B87 F48:G87 B4:B43" xr:uid="{A2498656-289E-4E1E-9681-46262ADA0761}"/>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="E4:E43 E48:E87" xr:uid="{17E53FB0-39BB-45C4-94C6-70C96885CF69}">
       <formula1>"国保中央病院,道立鬼脇診療所,カムイウイスキー,福士水産㈱,糀谷商店,米田商店"</formula1>
+    </dataValidation>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="K4:K43 K48:K87" xr:uid="{0AF7E623-3ED6-42A7-99FF-D93D075A9296}">
+      <formula1>"医療,動植"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -46497,7 +46497,7 @@
       <c r="I4" s="25"/>
       <c r="J4" s="25"/>
       <c r="K4" s="25" t="str">
-        <f t="shared" ref="K4:K43" si="2">IF(E4="","",IF(E4="国保中央病院","医療","水産"))</f>
+        <f>IF(E4="","",IF(E4="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -46521,7 +46521,7 @@
       <c r="I5" s="25"/>
       <c r="J5" s="25"/>
       <c r="K5" s="25" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="K5:K43" si="2">IF(E5="","",IF(E5="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -47544,7 +47544,7 @@
       <c r="I48" s="25"/>
       <c r="J48" s="25"/>
       <c r="K48" s="25" t="str">
-        <f t="shared" ref="K48:K87" si="5">IF(E48="","",IF(E48="国保中央病院","医療","水産"))</f>
+        <f>IF(E48="","",IF(E48="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -47568,7 +47568,7 @@
       <c r="I49" s="25"/>
       <c r="J49" s="25"/>
       <c r="K49" s="25" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="K49:K87" si="5">IF(E49="","",IF(E49="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -48461,25 +48461,25 @@
       </c>
     </row>
     <row r="87" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="25">
+      <c r="A87" s="36">
         <v>80</v>
       </c>
-      <c r="B87" s="27"/>
-      <c r="C87" s="25"/>
-      <c r="D87" s="26"/>
+      <c r="B87" s="37"/>
+      <c r="C87" s="36"/>
+      <c r="D87" s="38"/>
       <c r="E87" s="39"/>
-      <c r="F87" s="29"/>
-      <c r="G87" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="H87" s="25" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="I87" s="25"/>
-      <c r="J87" s="25"/>
-      <c r="K87" s="25" t="str">
+      <c r="F87" s="40"/>
+      <c r="G87" s="40" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H87" s="36" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="I87" s="36"/>
+      <c r="J87" s="36"/>
+      <c r="K87" s="36" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -48506,19 +48506,19 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="5">
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="K4:K43 K48:K87" xr:uid="{0E6D87B1-D8CA-492A-B76C-6C64419FDD80}">
-      <formula1>"医療,水産,木くず"</formula1>
-    </dataValidation>
-    <dataValidation type="whole" imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I48:J87 I4:J43" xr:uid="{77AC9220-C2E0-4D80-8721-F1199B2DDCD8}">
+    <dataValidation type="whole" imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I48:J87 I4:J43" xr:uid="{F2FCE3A1-60F6-4B06-BEF2-9CCF5F10B8CA}">
       <formula1>1</formula1>
       <formula2>99999</formula2>
     </dataValidation>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C48:C87 C4:C43" xr:uid="{8E1292CC-FE6D-4D22-8915-46FE9B3BCE12}">
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C48:C87 C4:C43" xr:uid="{E4AADDFE-CA77-48C8-ADDD-41BB15DBEA8A}">
       <formula1>"鴛 泊,鬼 脇,沓 形,仙法志"</formula1>
     </dataValidation>
-    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:G43 B48:B87 F48:G87 B4:B43" xr:uid="{C754BD7D-8773-4D8C-AE1D-CE4130D2FBE3}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="E4:E43 E48:E87" xr:uid="{C2BE5E75-191F-4EB0-86E7-FAAF1B1DBEEC}">
+    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:G43 B48:B87 F48:G87 B4:B43" xr:uid="{2008A6DA-BB64-47CE-8AE3-57650B983A5B}"/>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="E4:E43 E48:E87" xr:uid="{DC84BFF1-AE6B-42F1-868E-6ADDA0B80DD1}">
       <formula1>"国保中央病院,道立鬼脇診療所,カムイウイスキー,福士水産㈱,糀谷商店,米田商店"</formula1>
+    </dataValidation>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="K4:K43 K48:K87" xr:uid="{CEEFAD08-CD9D-40C7-AC63-339FD36ACB7D}">
+      <formula1>"医療,動植"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -48629,7 +48629,7 @@
       <c r="I4" s="25"/>
       <c r="J4" s="25"/>
       <c r="K4" s="25" t="str">
-        <f t="shared" ref="K4:K43" si="2">IF(E4="","",IF(E4="国保中央病院","医療","水産"))</f>
+        <f>IF(E4="","",IF(E4="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -48653,7 +48653,7 @@
       <c r="I5" s="25"/>
       <c r="J5" s="25"/>
       <c r="K5" s="25" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="K5:K43" si="2">IF(E5="","",IF(E5="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -49676,7 +49676,7 @@
       <c r="I48" s="25"/>
       <c r="J48" s="25"/>
       <c r="K48" s="25" t="str">
-        <f t="shared" ref="K48:K87" si="5">IF(E48="","",IF(E48="国保中央病院","医療","水産"))</f>
+        <f>IF(E48="","",IF(E48="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -49700,7 +49700,7 @@
       <c r="I49" s="25"/>
       <c r="J49" s="25"/>
       <c r="K49" s="25" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="K49:K87" si="5">IF(E49="","",IF(E49="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -50593,25 +50593,25 @@
       </c>
     </row>
     <row r="87" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="25">
+      <c r="A87" s="36">
         <v>80</v>
       </c>
-      <c r="B87" s="27"/>
-      <c r="C87" s="25"/>
-      <c r="D87" s="26"/>
+      <c r="B87" s="37"/>
+      <c r="C87" s="36"/>
+      <c r="D87" s="38"/>
       <c r="E87" s="39"/>
-      <c r="F87" s="29"/>
-      <c r="G87" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="H87" s="25" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="I87" s="25"/>
-      <c r="J87" s="25"/>
-      <c r="K87" s="25" t="str">
+      <c r="F87" s="40"/>
+      <c r="G87" s="40" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H87" s="36" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="I87" s="36"/>
+      <c r="J87" s="36"/>
+      <c r="K87" s="36" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -50638,19 +50638,19 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="5">
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="K4:K43 K48:K87" xr:uid="{397A1C33-9BF8-4369-BC6C-532CFE36FB02}">
-      <formula1>"医療,水産,木くず"</formula1>
-    </dataValidation>
-    <dataValidation type="whole" imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I48:J87 I4:J43" xr:uid="{8034B150-CE6A-4AB4-9489-9578D092009C}">
+    <dataValidation type="whole" imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I48:J87 I4:J43" xr:uid="{23541E70-E63B-4AC7-94ED-312EE91E9C0F}">
       <formula1>1</formula1>
       <formula2>99999</formula2>
     </dataValidation>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C48:C87 C4:C43" xr:uid="{2985913D-F6FE-4604-A22A-0253D64CE6C9}">
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C48:C87 C4:C43" xr:uid="{A9D3A217-42FD-4F6C-8E25-60F69ACDDBD7}">
       <formula1>"鴛 泊,鬼 脇,沓 形,仙法志"</formula1>
     </dataValidation>
-    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:G43 B48:B87 F48:G87 B4:B43" xr:uid="{F8F9C7D2-244A-43DE-9798-84623CDA3F3F}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="E4:E43 E48:E87" xr:uid="{61A8A38F-26B4-42B7-AD45-794D3784C4C8}">
+    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:G43 B48:B87 F48:G87 B4:B43" xr:uid="{43EB4794-241D-4205-8C52-24B5615BF5F3}"/>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="E4:E43 E48:E87" xr:uid="{1D2A9254-73C0-4B25-8021-70ACB38D54BB}">
       <formula1>"国保中央病院,道立鬼脇診療所,カムイウイスキー,福士水産㈱,糀谷商店,米田商店"</formula1>
+    </dataValidation>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="K4:K43 K48:K87" xr:uid="{D00A6877-7BCE-4A51-9469-80B45A562837}">
+      <formula1>"医療,動植"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -50761,7 +50761,7 @@
       <c r="I4" s="25"/>
       <c r="J4" s="25"/>
       <c r="K4" s="25" t="str">
-        <f t="shared" ref="K4:K43" si="2">IF(E4="","",IF(E4="国保中央病院","医療","水産"))</f>
+        <f>IF(E4="","",IF(E4="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -50785,7 +50785,7 @@
       <c r="I5" s="25"/>
       <c r="J5" s="25"/>
       <c r="K5" s="25" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="K5:K43" si="2">IF(E5="","",IF(E5="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -51808,7 +51808,7 @@
       <c r="I48" s="25"/>
       <c r="J48" s="25"/>
       <c r="K48" s="25" t="str">
-        <f t="shared" ref="K48:K87" si="5">IF(E48="","",IF(E48="国保中央病院","医療","水産"))</f>
+        <f>IF(E48="","",IF(E48="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -51832,7 +51832,7 @@
       <c r="I49" s="25"/>
       <c r="J49" s="25"/>
       <c r="K49" s="25" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="K49:K87" si="5">IF(E49="","",IF(E49="国保中央病院","医療","動植"))</f>
         <v/>
       </c>
     </row>
@@ -52725,25 +52725,25 @@
       </c>
     </row>
     <row r="87" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="25">
+      <c r="A87" s="36">
         <v>80</v>
       </c>
-      <c r="B87" s="27"/>
-      <c r="C87" s="25"/>
-      <c r="D87" s="26"/>
+      <c r="B87" s="37"/>
+      <c r="C87" s="36"/>
+      <c r="D87" s="38"/>
       <c r="E87" s="39"/>
-      <c r="F87" s="29"/>
-      <c r="G87" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="H87" s="25" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="I87" s="25"/>
-      <c r="J87" s="25"/>
-      <c r="K87" s="25" t="str">
+      <c r="F87" s="40"/>
+      <c r="G87" s="40" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H87" s="36" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="I87" s="36"/>
+      <c r="J87" s="36"/>
+      <c r="K87" s="36" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -52770,19 +52770,19 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="5">
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="K4:K43 K48:K87" xr:uid="{1EF72024-A452-42DD-8531-F0DF09B428B0}">
-      <formula1>"医療,水産,木くず"</formula1>
-    </dataValidation>
-    <dataValidation type="whole" imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I48:J87 I4:J43" xr:uid="{0629D84C-8374-4F7F-A8E2-304AF83F0626}">
+    <dataValidation type="whole" imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I48:J87 I4:J43" xr:uid="{F27AEA6C-960C-4A53-A026-A58DB14EAACE}">
       <formula1>1</formula1>
       <formula2>99999</formula2>
     </dataValidation>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C48:C87 C4:C43" xr:uid="{A04AF198-5409-48B7-9868-F0AAB08FB089}">
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C48:C87 C4:C43" xr:uid="{C4E2983D-D9E0-4E2D-9943-3CF043BFB6CB}">
       <formula1>"鴛 泊,鬼 脇,沓 形,仙法志"</formula1>
     </dataValidation>
-    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:G43 B48:B87 F48:G87 B4:B43" xr:uid="{841ADB41-3268-4A53-A571-CB590D5C1F77}"/>
-    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="E4:E43 E48:E87" xr:uid="{5A4A6281-00FB-4D51-8113-86B351AA7E6D}">
+    <dataValidation imeMode="disabled" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:G43 B48:B87 F48:G87 B4:B43" xr:uid="{2CA106B3-3D11-4EAB-ACF7-D6C7310B288A}"/>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="E4:E43 E48:E87" xr:uid="{C956A1E2-492C-44AD-B25D-8ED2B6238F18}">
       <formula1>"国保中央病院,道立鬼脇診療所,カムイウイスキー,福士水産㈱,糀谷商店,米田商店"</formula1>
+    </dataValidation>
+    <dataValidation type="list" imeMode="on" allowBlank="1" showInputMessage="1" sqref="K4:K43 K48:K87" xr:uid="{25324131-6AC6-4EDA-9BF6-04CD9DCBF791}">
+      <formula1>"医療,動植"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/(枠)◯年度一式/産廃原簿.xlsx
+++ b/(枠)◯年度一式/産廃原簿.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\layhi\OneDrive\ドキュメント\日報月報他\(枠)◯年度一式\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D51A5CA-F132-48AB-BAA0-9000D6CBC30C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC2B8A4-495E-4BD5-838E-F534E6159C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="20100" windowHeight="14565" tabRatio="942" firstSheet="10" activeTab="24" xr2:uid="{5AD5A155-4AC2-4929-A579-33332D170D49}"/>
+    <workbookView xWindow="540" yWindow="765" windowWidth="20670" windowHeight="14715" tabRatio="942" firstSheet="9" activeTab="24" xr2:uid="{5AD5A155-4AC2-4929-A579-33332D170D49}"/>
   </bookViews>
   <sheets>
     <sheet name="受付04" sheetId="20" r:id="rId1"/>
@@ -1080,10 +1080,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1092,13 +1095,25 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1114,21 +1129,6 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -10392,11 +10392,11 @@
       <c r="D1" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="64" t="s">
+      <c r="E1" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
       <c r="J1" s="21"/>
       <c r="K1" s="22"/>
     </row>
@@ -10413,16 +10413,16 @@
       <c r="D2" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="65" t="s">
+      <c r="E2" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="59" t="s">
+      <c r="F2" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="61" t="s">
+      <c r="G2" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="62" t="s">
+      <c r="H2" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="55" t="s">
@@ -10431,7 +10431,7 @@
       <c r="J2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="60" t="s">
+      <c r="K2" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -10440,13 +10440,13 @@
       <c r="B3" s="56"/>
       <c r="C3" s="56"/>
       <c r="D3" s="58"/>
-      <c r="E3" s="63"/>
+      <c r="E3" s="60"/>
       <c r="F3" s="56"/>
       <c r="G3" s="58"/>
-      <c r="H3" s="63"/>
+      <c r="H3" s="60"/>
       <c r="I3" s="56"/>
       <c r="J3" s="56"/>
-      <c r="K3" s="60"/>
+      <c r="K3" s="64"/>
     </row>
     <row r="4" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="7">
@@ -10659,11 +10659,11 @@
       <c r="D15" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="64" t="s">
+      <c r="E15" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="65"/>
       <c r="J15" s="21"/>
       <c r="K15" s="22"/>
     </row>
@@ -10680,16 +10680,16 @@
       <c r="D16" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="65" t="s">
+      <c r="E16" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="59" t="s">
+      <c r="F16" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="61" t="s">
+      <c r="G16" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="62" t="s">
+      <c r="H16" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I16" s="55" t="s">
@@ -10698,7 +10698,7 @@
       <c r="J16" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="60" t="s">
+      <c r="K16" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -10707,13 +10707,13 @@
       <c r="B17" s="56"/>
       <c r="C17" s="56"/>
       <c r="D17" s="58"/>
-      <c r="E17" s="63"/>
+      <c r="E17" s="60"/>
       <c r="F17" s="56"/>
       <c r="G17" s="58"/>
-      <c r="H17" s="63"/>
+      <c r="H17" s="60"/>
       <c r="I17" s="56"/>
       <c r="J17" s="56"/>
-      <c r="K17" s="60"/>
+      <c r="K17" s="64"/>
     </row>
     <row r="18" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7">
@@ -10926,11 +10926,11 @@
       <c r="D29" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E29" s="64" t="s">
+      <c r="E29" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="64"/>
-      <c r="G29" s="64"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="65"/>
       <c r="J29" s="21"/>
       <c r="K29" s="22"/>
     </row>
@@ -10947,16 +10947,16 @@
       <c r="D30" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E30" s="65" t="s">
+      <c r="E30" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F30" s="59" t="s">
+      <c r="F30" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G30" s="61" t="s">
+      <c r="G30" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="62" t="s">
+      <c r="H30" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I30" s="55" t="s">
@@ -10965,7 +10965,7 @@
       <c r="J30" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K30" s="60" t="s">
+      <c r="K30" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -10974,13 +10974,13 @@
       <c r="B31" s="56"/>
       <c r="C31" s="56"/>
       <c r="D31" s="58"/>
-      <c r="E31" s="63"/>
+      <c r="E31" s="60"/>
       <c r="F31" s="56"/>
       <c r="G31" s="58"/>
-      <c r="H31" s="63"/>
+      <c r="H31" s="60"/>
       <c r="I31" s="56"/>
       <c r="J31" s="56"/>
-      <c r="K31" s="60"/>
+      <c r="K31" s="64"/>
     </row>
     <row r="32" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7">
@@ -11193,11 +11193,11 @@
       <c r="D43" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E43" s="64" t="s">
+      <c r="E43" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="64"/>
-      <c r="G43" s="64"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
       <c r="J43" s="21"/>
       <c r="K43" s="22"/>
     </row>
@@ -11214,16 +11214,16 @@
       <c r="D44" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="65" t="s">
+      <c r="E44" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="59" t="s">
+      <c r="F44" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G44" s="61" t="s">
+      <c r="G44" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H44" s="62" t="s">
+      <c r="H44" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I44" s="55" t="s">
@@ -11232,7 +11232,7 @@
       <c r="J44" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="60" t="s">
+      <c r="K44" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -11241,13 +11241,13 @@
       <c r="B45" s="56"/>
       <c r="C45" s="56"/>
       <c r="D45" s="58"/>
-      <c r="E45" s="63"/>
+      <c r="E45" s="60"/>
       <c r="F45" s="56"/>
       <c r="G45" s="58"/>
-      <c r="H45" s="63"/>
+      <c r="H45" s="60"/>
       <c r="I45" s="56"/>
       <c r="J45" s="56"/>
-      <c r="K45" s="60"/>
+      <c r="K45" s="64"/>
     </row>
     <row r="46" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7">
@@ -11460,11 +11460,11 @@
       <c r="D57" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E57" s="64" t="s">
+      <c r="E57" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="64"/>
-      <c r="G57" s="64"/>
+      <c r="F57" s="65"/>
+      <c r="G57" s="65"/>
       <c r="J57" s="21"/>
       <c r="K57" s="22"/>
     </row>
@@ -11481,16 +11481,16 @@
       <c r="D58" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="65" t="s">
+      <c r="E58" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F58" s="59" t="s">
+      <c r="F58" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G58" s="61" t="s">
+      <c r="G58" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H58" s="62" t="s">
+      <c r="H58" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I58" s="55" t="s">
@@ -11499,7 +11499,7 @@
       <c r="J58" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K58" s="60" t="s">
+      <c r="K58" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -11508,13 +11508,13 @@
       <c r="B59" s="56"/>
       <c r="C59" s="56"/>
       <c r="D59" s="58"/>
-      <c r="E59" s="63"/>
+      <c r="E59" s="60"/>
       <c r="F59" s="56"/>
       <c r="G59" s="58"/>
-      <c r="H59" s="63"/>
+      <c r="H59" s="60"/>
       <c r="I59" s="56"/>
       <c r="J59" s="56"/>
-      <c r="K59" s="60"/>
+      <c r="K59" s="64"/>
     </row>
     <row r="60" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="7">
@@ -11727,11 +11727,11 @@
       <c r="D71" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E71" s="64" t="s">
+      <c r="E71" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F71" s="64"/>
-      <c r="G71" s="64"/>
+      <c r="F71" s="65"/>
+      <c r="G71" s="65"/>
       <c r="J71" s="21"/>
       <c r="K71" s="22"/>
     </row>
@@ -11748,16 +11748,16 @@
       <c r="D72" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E72" s="65" t="s">
+      <c r="E72" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F72" s="59" t="s">
+      <c r="F72" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G72" s="61" t="s">
+      <c r="G72" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H72" s="62" t="s">
+      <c r="H72" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I72" s="55" t="s">
@@ -11766,7 +11766,7 @@
       <c r="J72" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K72" s="60" t="s">
+      <c r="K72" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -11775,13 +11775,13 @@
       <c r="B73" s="56"/>
       <c r="C73" s="56"/>
       <c r="D73" s="58"/>
-      <c r="E73" s="63"/>
+      <c r="E73" s="60"/>
       <c r="F73" s="56"/>
       <c r="G73" s="58"/>
-      <c r="H73" s="63"/>
+      <c r="H73" s="60"/>
       <c r="I73" s="56"/>
       <c r="J73" s="56"/>
-      <c r="K73" s="60"/>
+      <c r="K73" s="64"/>
     </row>
     <row r="74" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="7">
@@ -11994,11 +11994,11 @@
       <c r="D85" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E85" s="64" t="s">
+      <c r="E85" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F85" s="64"/>
-      <c r="G85" s="64"/>
+      <c r="F85" s="65"/>
+      <c r="G85" s="65"/>
       <c r="J85" s="21"/>
       <c r="K85" s="22"/>
     </row>
@@ -12015,16 +12015,16 @@
       <c r="D86" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E86" s="65" t="s">
+      <c r="E86" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F86" s="59" t="s">
+      <c r="F86" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G86" s="61" t="s">
+      <c r="G86" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H86" s="62" t="s">
+      <c r="H86" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I86" s="55" t="s">
@@ -12033,7 +12033,7 @@
       <c r="J86" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K86" s="60" t="s">
+      <c r="K86" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -12042,13 +12042,13 @@
       <c r="B87" s="56"/>
       <c r="C87" s="56"/>
       <c r="D87" s="58"/>
-      <c r="E87" s="63"/>
+      <c r="E87" s="60"/>
       <c r="F87" s="56"/>
       <c r="G87" s="58"/>
-      <c r="H87" s="63"/>
+      <c r="H87" s="60"/>
       <c r="I87" s="56"/>
       <c r="J87" s="56"/>
-      <c r="K87" s="60"/>
+      <c r="K87" s="64"/>
     </row>
     <row r="88" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="7">
@@ -12261,11 +12261,11 @@
       <c r="D99" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E99" s="64" t="s">
+      <c r="E99" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F99" s="64"/>
-      <c r="G99" s="64"/>
+      <c r="F99" s="65"/>
+      <c r="G99" s="65"/>
       <c r="J99" s="21"/>
       <c r="K99" s="22"/>
     </row>
@@ -12282,16 +12282,16 @@
       <c r="D100" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E100" s="65" t="s">
+      <c r="E100" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F100" s="59" t="s">
+      <c r="F100" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G100" s="61" t="s">
+      <c r="G100" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H100" s="62" t="s">
+      <c r="H100" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I100" s="55" t="s">
@@ -12300,7 +12300,7 @@
       <c r="J100" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K100" s="60" t="s">
+      <c r="K100" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -12309,13 +12309,13 @@
       <c r="B101" s="56"/>
       <c r="C101" s="56"/>
       <c r="D101" s="58"/>
-      <c r="E101" s="63"/>
+      <c r="E101" s="60"/>
       <c r="F101" s="56"/>
       <c r="G101" s="58"/>
-      <c r="H101" s="63"/>
+      <c r="H101" s="60"/>
       <c r="I101" s="56"/>
       <c r="J101" s="56"/>
-      <c r="K101" s="60"/>
+      <c r="K101" s="64"/>
     </row>
     <row r="102" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="7">
@@ -12528,11 +12528,11 @@
       <c r="D113" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E113" s="64" t="s">
+      <c r="E113" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F113" s="64"/>
-      <c r="G113" s="64"/>
+      <c r="F113" s="65"/>
+      <c r="G113" s="65"/>
       <c r="J113" s="21"/>
       <c r="K113" s="22"/>
     </row>
@@ -12549,16 +12549,16 @@
       <c r="D114" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E114" s="65" t="s">
+      <c r="E114" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F114" s="59" t="s">
+      <c r="F114" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G114" s="61" t="s">
+      <c r="G114" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H114" s="62" t="s">
+      <c r="H114" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I114" s="55" t="s">
@@ -12567,7 +12567,7 @@
       <c r="J114" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K114" s="60" t="s">
+      <c r="K114" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -12576,13 +12576,13 @@
       <c r="B115" s="56"/>
       <c r="C115" s="56"/>
       <c r="D115" s="58"/>
-      <c r="E115" s="63"/>
+      <c r="E115" s="60"/>
       <c r="F115" s="56"/>
       <c r="G115" s="58"/>
-      <c r="H115" s="63"/>
+      <c r="H115" s="60"/>
       <c r="I115" s="56"/>
       <c r="J115" s="56"/>
-      <c r="K115" s="60"/>
+      <c r="K115" s="64"/>
     </row>
     <row r="116" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="7">
@@ -12795,11 +12795,11 @@
       <c r="D127" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E127" s="64" t="s">
+      <c r="E127" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F127" s="64"/>
-      <c r="G127" s="64"/>
+      <c r="F127" s="65"/>
+      <c r="G127" s="65"/>
       <c r="J127" s="21"/>
       <c r="K127" s="22"/>
     </row>
@@ -12816,16 +12816,16 @@
       <c r="D128" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E128" s="65" t="s">
+      <c r="E128" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F128" s="59" t="s">
+      <c r="F128" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G128" s="61" t="s">
+      <c r="G128" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H128" s="62" t="s">
+      <c r="H128" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I128" s="55" t="s">
@@ -12834,7 +12834,7 @@
       <c r="J128" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K128" s="60" t="s">
+      <c r="K128" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -12843,13 +12843,13 @@
       <c r="B129" s="56"/>
       <c r="C129" s="56"/>
       <c r="D129" s="58"/>
-      <c r="E129" s="63"/>
+      <c r="E129" s="60"/>
       <c r="F129" s="56"/>
       <c r="G129" s="58"/>
-      <c r="H129" s="63"/>
+      <c r="H129" s="60"/>
       <c r="I129" s="56"/>
       <c r="J129" s="56"/>
-      <c r="K129" s="60"/>
+      <c r="K129" s="64"/>
     </row>
     <row r="130" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="7">
@@ -13062,11 +13062,11 @@
       <c r="D141" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E141" s="64" t="s">
+      <c r="E141" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F141" s="64"/>
-      <c r="G141" s="64"/>
+      <c r="F141" s="65"/>
+      <c r="G141" s="65"/>
       <c r="J141" s="21"/>
       <c r="K141" s="22"/>
     </row>
@@ -13083,16 +13083,16 @@
       <c r="D142" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E142" s="65" t="s">
+      <c r="E142" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F142" s="59" t="s">
+      <c r="F142" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G142" s="61" t="s">
+      <c r="G142" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H142" s="62" t="s">
+      <c r="H142" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I142" s="55" t="s">
@@ -13101,7 +13101,7 @@
       <c r="J142" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K142" s="60" t="s">
+      <c r="K142" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -13110,13 +13110,13 @@
       <c r="B143" s="56"/>
       <c r="C143" s="56"/>
       <c r="D143" s="58"/>
-      <c r="E143" s="63"/>
+      <c r="E143" s="60"/>
       <c r="F143" s="56"/>
       <c r="G143" s="58"/>
-      <c r="H143" s="63"/>
+      <c r="H143" s="60"/>
       <c r="I143" s="56"/>
       <c r="J143" s="56"/>
-      <c r="K143" s="60"/>
+      <c r="K143" s="64"/>
     </row>
     <row r="144" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144" s="7">
@@ -13329,11 +13329,11 @@
       <c r="D155" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E155" s="64" t="s">
+      <c r="E155" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F155" s="64"/>
-      <c r="G155" s="64"/>
+      <c r="F155" s="65"/>
+      <c r="G155" s="65"/>
       <c r="J155" s="21"/>
       <c r="K155" s="22"/>
     </row>
@@ -13350,16 +13350,16 @@
       <c r="D156" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E156" s="65" t="s">
+      <c r="E156" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F156" s="59" t="s">
+      <c r="F156" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G156" s="61" t="s">
+      <c r="G156" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H156" s="62" t="s">
+      <c r="H156" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I156" s="55" t="s">
@@ -13368,7 +13368,7 @@
       <c r="J156" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K156" s="60" t="s">
+      <c r="K156" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -13377,13 +13377,13 @@
       <c r="B157" s="56"/>
       <c r="C157" s="56"/>
       <c r="D157" s="58"/>
-      <c r="E157" s="63"/>
+      <c r="E157" s="60"/>
       <c r="F157" s="56"/>
       <c r="G157" s="58"/>
-      <c r="H157" s="63"/>
+      <c r="H157" s="60"/>
       <c r="I157" s="56"/>
       <c r="J157" s="56"/>
-      <c r="K157" s="60"/>
+      <c r="K157" s="64"/>
     </row>
     <row r="158" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A158" s="7">
@@ -13596,11 +13596,11 @@
       <c r="D169" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E169" s="64" t="s">
+      <c r="E169" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F169" s="64"/>
-      <c r="G169" s="64"/>
+      <c r="F169" s="65"/>
+      <c r="G169" s="65"/>
       <c r="J169" s="21"/>
       <c r="K169" s="22"/>
     </row>
@@ -13617,16 +13617,16 @@
       <c r="D170" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E170" s="65" t="s">
+      <c r="E170" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F170" s="59" t="s">
+      <c r="F170" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G170" s="61" t="s">
+      <c r="G170" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H170" s="62" t="s">
+      <c r="H170" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I170" s="55" t="s">
@@ -13635,7 +13635,7 @@
       <c r="J170" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K170" s="60" t="s">
+      <c r="K170" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -13644,13 +13644,13 @@
       <c r="B171" s="56"/>
       <c r="C171" s="56"/>
       <c r="D171" s="58"/>
-      <c r="E171" s="63"/>
+      <c r="E171" s="60"/>
       <c r="F171" s="56"/>
       <c r="G171" s="58"/>
-      <c r="H171" s="63"/>
+      <c r="H171" s="60"/>
       <c r="I171" s="56"/>
       <c r="J171" s="56"/>
-      <c r="K171" s="60"/>
+      <c r="K171" s="64"/>
     </row>
     <row r="172" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A172" s="7">
@@ -13863,11 +13863,11 @@
       <c r="D183" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E183" s="64" t="s">
+      <c r="E183" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F183" s="64"/>
-      <c r="G183" s="64"/>
+      <c r="F183" s="65"/>
+      <c r="G183" s="65"/>
       <c r="J183" s="21"/>
       <c r="K183" s="22"/>
     </row>
@@ -13884,16 +13884,16 @@
       <c r="D184" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E184" s="65" t="s">
+      <c r="E184" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F184" s="59" t="s">
+      <c r="F184" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G184" s="61" t="s">
+      <c r="G184" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H184" s="62" t="s">
+      <c r="H184" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I184" s="55" t="s">
@@ -13902,7 +13902,7 @@
       <c r="J184" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K184" s="60" t="s">
+      <c r="K184" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -13911,13 +13911,13 @@
       <c r="B185" s="56"/>
       <c r="C185" s="56"/>
       <c r="D185" s="58"/>
-      <c r="E185" s="63"/>
+      <c r="E185" s="60"/>
       <c r="F185" s="56"/>
       <c r="G185" s="58"/>
-      <c r="H185" s="63"/>
+      <c r="H185" s="60"/>
       <c r="I185" s="56"/>
       <c r="J185" s="56"/>
-      <c r="K185" s="60"/>
+      <c r="K185" s="64"/>
     </row>
     <row r="186" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A186" s="7">
@@ -14130,11 +14130,11 @@
       <c r="D197" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E197" s="64" t="s">
+      <c r="E197" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F197" s="64"/>
-      <c r="G197" s="64"/>
+      <c r="F197" s="65"/>
+      <c r="G197" s="65"/>
       <c r="J197" s="21"/>
       <c r="K197" s="22"/>
     </row>
@@ -14151,16 +14151,16 @@
       <c r="D198" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E198" s="65" t="s">
+      <c r="E198" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F198" s="59" t="s">
+      <c r="F198" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G198" s="61" t="s">
+      <c r="G198" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H198" s="62" t="s">
+      <c r="H198" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I198" s="55" t="s">
@@ -14169,7 +14169,7 @@
       <c r="J198" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K198" s="60" t="s">
+      <c r="K198" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -14178,13 +14178,13 @@
       <c r="B199" s="56"/>
       <c r="C199" s="56"/>
       <c r="D199" s="58"/>
-      <c r="E199" s="63"/>
+      <c r="E199" s="60"/>
       <c r="F199" s="56"/>
       <c r="G199" s="58"/>
-      <c r="H199" s="63"/>
+      <c r="H199" s="60"/>
       <c r="I199" s="56"/>
       <c r="J199" s="56"/>
-      <c r="K199" s="60"/>
+      <c r="K199" s="64"/>
     </row>
     <row r="200" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A200" s="7">
@@ -14397,11 +14397,11 @@
       <c r="D211" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E211" s="68" t="s">
+      <c r="E211" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="F211" s="68"/>
-      <c r="G211" s="68"/>
+      <c r="F211" s="73"/>
+      <c r="G211" s="73"/>
       <c r="J211" s="21"/>
       <c r="K211" s="22"/>
     </row>
@@ -14415,19 +14415,19 @@
       <c r="C212" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="D212" s="74" t="s">
+      <c r="D212" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="E212" s="69" t="s">
+      <c r="E212" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="F212" s="71" t="s">
+      <c r="F212" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="G212" s="72" t="s">
+      <c r="G212" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="H212" s="66" t="s">
+      <c r="H212" s="71" t="s">
         <v>4</v>
       </c>
       <c r="I212" s="55" t="s">
@@ -14436,7 +14436,7 @@
       <c r="J212" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K212" s="60" t="s">
+      <c r="K212" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -14444,14 +14444,14 @@
       <c r="A213" s="56"/>
       <c r="B213" s="56"/>
       <c r="C213" s="56"/>
-      <c r="D213" s="75"/>
-      <c r="E213" s="70"/>
-      <c r="F213" s="60"/>
-      <c r="G213" s="73"/>
-      <c r="H213" s="67"/>
+      <c r="D213" s="70"/>
+      <c r="E213" s="75"/>
+      <c r="F213" s="64"/>
+      <c r="G213" s="68"/>
+      <c r="H213" s="72"/>
       <c r="I213" s="56"/>
       <c r="J213" s="56"/>
-      <c r="K213" s="60"/>
+      <c r="K213" s="64"/>
     </row>
     <row r="214" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A214" s="7">
@@ -14664,11 +14664,11 @@
       <c r="D225" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E225" s="64" t="s">
+      <c r="E225" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F225" s="64"/>
-      <c r="G225" s="64"/>
+      <c r="F225" s="65"/>
+      <c r="G225" s="65"/>
       <c r="J225" s="21"/>
       <c r="K225" s="22"/>
     </row>
@@ -14685,16 +14685,16 @@
       <c r="D226" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E226" s="65" t="s">
+      <c r="E226" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F226" s="59" t="s">
+      <c r="F226" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G226" s="61" t="s">
+      <c r="G226" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H226" s="62" t="s">
+      <c r="H226" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I226" s="55" t="s">
@@ -14703,7 +14703,7 @@
       <c r="J226" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K226" s="60" t="s">
+      <c r="K226" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -14712,13 +14712,13 @@
       <c r="B227" s="56"/>
       <c r="C227" s="56"/>
       <c r="D227" s="58"/>
-      <c r="E227" s="63"/>
+      <c r="E227" s="60"/>
       <c r="F227" s="56"/>
       <c r="G227" s="58"/>
-      <c r="H227" s="63"/>
+      <c r="H227" s="60"/>
       <c r="I227" s="56"/>
       <c r="J227" s="56"/>
-      <c r="K227" s="60"/>
+      <c r="K227" s="64"/>
     </row>
     <row r="228" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A228" s="7">
@@ -14931,11 +14931,11 @@
       <c r="D239" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E239" s="64" t="s">
+      <c r="E239" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F239" s="64"/>
-      <c r="G239" s="64"/>
+      <c r="F239" s="65"/>
+      <c r="G239" s="65"/>
       <c r="J239" s="21"/>
       <c r="K239" s="22"/>
     </row>
@@ -14952,16 +14952,16 @@
       <c r="D240" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E240" s="65" t="s">
+      <c r="E240" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F240" s="59" t="s">
+      <c r="F240" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G240" s="61" t="s">
+      <c r="G240" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H240" s="62" t="s">
+      <c r="H240" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I240" s="55" t="s">
@@ -14970,7 +14970,7 @@
       <c r="J240" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K240" s="60" t="s">
+      <c r="K240" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -14979,13 +14979,13 @@
       <c r="B241" s="56"/>
       <c r="C241" s="56"/>
       <c r="D241" s="58"/>
-      <c r="E241" s="63"/>
+      <c r="E241" s="60"/>
       <c r="F241" s="56"/>
       <c r="G241" s="58"/>
-      <c r="H241" s="63"/>
+      <c r="H241" s="60"/>
       <c r="I241" s="56"/>
       <c r="J241" s="56"/>
-      <c r="K241" s="60"/>
+      <c r="K241" s="64"/>
     </row>
     <row r="242" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A242" s="7">
@@ -15198,11 +15198,11 @@
       <c r="D253" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E253" s="64" t="s">
+      <c r="E253" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F253" s="64"/>
-      <c r="G253" s="64"/>
+      <c r="F253" s="65"/>
+      <c r="G253" s="65"/>
       <c r="J253" s="21"/>
       <c r="K253" s="22"/>
     </row>
@@ -15219,16 +15219,16 @@
       <c r="D254" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E254" s="65" t="s">
+      <c r="E254" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F254" s="59" t="s">
+      <c r="F254" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G254" s="61" t="s">
+      <c r="G254" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H254" s="62" t="s">
+      <c r="H254" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I254" s="55" t="s">
@@ -15237,7 +15237,7 @@
       <c r="J254" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K254" s="60" t="s">
+      <c r="K254" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -15246,13 +15246,13 @@
       <c r="B255" s="56"/>
       <c r="C255" s="56"/>
       <c r="D255" s="58"/>
-      <c r="E255" s="63"/>
+      <c r="E255" s="60"/>
       <c r="F255" s="56"/>
       <c r="G255" s="58"/>
-      <c r="H255" s="63"/>
+      <c r="H255" s="60"/>
       <c r="I255" s="56"/>
       <c r="J255" s="56"/>
-      <c r="K255" s="60"/>
+      <c r="K255" s="64"/>
     </row>
     <row r="256" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A256" s="7">
@@ -15465,11 +15465,11 @@
       <c r="D267" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E267" s="64" t="s">
+      <c r="E267" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F267" s="64"/>
-      <c r="G267" s="64"/>
+      <c r="F267" s="65"/>
+      <c r="G267" s="65"/>
       <c r="J267" s="21"/>
       <c r="K267" s="22"/>
     </row>
@@ -15486,16 +15486,16 @@
       <c r="D268" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E268" s="65" t="s">
+      <c r="E268" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F268" s="59" t="s">
+      <c r="F268" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G268" s="61" t="s">
+      <c r="G268" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H268" s="62" t="s">
+      <c r="H268" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I268" s="55" t="s">
@@ -15504,7 +15504,7 @@
       <c r="J268" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K268" s="60" t="s">
+      <c r="K268" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -15513,13 +15513,13 @@
       <c r="B269" s="56"/>
       <c r="C269" s="56"/>
       <c r="D269" s="58"/>
-      <c r="E269" s="63"/>
+      <c r="E269" s="60"/>
       <c r="F269" s="56"/>
       <c r="G269" s="58"/>
-      <c r="H269" s="63"/>
+      <c r="H269" s="60"/>
       <c r="I269" s="56"/>
       <c r="J269" s="56"/>
-      <c r="K269" s="60"/>
+      <c r="K269" s="64"/>
     </row>
     <row r="270" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A270" s="7">
@@ -15732,11 +15732,11 @@
       <c r="D281" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E281" s="64" t="s">
+      <c r="E281" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F281" s="64"/>
-      <c r="G281" s="64"/>
+      <c r="F281" s="65"/>
+      <c r="G281" s="65"/>
       <c r="J281" s="21"/>
       <c r="K281" s="22"/>
     </row>
@@ -15753,16 +15753,16 @@
       <c r="D282" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E282" s="65" t="s">
+      <c r="E282" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F282" s="59" t="s">
+      <c r="F282" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G282" s="61" t="s">
+      <c r="G282" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H282" s="62" t="s">
+      <c r="H282" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I282" s="55" t="s">
@@ -15771,7 +15771,7 @@
       <c r="J282" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K282" s="60" t="s">
+      <c r="K282" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -15780,13 +15780,13 @@
       <c r="B283" s="56"/>
       <c r="C283" s="56"/>
       <c r="D283" s="58"/>
-      <c r="E283" s="63"/>
+      <c r="E283" s="60"/>
       <c r="F283" s="56"/>
       <c r="G283" s="58"/>
-      <c r="H283" s="63"/>
+      <c r="H283" s="60"/>
       <c r="I283" s="56"/>
       <c r="J283" s="56"/>
-      <c r="K283" s="60"/>
+      <c r="K283" s="64"/>
     </row>
     <row r="284" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A284" s="7">
@@ -15999,11 +15999,11 @@
       <c r="D295" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E295" s="64" t="s">
+      <c r="E295" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F295" s="64"/>
-      <c r="G295" s="64"/>
+      <c r="F295" s="65"/>
+      <c r="G295" s="65"/>
       <c r="J295" s="21"/>
       <c r="K295" s="22"/>
     </row>
@@ -16020,16 +16020,16 @@
       <c r="D296" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E296" s="65" t="s">
+      <c r="E296" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F296" s="59" t="s">
+      <c r="F296" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G296" s="61" t="s">
+      <c r="G296" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H296" s="62" t="s">
+      <c r="H296" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I296" s="55" t="s">
@@ -16038,7 +16038,7 @@
       <c r="J296" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K296" s="60" t="s">
+      <c r="K296" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -16047,13 +16047,13 @@
       <c r="B297" s="56"/>
       <c r="C297" s="56"/>
       <c r="D297" s="58"/>
-      <c r="E297" s="63"/>
+      <c r="E297" s="60"/>
       <c r="F297" s="56"/>
       <c r="G297" s="58"/>
-      <c r="H297" s="63"/>
+      <c r="H297" s="60"/>
       <c r="I297" s="56"/>
       <c r="J297" s="56"/>
-      <c r="K297" s="60"/>
+      <c r="K297" s="64"/>
     </row>
     <row r="298" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A298" s="7">
@@ -16266,11 +16266,11 @@
       <c r="D309" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E309" s="64" t="s">
+      <c r="E309" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F309" s="64"/>
-      <c r="G309" s="64"/>
+      <c r="F309" s="65"/>
+      <c r="G309" s="65"/>
       <c r="J309" s="21"/>
       <c r="K309" s="22"/>
     </row>
@@ -16287,16 +16287,16 @@
       <c r="D310" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E310" s="65" t="s">
+      <c r="E310" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F310" s="59" t="s">
+      <c r="F310" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G310" s="61" t="s">
+      <c r="G310" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H310" s="62" t="s">
+      <c r="H310" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I310" s="55" t="s">
@@ -16305,7 +16305,7 @@
       <c r="J310" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K310" s="60" t="s">
+      <c r="K310" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -16314,13 +16314,13 @@
       <c r="B311" s="56"/>
       <c r="C311" s="56"/>
       <c r="D311" s="58"/>
-      <c r="E311" s="63"/>
+      <c r="E311" s="60"/>
       <c r="F311" s="56"/>
       <c r="G311" s="58"/>
-      <c r="H311" s="63"/>
+      <c r="H311" s="60"/>
       <c r="I311" s="56"/>
       <c r="J311" s="56"/>
-      <c r="K311" s="60"/>
+      <c r="K311" s="64"/>
     </row>
     <row r="312" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A312" s="7">
@@ -16533,11 +16533,11 @@
       <c r="D323" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E323" s="64" t="s">
+      <c r="E323" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F323" s="64"/>
-      <c r="G323" s="64"/>
+      <c r="F323" s="65"/>
+      <c r="G323" s="65"/>
       <c r="J323" s="21"/>
       <c r="K323" s="22"/>
     </row>
@@ -16554,16 +16554,16 @@
       <c r="D324" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E324" s="65" t="s">
+      <c r="E324" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F324" s="59" t="s">
+      <c r="F324" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G324" s="61" t="s">
+      <c r="G324" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H324" s="62" t="s">
+      <c r="H324" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I324" s="55" t="s">
@@ -16572,7 +16572,7 @@
       <c r="J324" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K324" s="60" t="s">
+      <c r="K324" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -16581,13 +16581,13 @@
       <c r="B325" s="56"/>
       <c r="C325" s="56"/>
       <c r="D325" s="58"/>
-      <c r="E325" s="63"/>
+      <c r="E325" s="60"/>
       <c r="F325" s="56"/>
       <c r="G325" s="58"/>
-      <c r="H325" s="63"/>
+      <c r="H325" s="60"/>
       <c r="I325" s="56"/>
       <c r="J325" s="56"/>
-      <c r="K325" s="60"/>
+      <c r="K325" s="64"/>
     </row>
     <row r="326" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A326" s="7">
@@ -16800,11 +16800,11 @@
       <c r="D337" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E337" s="64" t="s">
+      <c r="E337" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F337" s="64"/>
-      <c r="G337" s="64"/>
+      <c r="F337" s="65"/>
+      <c r="G337" s="65"/>
       <c r="J337" s="21"/>
       <c r="K337" s="22"/>
     </row>
@@ -16821,16 +16821,16 @@
       <c r="D338" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E338" s="65" t="s">
+      <c r="E338" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F338" s="59" t="s">
+      <c r="F338" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G338" s="61" t="s">
+      <c r="G338" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H338" s="62" t="s">
+      <c r="H338" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I338" s="55" t="s">
@@ -16839,7 +16839,7 @@
       <c r="J338" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K338" s="60" t="s">
+      <c r="K338" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -16848,13 +16848,13 @@
       <c r="B339" s="56"/>
       <c r="C339" s="56"/>
       <c r="D339" s="58"/>
-      <c r="E339" s="63"/>
+      <c r="E339" s="60"/>
       <c r="F339" s="56"/>
       <c r="G339" s="58"/>
-      <c r="H339" s="63"/>
+      <c r="H339" s="60"/>
       <c r="I339" s="56"/>
       <c r="J339" s="56"/>
-      <c r="K339" s="60"/>
+      <c r="K339" s="64"/>
     </row>
     <row r="340" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A340" s="7">
@@ -17059,11 +17059,11 @@
       <c r="D351" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E351" s="64" t="s">
+      <c r="E351" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F351" s="64"/>
-      <c r="G351" s="64"/>
+      <c r="F351" s="65"/>
+      <c r="G351" s="65"/>
       <c r="J351" s="21"/>
       <c r="K351" s="22"/>
     </row>
@@ -17080,16 +17080,16 @@
       <c r="D352" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E352" s="65" t="s">
+      <c r="E352" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F352" s="59" t="s">
+      <c r="F352" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G352" s="61" t="s">
+      <c r="G352" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H352" s="62" t="s">
+      <c r="H352" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I352" s="55" t="s">
@@ -17098,7 +17098,7 @@
       <c r="J352" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K352" s="60" t="s">
+      <c r="K352" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -17107,13 +17107,13 @@
       <c r="B353" s="56"/>
       <c r="C353" s="56"/>
       <c r="D353" s="58"/>
-      <c r="E353" s="63"/>
+      <c r="E353" s="60"/>
       <c r="F353" s="56"/>
       <c r="G353" s="58"/>
-      <c r="H353" s="63"/>
+      <c r="H353" s="60"/>
       <c r="I353" s="56"/>
       <c r="J353" s="56"/>
-      <c r="K353" s="60"/>
+      <c r="K353" s="64"/>
     </row>
     <row r="354" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A354" s="7">
@@ -17318,11 +17318,11 @@
       <c r="D365" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E365" s="64" t="s">
+      <c r="E365" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F365" s="64"/>
-      <c r="G365" s="64"/>
+      <c r="F365" s="65"/>
+      <c r="G365" s="65"/>
       <c r="J365" s="21"/>
       <c r="K365" s="22"/>
     </row>
@@ -17339,16 +17339,16 @@
       <c r="D366" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E366" s="65" t="s">
+      <c r="E366" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F366" s="59" t="s">
+      <c r="F366" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G366" s="61" t="s">
+      <c r="G366" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H366" s="62" t="s">
+      <c r="H366" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I366" s="55" t="s">
@@ -17357,7 +17357,7 @@
       <c r="J366" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K366" s="60" t="s">
+      <c r="K366" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -17366,13 +17366,13 @@
       <c r="B367" s="56"/>
       <c r="C367" s="56"/>
       <c r="D367" s="58"/>
-      <c r="E367" s="63"/>
+      <c r="E367" s="60"/>
       <c r="F367" s="56"/>
       <c r="G367" s="58"/>
-      <c r="H367" s="63"/>
+      <c r="H367" s="60"/>
       <c r="I367" s="56"/>
       <c r="J367" s="56"/>
-      <c r="K367" s="60"/>
+      <c r="K367" s="64"/>
     </row>
     <row r="368" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A368" s="7">
@@ -17577,11 +17577,11 @@
       <c r="D379" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E379" s="64" t="s">
+      <c r="E379" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F379" s="64"/>
-      <c r="G379" s="64"/>
+      <c r="F379" s="65"/>
+      <c r="G379" s="65"/>
       <c r="J379" s="21"/>
       <c r="K379" s="22"/>
     </row>
@@ -17598,16 +17598,16 @@
       <c r="D380" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E380" s="65" t="s">
+      <c r="E380" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F380" s="59" t="s">
+      <c r="F380" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G380" s="61" t="s">
+      <c r="G380" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H380" s="62" t="s">
+      <c r="H380" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I380" s="55" t="s">
@@ -17616,7 +17616,7 @@
       <c r="J380" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K380" s="60" t="s">
+      <c r="K380" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -17625,13 +17625,13 @@
       <c r="B381" s="56"/>
       <c r="C381" s="56"/>
       <c r="D381" s="58"/>
-      <c r="E381" s="63"/>
+      <c r="E381" s="60"/>
       <c r="F381" s="56"/>
       <c r="G381" s="58"/>
-      <c r="H381" s="63"/>
+      <c r="H381" s="60"/>
       <c r="I381" s="56"/>
       <c r="J381" s="56"/>
-      <c r="K381" s="60"/>
+      <c r="K381" s="64"/>
     </row>
     <row r="382" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A382" s="7">
@@ -17836,11 +17836,11 @@
       <c r="D393" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E393" s="64" t="s">
+      <c r="E393" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F393" s="64"/>
-      <c r="G393" s="64"/>
+      <c r="F393" s="65"/>
+      <c r="G393" s="65"/>
       <c r="J393" s="21"/>
       <c r="K393" s="22"/>
     </row>
@@ -17857,16 +17857,16 @@
       <c r="D394" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E394" s="65" t="s">
+      <c r="E394" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F394" s="59" t="s">
+      <c r="F394" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G394" s="61" t="s">
+      <c r="G394" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H394" s="62" t="s">
+      <c r="H394" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I394" s="55" t="s">
@@ -17875,7 +17875,7 @@
       <c r="J394" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K394" s="60" t="s">
+      <c r="K394" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -17884,13 +17884,13 @@
       <c r="B395" s="56"/>
       <c r="C395" s="56"/>
       <c r="D395" s="58"/>
-      <c r="E395" s="63"/>
+      <c r="E395" s="60"/>
       <c r="F395" s="56"/>
       <c r="G395" s="58"/>
-      <c r="H395" s="63"/>
+      <c r="H395" s="60"/>
       <c r="I395" s="56"/>
       <c r="J395" s="56"/>
-      <c r="K395" s="60"/>
+      <c r="K395" s="64"/>
     </row>
     <row r="396" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A396" s="7">
@@ -18095,11 +18095,11 @@
       <c r="D407" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E407" s="64" t="s">
+      <c r="E407" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F407" s="64"/>
-      <c r="G407" s="64"/>
+      <c r="F407" s="65"/>
+      <c r="G407" s="65"/>
       <c r="J407" s="21"/>
       <c r="K407" s="22"/>
     </row>
@@ -18116,16 +18116,16 @@
       <c r="D408" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E408" s="65" t="s">
+      <c r="E408" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F408" s="59" t="s">
+      <c r="F408" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G408" s="61" t="s">
+      <c r="G408" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H408" s="62" t="s">
+      <c r="H408" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I408" s="55" t="s">
@@ -18134,7 +18134,7 @@
       <c r="J408" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K408" s="60" t="s">
+      <c r="K408" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -18143,13 +18143,13 @@
       <c r="B409" s="56"/>
       <c r="C409" s="56"/>
       <c r="D409" s="58"/>
-      <c r="E409" s="63"/>
+      <c r="E409" s="60"/>
       <c r="F409" s="56"/>
       <c r="G409" s="58"/>
-      <c r="H409" s="63"/>
+      <c r="H409" s="60"/>
       <c r="I409" s="56"/>
       <c r="J409" s="56"/>
-      <c r="K409" s="60"/>
+      <c r="K409" s="64"/>
     </row>
     <row r="410" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A410" s="7">
@@ -18354,11 +18354,11 @@
       <c r="D421" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E421" s="64" t="s">
+      <c r="E421" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F421" s="64"/>
-      <c r="G421" s="64"/>
+      <c r="F421" s="65"/>
+      <c r="G421" s="65"/>
       <c r="J421" s="21"/>
       <c r="K421" s="22"/>
     </row>
@@ -18375,16 +18375,16 @@
       <c r="D422" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E422" s="65" t="s">
+      <c r="E422" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F422" s="59" t="s">
+      <c r="F422" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G422" s="61" t="s">
+      <c r="G422" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H422" s="62" t="s">
+      <c r="H422" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I422" s="55" t="s">
@@ -18393,7 +18393,7 @@
       <c r="J422" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K422" s="60" t="s">
+      <c r="K422" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -18402,13 +18402,13 @@
       <c r="B423" s="56"/>
       <c r="C423" s="56"/>
       <c r="D423" s="58"/>
-      <c r="E423" s="63"/>
+      <c r="E423" s="60"/>
       <c r="F423" s="56"/>
       <c r="G423" s="58"/>
-      <c r="H423" s="63"/>
+      <c r="H423" s="60"/>
       <c r="I423" s="56"/>
       <c r="J423" s="56"/>
-      <c r="K423" s="60"/>
+      <c r="K423" s="64"/>
     </row>
     <row r="424" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A424" s="7">
@@ -18613,11 +18613,11 @@
       <c r="D435" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E435" s="64" t="s">
+      <c r="E435" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F435" s="64"/>
-      <c r="G435" s="64"/>
+      <c r="F435" s="65"/>
+      <c r="G435" s="65"/>
       <c r="J435" s="21"/>
       <c r="K435" s="22"/>
     </row>
@@ -18634,16 +18634,16 @@
       <c r="D436" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E436" s="65" t="s">
+      <c r="E436" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F436" s="59" t="s">
+      <c r="F436" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G436" s="61" t="s">
+      <c r="G436" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H436" s="62" t="s">
+      <c r="H436" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I436" s="55" t="s">
@@ -18652,7 +18652,7 @@
       <c r="J436" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K436" s="60" t="s">
+      <c r="K436" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -18661,13 +18661,13 @@
       <c r="B437" s="56"/>
       <c r="C437" s="56"/>
       <c r="D437" s="58"/>
-      <c r="E437" s="63"/>
+      <c r="E437" s="60"/>
       <c r="F437" s="56"/>
       <c r="G437" s="58"/>
-      <c r="H437" s="63"/>
+      <c r="H437" s="60"/>
       <c r="I437" s="56"/>
       <c r="J437" s="56"/>
-      <c r="K437" s="60"/>
+      <c r="K437" s="64"/>
     </row>
     <row r="438" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A438" s="7">
@@ -18872,11 +18872,11 @@
       <c r="D449" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E449" s="64" t="s">
+      <c r="E449" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F449" s="64"/>
-      <c r="G449" s="64"/>
+      <c r="F449" s="65"/>
+      <c r="G449" s="65"/>
       <c r="J449" s="21"/>
       <c r="K449" s="22"/>
     </row>
@@ -18893,16 +18893,16 @@
       <c r="D450" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E450" s="65" t="s">
+      <c r="E450" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F450" s="59" t="s">
+      <c r="F450" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G450" s="61" t="s">
+      <c r="G450" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H450" s="62" t="s">
+      <c r="H450" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I450" s="55" t="s">
@@ -18911,7 +18911,7 @@
       <c r="J450" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K450" s="60" t="s">
+      <c r="K450" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -18920,13 +18920,13 @@
       <c r="B451" s="56"/>
       <c r="C451" s="56"/>
       <c r="D451" s="58"/>
-      <c r="E451" s="63"/>
+      <c r="E451" s="60"/>
       <c r="F451" s="56"/>
       <c r="G451" s="58"/>
-      <c r="H451" s="63"/>
+      <c r="H451" s="60"/>
       <c r="I451" s="56"/>
       <c r="J451" s="56"/>
-      <c r="K451" s="60"/>
+      <c r="K451" s="64"/>
     </row>
     <row r="452" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A452" s="7">
@@ -19131,11 +19131,11 @@
       <c r="D463" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E463" s="64" t="s">
+      <c r="E463" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F463" s="64"/>
-      <c r="G463" s="64"/>
+      <c r="F463" s="65"/>
+      <c r="G463" s="65"/>
       <c r="J463" s="21"/>
       <c r="K463" s="22"/>
     </row>
@@ -19152,16 +19152,16 @@
       <c r="D464" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E464" s="65" t="s">
+      <c r="E464" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F464" s="59" t="s">
+      <c r="F464" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G464" s="61" t="s">
+      <c r="G464" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H464" s="62" t="s">
+      <c r="H464" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I464" s="55" t="s">
@@ -19170,7 +19170,7 @@
       <c r="J464" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K464" s="60" t="s">
+      <c r="K464" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -19179,13 +19179,13 @@
       <c r="B465" s="56"/>
       <c r="C465" s="56"/>
       <c r="D465" s="58"/>
-      <c r="E465" s="63"/>
+      <c r="E465" s="60"/>
       <c r="F465" s="56"/>
       <c r="G465" s="58"/>
-      <c r="H465" s="63"/>
+      <c r="H465" s="60"/>
       <c r="I465" s="56"/>
       <c r="J465" s="56"/>
-      <c r="K465" s="60"/>
+      <c r="K465" s="64"/>
     </row>
     <row r="466" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A466" s="7">
@@ -19390,11 +19390,11 @@
       <c r="D477" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E477" s="64" t="s">
+      <c r="E477" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F477" s="64"/>
-      <c r="G477" s="64"/>
+      <c r="F477" s="65"/>
+      <c r="G477" s="65"/>
       <c r="J477" s="21"/>
       <c r="K477" s="22"/>
     </row>
@@ -19411,16 +19411,16 @@
       <c r="D478" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E478" s="65" t="s">
+      <c r="E478" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F478" s="59" t="s">
+      <c r="F478" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G478" s="61" t="s">
+      <c r="G478" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H478" s="62" t="s">
+      <c r="H478" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I478" s="55" t="s">
@@ -19429,7 +19429,7 @@
       <c r="J478" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K478" s="60" t="s">
+      <c r="K478" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -19438,13 +19438,13 @@
       <c r="B479" s="56"/>
       <c r="C479" s="56"/>
       <c r="D479" s="58"/>
-      <c r="E479" s="63"/>
+      <c r="E479" s="60"/>
       <c r="F479" s="56"/>
       <c r="G479" s="58"/>
-      <c r="H479" s="63"/>
+      <c r="H479" s="60"/>
       <c r="I479" s="56"/>
       <c r="J479" s="56"/>
-      <c r="K479" s="60"/>
+      <c r="K479" s="64"/>
     </row>
     <row r="480" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A480" s="7">
@@ -19644,15 +19644,393 @@
     </row>
   </sheetData>
   <mergeCells count="420">
-    <mergeCell ref="A478:A479"/>
-    <mergeCell ref="B478:B479"/>
-    <mergeCell ref="C478:C479"/>
-    <mergeCell ref="D478:D479"/>
-    <mergeCell ref="E478:E479"/>
-    <mergeCell ref="F478:F479"/>
-    <mergeCell ref="G478:G479"/>
-    <mergeCell ref="H478:H479"/>
-    <mergeCell ref="I478:I479"/>
+    <mergeCell ref="F268:F269"/>
+    <mergeCell ref="K240:K241"/>
+    <mergeCell ref="G268:G269"/>
+    <mergeCell ref="G254:G255"/>
+    <mergeCell ref="H240:H241"/>
+    <mergeCell ref="E267:G267"/>
+    <mergeCell ref="H268:H269"/>
+    <mergeCell ref="H254:H255"/>
+    <mergeCell ref="E240:E241"/>
+    <mergeCell ref="I268:I269"/>
+    <mergeCell ref="E254:E255"/>
+    <mergeCell ref="K254:K255"/>
+    <mergeCell ref="I254:I255"/>
+    <mergeCell ref="E268:E269"/>
+    <mergeCell ref="F254:F255"/>
+    <mergeCell ref="K268:K269"/>
+    <mergeCell ref="E253:G253"/>
+    <mergeCell ref="H226:H227"/>
+    <mergeCell ref="H212:H213"/>
+    <mergeCell ref="J114:J115"/>
+    <mergeCell ref="H100:H101"/>
+    <mergeCell ref="H184:H185"/>
+    <mergeCell ref="E198:E199"/>
+    <mergeCell ref="J184:J185"/>
+    <mergeCell ref="J142:J143"/>
+    <mergeCell ref="G170:G171"/>
+    <mergeCell ref="I142:I143"/>
+    <mergeCell ref="H156:H157"/>
+    <mergeCell ref="E211:G211"/>
+    <mergeCell ref="E212:E213"/>
+    <mergeCell ref="E183:G183"/>
+    <mergeCell ref="D212:D213"/>
+    <mergeCell ref="A254:A255"/>
+    <mergeCell ref="B254:B255"/>
+    <mergeCell ref="B268:B269"/>
+    <mergeCell ref="C254:C255"/>
+    <mergeCell ref="D254:D255"/>
+    <mergeCell ref="C268:C269"/>
+    <mergeCell ref="D268:D269"/>
+    <mergeCell ref="D240:D241"/>
+    <mergeCell ref="B226:B227"/>
+    <mergeCell ref="C226:C227"/>
+    <mergeCell ref="D226:D227"/>
+    <mergeCell ref="C240:C241"/>
+    <mergeCell ref="B240:B241"/>
+    <mergeCell ref="A198:A199"/>
+    <mergeCell ref="C142:C143"/>
+    <mergeCell ref="A156:A157"/>
+    <mergeCell ref="B170:B171"/>
+    <mergeCell ref="B184:B185"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="C198:C199"/>
+    <mergeCell ref="D170:D171"/>
+    <mergeCell ref="D184:D185"/>
+    <mergeCell ref="C156:C157"/>
+    <mergeCell ref="C128:C129"/>
+    <mergeCell ref="D114:D115"/>
+    <mergeCell ref="B198:B199"/>
+    <mergeCell ref="D198:D199"/>
+    <mergeCell ref="D156:D157"/>
+    <mergeCell ref="D128:D129"/>
+    <mergeCell ref="K142:K143"/>
+    <mergeCell ref="J156:J157"/>
+    <mergeCell ref="K156:K157"/>
+    <mergeCell ref="K128:K129"/>
+    <mergeCell ref="D142:D143"/>
+    <mergeCell ref="I128:I129"/>
+    <mergeCell ref="I156:I157"/>
+    <mergeCell ref="J128:J129"/>
+    <mergeCell ref="H142:H143"/>
+    <mergeCell ref="H128:H129"/>
+    <mergeCell ref="K184:K185"/>
+    <mergeCell ref="J170:J171"/>
+    <mergeCell ref="K170:K171"/>
+    <mergeCell ref="E184:E185"/>
+    <mergeCell ref="F184:F185"/>
+    <mergeCell ref="G184:G185"/>
+    <mergeCell ref="E170:E171"/>
+    <mergeCell ref="H170:H171"/>
+    <mergeCell ref="I170:I171"/>
+    <mergeCell ref="F170:F171"/>
+    <mergeCell ref="I184:I185"/>
+    <mergeCell ref="E155:G155"/>
+    <mergeCell ref="K86:K87"/>
+    <mergeCell ref="J86:J87"/>
+    <mergeCell ref="G86:G87"/>
+    <mergeCell ref="I212:I213"/>
+    <mergeCell ref="J212:J213"/>
+    <mergeCell ref="K212:K213"/>
+    <mergeCell ref="H86:H87"/>
+    <mergeCell ref="I86:I87"/>
+    <mergeCell ref="F212:F213"/>
+    <mergeCell ref="I100:I101"/>
+    <mergeCell ref="E197:G197"/>
+    <mergeCell ref="F198:F199"/>
+    <mergeCell ref="G198:G199"/>
+    <mergeCell ref="H198:H199"/>
+    <mergeCell ref="G212:G213"/>
+    <mergeCell ref="K100:K101"/>
+    <mergeCell ref="K114:K115"/>
+    <mergeCell ref="B156:B157"/>
+    <mergeCell ref="B114:B115"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="A184:A185"/>
+    <mergeCell ref="A114:A115"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="B128:B129"/>
+    <mergeCell ref="A142:A143"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="C170:C171"/>
+    <mergeCell ref="C184:C185"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="E85:G85"/>
+    <mergeCell ref="E86:E87"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="E57:G57"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="E71:G71"/>
+    <mergeCell ref="F72:F73"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="G72:G73"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="K72:K73"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="J72:J73"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="K30:K31"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="H72:H73"/>
+    <mergeCell ref="I72:I73"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="D86:D87"/>
+    <mergeCell ref="F114:F115"/>
+    <mergeCell ref="C100:C101"/>
+    <mergeCell ref="D100:D101"/>
+    <mergeCell ref="E100:E101"/>
+    <mergeCell ref="F100:F101"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="G100:G101"/>
+    <mergeCell ref="E114:E115"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="E281:G281"/>
+    <mergeCell ref="E282:E283"/>
+    <mergeCell ref="F282:F283"/>
+    <mergeCell ref="G282:G283"/>
+    <mergeCell ref="I282:I283"/>
+    <mergeCell ref="J100:J101"/>
+    <mergeCell ref="I114:I115"/>
+    <mergeCell ref="H114:H115"/>
+    <mergeCell ref="F86:F87"/>
+    <mergeCell ref="E169:G169"/>
+    <mergeCell ref="E99:G99"/>
+    <mergeCell ref="G114:G115"/>
+    <mergeCell ref="E127:G127"/>
+    <mergeCell ref="E128:E129"/>
+    <mergeCell ref="F128:F129"/>
+    <mergeCell ref="E113:G113"/>
+    <mergeCell ref="G128:G129"/>
+    <mergeCell ref="G156:G157"/>
+    <mergeCell ref="E141:G141"/>
+    <mergeCell ref="E142:E143"/>
+    <mergeCell ref="F142:F143"/>
+    <mergeCell ref="G142:G143"/>
+    <mergeCell ref="F156:F157"/>
+    <mergeCell ref="E156:E157"/>
+    <mergeCell ref="E225:G225"/>
+    <mergeCell ref="G226:G227"/>
+    <mergeCell ref="E226:E227"/>
+    <mergeCell ref="E239:G239"/>
+    <mergeCell ref="A282:A283"/>
+    <mergeCell ref="B282:B283"/>
+    <mergeCell ref="C282:C283"/>
+    <mergeCell ref="D282:D283"/>
+    <mergeCell ref="K198:K199"/>
+    <mergeCell ref="I198:I199"/>
+    <mergeCell ref="J198:J199"/>
+    <mergeCell ref="J268:J269"/>
+    <mergeCell ref="J254:J255"/>
+    <mergeCell ref="K226:K227"/>
+    <mergeCell ref="J226:J227"/>
+    <mergeCell ref="J240:J241"/>
+    <mergeCell ref="I226:I227"/>
+    <mergeCell ref="I240:I241"/>
+    <mergeCell ref="F226:F227"/>
+    <mergeCell ref="G240:G241"/>
+    <mergeCell ref="F240:F241"/>
+    <mergeCell ref="A212:A213"/>
+    <mergeCell ref="B212:B213"/>
+    <mergeCell ref="C212:C213"/>
+    <mergeCell ref="A226:A227"/>
+    <mergeCell ref="A240:A241"/>
+    <mergeCell ref="A268:A269"/>
+    <mergeCell ref="J310:J311"/>
+    <mergeCell ref="K310:K311"/>
+    <mergeCell ref="J296:J297"/>
+    <mergeCell ref="K296:K297"/>
+    <mergeCell ref="J282:J283"/>
+    <mergeCell ref="K282:K283"/>
+    <mergeCell ref="D296:D297"/>
+    <mergeCell ref="E296:E297"/>
+    <mergeCell ref="F296:F297"/>
+    <mergeCell ref="H310:H311"/>
+    <mergeCell ref="I310:I311"/>
+    <mergeCell ref="A296:A297"/>
+    <mergeCell ref="A310:A311"/>
+    <mergeCell ref="B310:B311"/>
+    <mergeCell ref="B296:B297"/>
+    <mergeCell ref="C296:C297"/>
+    <mergeCell ref="I296:I297"/>
+    <mergeCell ref="E295:G295"/>
+    <mergeCell ref="G296:G297"/>
+    <mergeCell ref="H282:H283"/>
+    <mergeCell ref="H296:H297"/>
+    <mergeCell ref="E323:G323"/>
+    <mergeCell ref="E324:E325"/>
+    <mergeCell ref="E309:G309"/>
+    <mergeCell ref="F310:F311"/>
+    <mergeCell ref="G310:G311"/>
+    <mergeCell ref="A324:A325"/>
+    <mergeCell ref="B324:B325"/>
+    <mergeCell ref="C324:C325"/>
+    <mergeCell ref="D324:D325"/>
+    <mergeCell ref="C310:C311"/>
+    <mergeCell ref="D310:D311"/>
+    <mergeCell ref="E310:E311"/>
+    <mergeCell ref="F324:F325"/>
+    <mergeCell ref="E337:G337"/>
+    <mergeCell ref="J324:J325"/>
+    <mergeCell ref="K324:K325"/>
+    <mergeCell ref="H324:H325"/>
+    <mergeCell ref="I324:I325"/>
+    <mergeCell ref="F338:F339"/>
+    <mergeCell ref="G338:G339"/>
+    <mergeCell ref="E338:E339"/>
+    <mergeCell ref="I338:I339"/>
+    <mergeCell ref="G324:G325"/>
+    <mergeCell ref="J366:J367"/>
+    <mergeCell ref="K366:K367"/>
+    <mergeCell ref="H352:H353"/>
+    <mergeCell ref="I352:I353"/>
+    <mergeCell ref="J352:J353"/>
+    <mergeCell ref="K352:K353"/>
+    <mergeCell ref="E365:G365"/>
+    <mergeCell ref="A338:A339"/>
+    <mergeCell ref="B338:B339"/>
+    <mergeCell ref="C338:C339"/>
+    <mergeCell ref="D338:D339"/>
+    <mergeCell ref="E351:G351"/>
+    <mergeCell ref="A352:A353"/>
+    <mergeCell ref="B352:B353"/>
+    <mergeCell ref="C352:C353"/>
+    <mergeCell ref="D352:D353"/>
+    <mergeCell ref="E352:E353"/>
+    <mergeCell ref="F352:F353"/>
+    <mergeCell ref="G352:G353"/>
+    <mergeCell ref="J338:J339"/>
+    <mergeCell ref="K338:K339"/>
+    <mergeCell ref="H338:H339"/>
+    <mergeCell ref="J394:J395"/>
+    <mergeCell ref="K394:K395"/>
+    <mergeCell ref="H380:H381"/>
+    <mergeCell ref="I380:I381"/>
+    <mergeCell ref="J380:J381"/>
+    <mergeCell ref="K380:K381"/>
+    <mergeCell ref="E393:G393"/>
+    <mergeCell ref="A366:A367"/>
+    <mergeCell ref="B366:B367"/>
+    <mergeCell ref="C366:C367"/>
+    <mergeCell ref="D366:D367"/>
+    <mergeCell ref="E366:E367"/>
+    <mergeCell ref="F366:F367"/>
+    <mergeCell ref="G366:G367"/>
+    <mergeCell ref="E379:G379"/>
+    <mergeCell ref="A380:A381"/>
+    <mergeCell ref="B380:B381"/>
+    <mergeCell ref="C380:C381"/>
+    <mergeCell ref="D380:D381"/>
+    <mergeCell ref="E380:E381"/>
+    <mergeCell ref="F380:F381"/>
+    <mergeCell ref="G380:G381"/>
+    <mergeCell ref="H366:H367"/>
+    <mergeCell ref="I366:I367"/>
+    <mergeCell ref="J422:J423"/>
+    <mergeCell ref="K422:K423"/>
+    <mergeCell ref="H408:H409"/>
+    <mergeCell ref="I408:I409"/>
+    <mergeCell ref="J408:J409"/>
+    <mergeCell ref="K408:K409"/>
+    <mergeCell ref="E421:G421"/>
+    <mergeCell ref="A394:A395"/>
+    <mergeCell ref="B394:B395"/>
+    <mergeCell ref="C394:C395"/>
+    <mergeCell ref="D394:D395"/>
+    <mergeCell ref="E394:E395"/>
+    <mergeCell ref="F394:F395"/>
+    <mergeCell ref="G394:G395"/>
+    <mergeCell ref="E407:G407"/>
+    <mergeCell ref="A408:A409"/>
+    <mergeCell ref="B408:B409"/>
+    <mergeCell ref="C408:C409"/>
+    <mergeCell ref="D408:D409"/>
+    <mergeCell ref="E408:E409"/>
+    <mergeCell ref="F408:F409"/>
+    <mergeCell ref="G408:G409"/>
+    <mergeCell ref="H394:H395"/>
+    <mergeCell ref="I394:I395"/>
+    <mergeCell ref="J450:J451"/>
+    <mergeCell ref="K450:K451"/>
+    <mergeCell ref="H436:H437"/>
+    <mergeCell ref="I436:I437"/>
+    <mergeCell ref="J436:J437"/>
+    <mergeCell ref="K436:K437"/>
+    <mergeCell ref="E449:G449"/>
+    <mergeCell ref="A422:A423"/>
+    <mergeCell ref="B422:B423"/>
+    <mergeCell ref="C422:C423"/>
+    <mergeCell ref="D422:D423"/>
+    <mergeCell ref="E422:E423"/>
+    <mergeCell ref="F422:F423"/>
+    <mergeCell ref="G422:G423"/>
+    <mergeCell ref="E435:G435"/>
+    <mergeCell ref="A436:A437"/>
+    <mergeCell ref="B436:B437"/>
+    <mergeCell ref="C436:C437"/>
+    <mergeCell ref="D436:D437"/>
+    <mergeCell ref="E436:E437"/>
+    <mergeCell ref="F436:F437"/>
+    <mergeCell ref="G436:G437"/>
+    <mergeCell ref="H422:H423"/>
+    <mergeCell ref="I422:I423"/>
     <mergeCell ref="J478:J479"/>
     <mergeCell ref="K478:K479"/>
     <mergeCell ref="H464:H465"/>
@@ -19677,393 +20055,15 @@
     <mergeCell ref="G464:G465"/>
     <mergeCell ref="H450:H451"/>
     <mergeCell ref="I450:I451"/>
-    <mergeCell ref="J450:J451"/>
-    <mergeCell ref="K450:K451"/>
-    <mergeCell ref="H436:H437"/>
-    <mergeCell ref="I436:I437"/>
-    <mergeCell ref="J436:J437"/>
-    <mergeCell ref="K436:K437"/>
-    <mergeCell ref="E449:G449"/>
-    <mergeCell ref="A422:A423"/>
-    <mergeCell ref="B422:B423"/>
-    <mergeCell ref="C422:C423"/>
-    <mergeCell ref="D422:D423"/>
-    <mergeCell ref="E422:E423"/>
-    <mergeCell ref="F422:F423"/>
-    <mergeCell ref="G422:G423"/>
-    <mergeCell ref="E435:G435"/>
-    <mergeCell ref="A436:A437"/>
-    <mergeCell ref="B436:B437"/>
-    <mergeCell ref="C436:C437"/>
-    <mergeCell ref="D436:D437"/>
-    <mergeCell ref="E436:E437"/>
-    <mergeCell ref="F436:F437"/>
-    <mergeCell ref="G436:G437"/>
-    <mergeCell ref="H422:H423"/>
-    <mergeCell ref="I422:I423"/>
-    <mergeCell ref="J422:J423"/>
-    <mergeCell ref="K422:K423"/>
-    <mergeCell ref="H408:H409"/>
-    <mergeCell ref="I408:I409"/>
-    <mergeCell ref="J408:J409"/>
-    <mergeCell ref="K408:K409"/>
-    <mergeCell ref="E421:G421"/>
-    <mergeCell ref="A394:A395"/>
-    <mergeCell ref="B394:B395"/>
-    <mergeCell ref="C394:C395"/>
-    <mergeCell ref="D394:D395"/>
-    <mergeCell ref="E394:E395"/>
-    <mergeCell ref="F394:F395"/>
-    <mergeCell ref="G394:G395"/>
-    <mergeCell ref="E407:G407"/>
-    <mergeCell ref="A408:A409"/>
-    <mergeCell ref="B408:B409"/>
-    <mergeCell ref="C408:C409"/>
-    <mergeCell ref="D408:D409"/>
-    <mergeCell ref="E408:E409"/>
-    <mergeCell ref="F408:F409"/>
-    <mergeCell ref="G408:G409"/>
-    <mergeCell ref="H394:H395"/>
-    <mergeCell ref="I394:I395"/>
-    <mergeCell ref="J394:J395"/>
-    <mergeCell ref="K394:K395"/>
-    <mergeCell ref="H380:H381"/>
-    <mergeCell ref="I380:I381"/>
-    <mergeCell ref="J380:J381"/>
-    <mergeCell ref="K380:K381"/>
-    <mergeCell ref="E393:G393"/>
-    <mergeCell ref="A366:A367"/>
-    <mergeCell ref="B366:B367"/>
-    <mergeCell ref="C366:C367"/>
-    <mergeCell ref="D366:D367"/>
-    <mergeCell ref="E366:E367"/>
-    <mergeCell ref="F366:F367"/>
-    <mergeCell ref="G366:G367"/>
-    <mergeCell ref="E379:G379"/>
-    <mergeCell ref="A380:A381"/>
-    <mergeCell ref="B380:B381"/>
-    <mergeCell ref="C380:C381"/>
-    <mergeCell ref="D380:D381"/>
-    <mergeCell ref="E380:E381"/>
-    <mergeCell ref="F380:F381"/>
-    <mergeCell ref="G380:G381"/>
-    <mergeCell ref="H366:H367"/>
-    <mergeCell ref="I366:I367"/>
-    <mergeCell ref="J366:J367"/>
-    <mergeCell ref="K366:K367"/>
-    <mergeCell ref="H352:H353"/>
-    <mergeCell ref="I352:I353"/>
-    <mergeCell ref="J352:J353"/>
-    <mergeCell ref="K352:K353"/>
-    <mergeCell ref="E365:G365"/>
-    <mergeCell ref="A338:A339"/>
-    <mergeCell ref="B338:B339"/>
-    <mergeCell ref="C338:C339"/>
-    <mergeCell ref="D338:D339"/>
-    <mergeCell ref="E351:G351"/>
-    <mergeCell ref="A352:A353"/>
-    <mergeCell ref="B352:B353"/>
-    <mergeCell ref="C352:C353"/>
-    <mergeCell ref="D352:D353"/>
-    <mergeCell ref="E352:E353"/>
-    <mergeCell ref="F352:F353"/>
-    <mergeCell ref="G352:G353"/>
-    <mergeCell ref="J338:J339"/>
-    <mergeCell ref="K338:K339"/>
-    <mergeCell ref="H338:H339"/>
-    <mergeCell ref="E337:G337"/>
-    <mergeCell ref="J324:J325"/>
-    <mergeCell ref="K324:K325"/>
-    <mergeCell ref="H324:H325"/>
-    <mergeCell ref="I324:I325"/>
-    <mergeCell ref="F338:F339"/>
-    <mergeCell ref="G338:G339"/>
-    <mergeCell ref="E338:E339"/>
-    <mergeCell ref="I338:I339"/>
-    <mergeCell ref="G324:G325"/>
-    <mergeCell ref="E323:G323"/>
-    <mergeCell ref="E324:E325"/>
-    <mergeCell ref="E309:G309"/>
-    <mergeCell ref="F310:F311"/>
-    <mergeCell ref="G310:G311"/>
-    <mergeCell ref="A324:A325"/>
-    <mergeCell ref="B324:B325"/>
-    <mergeCell ref="C324:C325"/>
-    <mergeCell ref="D324:D325"/>
-    <mergeCell ref="C310:C311"/>
-    <mergeCell ref="D310:D311"/>
-    <mergeCell ref="E310:E311"/>
-    <mergeCell ref="F324:F325"/>
-    <mergeCell ref="A226:A227"/>
-    <mergeCell ref="A240:A241"/>
-    <mergeCell ref="A268:A269"/>
-    <mergeCell ref="J310:J311"/>
-    <mergeCell ref="K310:K311"/>
-    <mergeCell ref="J296:J297"/>
-    <mergeCell ref="K296:K297"/>
-    <mergeCell ref="J282:J283"/>
-    <mergeCell ref="K282:K283"/>
-    <mergeCell ref="D296:D297"/>
-    <mergeCell ref="E296:E297"/>
-    <mergeCell ref="F296:F297"/>
-    <mergeCell ref="H310:H311"/>
-    <mergeCell ref="I310:I311"/>
-    <mergeCell ref="A296:A297"/>
-    <mergeCell ref="A310:A311"/>
-    <mergeCell ref="B310:B311"/>
-    <mergeCell ref="B296:B297"/>
-    <mergeCell ref="C296:C297"/>
-    <mergeCell ref="E225:G225"/>
-    <mergeCell ref="G226:G227"/>
-    <mergeCell ref="E226:E227"/>
-    <mergeCell ref="E239:G239"/>
-    <mergeCell ref="A282:A283"/>
-    <mergeCell ref="B282:B283"/>
-    <mergeCell ref="C282:C283"/>
-    <mergeCell ref="D282:D283"/>
-    <mergeCell ref="K198:K199"/>
-    <mergeCell ref="I198:I199"/>
-    <mergeCell ref="J198:J199"/>
-    <mergeCell ref="J268:J269"/>
-    <mergeCell ref="J254:J255"/>
-    <mergeCell ref="K226:K227"/>
-    <mergeCell ref="J226:J227"/>
-    <mergeCell ref="J240:J241"/>
-    <mergeCell ref="I226:I227"/>
-    <mergeCell ref="I240:I241"/>
-    <mergeCell ref="F226:F227"/>
-    <mergeCell ref="G240:G241"/>
-    <mergeCell ref="F240:F241"/>
-    <mergeCell ref="A212:A213"/>
-    <mergeCell ref="B212:B213"/>
-    <mergeCell ref="C212:C213"/>
-    <mergeCell ref="I296:I297"/>
-    <mergeCell ref="E295:G295"/>
-    <mergeCell ref="G296:G297"/>
-    <mergeCell ref="H282:H283"/>
-    <mergeCell ref="H296:H297"/>
-    <mergeCell ref="E281:G281"/>
-    <mergeCell ref="E282:E283"/>
-    <mergeCell ref="F282:F283"/>
-    <mergeCell ref="G282:G283"/>
-    <mergeCell ref="I282:I283"/>
-    <mergeCell ref="J100:J101"/>
-    <mergeCell ref="I114:I115"/>
-    <mergeCell ref="H114:H115"/>
-    <mergeCell ref="F86:F87"/>
-    <mergeCell ref="D86:D87"/>
-    <mergeCell ref="F114:F115"/>
-    <mergeCell ref="C100:C101"/>
-    <mergeCell ref="D100:D101"/>
-    <mergeCell ref="E100:E101"/>
-    <mergeCell ref="F100:F101"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="G100:G101"/>
-    <mergeCell ref="E114:E115"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="K72:K73"/>
-    <mergeCell ref="K44:K45"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="J72:J73"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="K30:K31"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="H72:H73"/>
-    <mergeCell ref="I72:I73"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="E57:G57"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="E71:G71"/>
-    <mergeCell ref="F72:F73"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="G72:G73"/>
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="E44:E45"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="B156:B157"/>
-    <mergeCell ref="B114:B115"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="A184:A185"/>
-    <mergeCell ref="A114:A115"/>
-    <mergeCell ref="A100:A101"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="B128:B129"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="C170:C171"/>
-    <mergeCell ref="C184:C185"/>
-    <mergeCell ref="E85:G85"/>
-    <mergeCell ref="E86:E87"/>
-    <mergeCell ref="E169:G169"/>
-    <mergeCell ref="E99:G99"/>
-    <mergeCell ref="G114:G115"/>
-    <mergeCell ref="E127:G127"/>
-    <mergeCell ref="E128:E129"/>
-    <mergeCell ref="F128:F129"/>
-    <mergeCell ref="E113:G113"/>
-    <mergeCell ref="G128:G129"/>
-    <mergeCell ref="G156:G157"/>
-    <mergeCell ref="E141:G141"/>
-    <mergeCell ref="E142:E143"/>
-    <mergeCell ref="F142:F143"/>
-    <mergeCell ref="G142:G143"/>
-    <mergeCell ref="F156:F157"/>
-    <mergeCell ref="E156:E157"/>
-    <mergeCell ref="E155:G155"/>
-    <mergeCell ref="K86:K87"/>
-    <mergeCell ref="J86:J87"/>
-    <mergeCell ref="G86:G87"/>
-    <mergeCell ref="I212:I213"/>
-    <mergeCell ref="J212:J213"/>
-    <mergeCell ref="K212:K213"/>
-    <mergeCell ref="H86:H87"/>
-    <mergeCell ref="I86:I87"/>
-    <mergeCell ref="D198:D199"/>
-    <mergeCell ref="D156:D157"/>
-    <mergeCell ref="D128:D129"/>
-    <mergeCell ref="K142:K143"/>
-    <mergeCell ref="J156:J157"/>
-    <mergeCell ref="K156:K157"/>
-    <mergeCell ref="K128:K129"/>
-    <mergeCell ref="D142:D143"/>
-    <mergeCell ref="I128:I129"/>
-    <mergeCell ref="I156:I157"/>
-    <mergeCell ref="J128:J129"/>
-    <mergeCell ref="H142:H143"/>
-    <mergeCell ref="H128:H129"/>
-    <mergeCell ref="K184:K185"/>
-    <mergeCell ref="J170:J171"/>
-    <mergeCell ref="K170:K171"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="A198:A199"/>
-    <mergeCell ref="C142:C143"/>
-    <mergeCell ref="A156:A157"/>
-    <mergeCell ref="B170:B171"/>
-    <mergeCell ref="B184:B185"/>
-    <mergeCell ref="B100:B101"/>
-    <mergeCell ref="C198:C199"/>
-    <mergeCell ref="D170:D171"/>
-    <mergeCell ref="D184:D185"/>
-    <mergeCell ref="E184:E185"/>
-    <mergeCell ref="F184:F185"/>
-    <mergeCell ref="G184:G185"/>
-    <mergeCell ref="F212:F213"/>
-    <mergeCell ref="I100:I101"/>
-    <mergeCell ref="C156:C157"/>
-    <mergeCell ref="C128:C129"/>
-    <mergeCell ref="D114:D115"/>
-    <mergeCell ref="B198:B199"/>
-    <mergeCell ref="E170:E171"/>
-    <mergeCell ref="H170:H171"/>
-    <mergeCell ref="I170:I171"/>
-    <mergeCell ref="F170:F171"/>
-    <mergeCell ref="I184:I185"/>
-    <mergeCell ref="E197:G197"/>
-    <mergeCell ref="F198:F199"/>
-    <mergeCell ref="G198:G199"/>
-    <mergeCell ref="H198:H199"/>
-    <mergeCell ref="G212:G213"/>
-    <mergeCell ref="D212:D213"/>
-    <mergeCell ref="A254:A255"/>
-    <mergeCell ref="B254:B255"/>
-    <mergeCell ref="B268:B269"/>
-    <mergeCell ref="C254:C255"/>
-    <mergeCell ref="D254:D255"/>
-    <mergeCell ref="C268:C269"/>
-    <mergeCell ref="D268:D269"/>
-    <mergeCell ref="D240:D241"/>
-    <mergeCell ref="K100:K101"/>
-    <mergeCell ref="K114:K115"/>
-    <mergeCell ref="H226:H227"/>
-    <mergeCell ref="H212:H213"/>
-    <mergeCell ref="J114:J115"/>
-    <mergeCell ref="H100:H101"/>
-    <mergeCell ref="H184:H185"/>
-    <mergeCell ref="E198:E199"/>
-    <mergeCell ref="J184:J185"/>
-    <mergeCell ref="J142:J143"/>
-    <mergeCell ref="G170:G171"/>
-    <mergeCell ref="I142:I143"/>
-    <mergeCell ref="H156:H157"/>
-    <mergeCell ref="E211:G211"/>
-    <mergeCell ref="E212:E213"/>
-    <mergeCell ref="E183:G183"/>
-    <mergeCell ref="B226:B227"/>
-    <mergeCell ref="C226:C227"/>
-    <mergeCell ref="D226:D227"/>
-    <mergeCell ref="C240:C241"/>
-    <mergeCell ref="F268:F269"/>
-    <mergeCell ref="K240:K241"/>
-    <mergeCell ref="G268:G269"/>
-    <mergeCell ref="G254:G255"/>
-    <mergeCell ref="H240:H241"/>
-    <mergeCell ref="E267:G267"/>
-    <mergeCell ref="H268:H269"/>
-    <mergeCell ref="H254:H255"/>
-    <mergeCell ref="E240:E241"/>
-    <mergeCell ref="I268:I269"/>
-    <mergeCell ref="E254:E255"/>
-    <mergeCell ref="K254:K255"/>
-    <mergeCell ref="I254:I255"/>
-    <mergeCell ref="E268:E269"/>
-    <mergeCell ref="F254:F255"/>
-    <mergeCell ref="K268:K269"/>
-    <mergeCell ref="E253:G253"/>
-    <mergeCell ref="B240:B241"/>
+    <mergeCell ref="A478:A479"/>
+    <mergeCell ref="B478:B479"/>
+    <mergeCell ref="C478:C479"/>
+    <mergeCell ref="D478:D479"/>
+    <mergeCell ref="E478:E479"/>
+    <mergeCell ref="F478:F479"/>
+    <mergeCell ref="G478:G479"/>
+    <mergeCell ref="H478:H479"/>
+    <mergeCell ref="I478:I479"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations xWindow="401" yWindow="629" count="6">
@@ -20112,11 +20112,11 @@
       <c r="D1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="64" t="s">
+      <c r="E1" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
       <c r="J1" s="21"/>
       <c r="K1" s="22"/>
     </row>
@@ -20133,16 +20133,16 @@
       <c r="D2" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="65" t="s">
+      <c r="E2" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="59" t="s">
+      <c r="F2" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="61" t="s">
+      <c r="G2" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="62" t="s">
+      <c r="H2" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="55" t="s">
@@ -20151,7 +20151,7 @@
       <c r="J2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="60" t="s">
+      <c r="K2" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -20160,13 +20160,13 @@
       <c r="B3" s="56"/>
       <c r="C3" s="56"/>
       <c r="D3" s="58"/>
-      <c r="E3" s="63"/>
+      <c r="E3" s="60"/>
       <c r="F3" s="56"/>
       <c r="G3" s="58"/>
-      <c r="H3" s="63"/>
+      <c r="H3" s="60"/>
       <c r="I3" s="56"/>
       <c r="J3" s="56"/>
-      <c r="K3" s="60"/>
+      <c r="K3" s="64"/>
     </row>
     <row r="4" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="7"/>
@@ -20351,11 +20351,11 @@
       <c r="D15" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="64" t="s">
+      <c r="E15" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="65"/>
       <c r="J15" s="21"/>
       <c r="K15" s="22"/>
     </row>
@@ -20372,16 +20372,16 @@
       <c r="D16" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="65" t="s">
+      <c r="E16" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="59" t="s">
+      <c r="F16" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="61" t="s">
+      <c r="G16" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="62" t="s">
+      <c r="H16" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I16" s="55" t="s">
@@ -20390,7 +20390,7 @@
       <c r="J16" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="60" t="s">
+      <c r="K16" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -20399,13 +20399,13 @@
       <c r="B17" s="56"/>
       <c r="C17" s="56"/>
       <c r="D17" s="58"/>
-      <c r="E17" s="63"/>
+      <c r="E17" s="60"/>
       <c r="F17" s="56"/>
       <c r="G17" s="58"/>
-      <c r="H17" s="63"/>
+      <c r="H17" s="60"/>
       <c r="I17" s="56"/>
       <c r="J17" s="56"/>
-      <c r="K17" s="60"/>
+      <c r="K17" s="64"/>
     </row>
     <row r="18" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7"/>
@@ -20590,11 +20590,11 @@
       <c r="D29" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="64" t="s">
+      <c r="E29" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="64"/>
-      <c r="G29" s="64"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="65"/>
       <c r="J29" s="21"/>
       <c r="K29" s="22"/>
     </row>
@@ -20611,16 +20611,16 @@
       <c r="D30" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E30" s="65" t="s">
+      <c r="E30" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F30" s="59" t="s">
+      <c r="F30" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G30" s="61" t="s">
+      <c r="G30" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="62" t="s">
+      <c r="H30" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I30" s="55" t="s">
@@ -20629,7 +20629,7 @@
       <c r="J30" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K30" s="60" t="s">
+      <c r="K30" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -20638,13 +20638,13 @@
       <c r="B31" s="56"/>
       <c r="C31" s="56"/>
       <c r="D31" s="58"/>
-      <c r="E31" s="63"/>
+      <c r="E31" s="60"/>
       <c r="F31" s="56"/>
       <c r="G31" s="58"/>
-      <c r="H31" s="63"/>
+      <c r="H31" s="60"/>
       <c r="I31" s="56"/>
       <c r="J31" s="56"/>
-      <c r="K31" s="60"/>
+      <c r="K31" s="64"/>
     </row>
     <row r="32" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7"/>
@@ -20829,11 +20829,11 @@
       <c r="D43" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="64" t="s">
+      <c r="E43" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="64"/>
-      <c r="G43" s="64"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
       <c r="J43" s="21"/>
       <c r="K43" s="22"/>
     </row>
@@ -20850,16 +20850,16 @@
       <c r="D44" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="65" t="s">
+      <c r="E44" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="59" t="s">
+      <c r="F44" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G44" s="61" t="s">
+      <c r="G44" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H44" s="62" t="s">
+      <c r="H44" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I44" s="55" t="s">
@@ -20868,7 +20868,7 @@
       <c r="J44" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="60" t="s">
+      <c r="K44" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -20877,13 +20877,13 @@
       <c r="B45" s="56"/>
       <c r="C45" s="56"/>
       <c r="D45" s="58"/>
-      <c r="E45" s="63"/>
+      <c r="E45" s="60"/>
       <c r="F45" s="56"/>
       <c r="G45" s="58"/>
-      <c r="H45" s="63"/>
+      <c r="H45" s="60"/>
       <c r="I45" s="56"/>
       <c r="J45" s="56"/>
-      <c r="K45" s="60"/>
+      <c r="K45" s="64"/>
     </row>
     <row r="46" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7"/>
@@ -21068,11 +21068,11 @@
       <c r="D57" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E57" s="64" t="s">
+      <c r="E57" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="64"/>
-      <c r="G57" s="64"/>
+      <c r="F57" s="65"/>
+      <c r="G57" s="65"/>
       <c r="J57" s="21"/>
       <c r="K57" s="22"/>
     </row>
@@ -21089,16 +21089,16 @@
       <c r="D58" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="65" t="s">
+      <c r="E58" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F58" s="59" t="s">
+      <c r="F58" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G58" s="61" t="s">
+      <c r="G58" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H58" s="62" t="s">
+      <c r="H58" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I58" s="55" t="s">
@@ -21107,7 +21107,7 @@
       <c r="J58" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K58" s="60" t="s">
+      <c r="K58" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -21116,13 +21116,13 @@
       <c r="B59" s="56"/>
       <c r="C59" s="56"/>
       <c r="D59" s="58"/>
-      <c r="E59" s="63"/>
+      <c r="E59" s="60"/>
       <c r="F59" s="56"/>
       <c r="G59" s="58"/>
-      <c r="H59" s="63"/>
+      <c r="H59" s="60"/>
       <c r="I59" s="56"/>
       <c r="J59" s="56"/>
-      <c r="K59" s="60"/>
+      <c r="K59" s="64"/>
     </row>
     <row r="60" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="7"/>
@@ -21309,29 +21309,27 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="K44:K45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="E16:E17"/>
     <mergeCell ref="E57:G57"/>
     <mergeCell ref="J16:J17"/>
     <mergeCell ref="K16:K17"/>
@@ -21348,27 +21346,29 @@
     <mergeCell ref="H16:H17"/>
     <mergeCell ref="E43:G43"/>
     <mergeCell ref="G30:G31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="6">
@@ -21416,11 +21416,11 @@
       <c r="D1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="64" t="s">
+      <c r="E1" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
       <c r="J1" s="21"/>
       <c r="K1" s="22"/>
     </row>
@@ -21437,16 +21437,16 @@
       <c r="D2" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="65" t="s">
+      <c r="E2" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="59" t="s">
+      <c r="F2" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="61" t="s">
+      <c r="G2" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="62" t="s">
+      <c r="H2" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="55" t="s">
@@ -21455,7 +21455,7 @@
       <c r="J2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="60" t="s">
+      <c r="K2" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -21464,13 +21464,13 @@
       <c r="B3" s="56"/>
       <c r="C3" s="56"/>
       <c r="D3" s="58"/>
-      <c r="E3" s="63"/>
+      <c r="E3" s="60"/>
       <c r="F3" s="56"/>
       <c r="G3" s="58"/>
-      <c r="H3" s="63"/>
+      <c r="H3" s="60"/>
       <c r="I3" s="56"/>
       <c r="J3" s="56"/>
-      <c r="K3" s="60"/>
+      <c r="K3" s="64"/>
     </row>
     <row r="4" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="7"/>
@@ -21655,11 +21655,11 @@
       <c r="D15" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="64" t="s">
+      <c r="E15" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="65"/>
       <c r="J15" s="21"/>
       <c r="K15" s="22"/>
     </row>
@@ -21676,16 +21676,16 @@
       <c r="D16" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="65" t="s">
+      <c r="E16" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="59" t="s">
+      <c r="F16" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="61" t="s">
+      <c r="G16" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="62" t="s">
+      <c r="H16" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I16" s="55" t="s">
@@ -21694,7 +21694,7 @@
       <c r="J16" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="60" t="s">
+      <c r="K16" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -21703,13 +21703,13 @@
       <c r="B17" s="56"/>
       <c r="C17" s="56"/>
       <c r="D17" s="58"/>
-      <c r="E17" s="63"/>
+      <c r="E17" s="60"/>
       <c r="F17" s="56"/>
       <c r="G17" s="58"/>
-      <c r="H17" s="63"/>
+      <c r="H17" s="60"/>
       <c r="I17" s="56"/>
       <c r="J17" s="56"/>
-      <c r="K17" s="60"/>
+      <c r="K17" s="64"/>
     </row>
     <row r="18" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7"/>
@@ -21894,11 +21894,11 @@
       <c r="D29" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="64" t="s">
+      <c r="E29" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="64"/>
-      <c r="G29" s="64"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="65"/>
       <c r="J29" s="21"/>
       <c r="K29" s="22"/>
     </row>
@@ -21915,16 +21915,16 @@
       <c r="D30" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E30" s="65" t="s">
+      <c r="E30" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F30" s="59" t="s">
+      <c r="F30" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G30" s="61" t="s">
+      <c r="G30" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="62" t="s">
+      <c r="H30" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I30" s="55" t="s">
@@ -21933,7 +21933,7 @@
       <c r="J30" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K30" s="60" t="s">
+      <c r="K30" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -21942,13 +21942,13 @@
       <c r="B31" s="56"/>
       <c r="C31" s="56"/>
       <c r="D31" s="58"/>
-      <c r="E31" s="63"/>
+      <c r="E31" s="60"/>
       <c r="F31" s="56"/>
       <c r="G31" s="58"/>
-      <c r="H31" s="63"/>
+      <c r="H31" s="60"/>
       <c r="I31" s="56"/>
       <c r="J31" s="56"/>
-      <c r="K31" s="60"/>
+      <c r="K31" s="64"/>
     </row>
     <row r="32" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7"/>
@@ -22133,11 +22133,11 @@
       <c r="D43" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="64" t="s">
+      <c r="E43" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="64"/>
-      <c r="G43" s="64"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
       <c r="J43" s="21"/>
       <c r="K43" s="22"/>
     </row>
@@ -22154,16 +22154,16 @@
       <c r="D44" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="65" t="s">
+      <c r="E44" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="59" t="s">
+      <c r="F44" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G44" s="61" t="s">
+      <c r="G44" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H44" s="62" t="s">
+      <c r="H44" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I44" s="55" t="s">
@@ -22172,7 +22172,7 @@
       <c r="J44" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="60" t="s">
+      <c r="K44" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -22181,13 +22181,13 @@
       <c r="B45" s="56"/>
       <c r="C45" s="56"/>
       <c r="D45" s="58"/>
-      <c r="E45" s="63"/>
+      <c r="E45" s="60"/>
       <c r="F45" s="56"/>
       <c r="G45" s="58"/>
-      <c r="H45" s="63"/>
+      <c r="H45" s="60"/>
       <c r="I45" s="56"/>
       <c r="J45" s="56"/>
-      <c r="K45" s="60"/>
+      <c r="K45" s="64"/>
     </row>
     <row r="46" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7"/>
@@ -22372,11 +22372,11 @@
       <c r="D57" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E57" s="64" t="s">
+      <c r="E57" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="64"/>
-      <c r="G57" s="64"/>
+      <c r="F57" s="65"/>
+      <c r="G57" s="65"/>
       <c r="J57" s="21"/>
       <c r="K57" s="22"/>
     </row>
@@ -22393,16 +22393,16 @@
       <c r="D58" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="65" t="s">
+      <c r="E58" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F58" s="59" t="s">
+      <c r="F58" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G58" s="61" t="s">
+      <c r="G58" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H58" s="62" t="s">
+      <c r="H58" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I58" s="55" t="s">
@@ -22411,7 +22411,7 @@
       <c r="J58" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K58" s="60" t="s">
+      <c r="K58" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -22420,13 +22420,13 @@
       <c r="B59" s="56"/>
       <c r="C59" s="56"/>
       <c r="D59" s="58"/>
-      <c r="E59" s="63"/>
+      <c r="E59" s="60"/>
       <c r="F59" s="56"/>
       <c r="G59" s="58"/>
-      <c r="H59" s="63"/>
+      <c r="H59" s="60"/>
       <c r="I59" s="56"/>
       <c r="J59" s="56"/>
-      <c r="K59" s="60"/>
+      <c r="K59" s="64"/>
     </row>
     <row r="60" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="7"/>
@@ -22613,29 +22613,27 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="K44:K45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="E16:E17"/>
     <mergeCell ref="E57:G57"/>
     <mergeCell ref="J16:J17"/>
     <mergeCell ref="K16:K17"/>
@@ -22652,27 +22650,29 @@
     <mergeCell ref="H16:H17"/>
     <mergeCell ref="E43:G43"/>
     <mergeCell ref="G30:G31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="6">
@@ -22720,11 +22720,11 @@
       <c r="D1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="64" t="s">
+      <c r="E1" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
       <c r="J1" s="21"/>
       <c r="K1" s="22"/>
     </row>
@@ -22741,16 +22741,16 @@
       <c r="D2" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="65" t="s">
+      <c r="E2" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="59" t="s">
+      <c r="F2" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="61" t="s">
+      <c r="G2" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="62" t="s">
+      <c r="H2" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="55" t="s">
@@ -22759,7 +22759,7 @@
       <c r="J2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="60" t="s">
+      <c r="K2" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -22768,13 +22768,13 @@
       <c r="B3" s="56"/>
       <c r="C3" s="56"/>
       <c r="D3" s="58"/>
-      <c r="E3" s="63"/>
+      <c r="E3" s="60"/>
       <c r="F3" s="56"/>
       <c r="G3" s="58"/>
-      <c r="H3" s="63"/>
+      <c r="H3" s="60"/>
       <c r="I3" s="56"/>
       <c r="J3" s="56"/>
-      <c r="K3" s="60"/>
+      <c r="K3" s="64"/>
     </row>
     <row r="4" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="7"/>
@@ -22959,11 +22959,11 @@
       <c r="D15" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="64" t="s">
+      <c r="E15" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="65"/>
       <c r="J15" s="21"/>
       <c r="K15" s="22"/>
     </row>
@@ -22980,16 +22980,16 @@
       <c r="D16" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="65" t="s">
+      <c r="E16" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="59" t="s">
+      <c r="F16" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="61" t="s">
+      <c r="G16" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="62" t="s">
+      <c r="H16" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I16" s="55" t="s">
@@ -22998,7 +22998,7 @@
       <c r="J16" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="60" t="s">
+      <c r="K16" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -23007,13 +23007,13 @@
       <c r="B17" s="56"/>
       <c r="C17" s="56"/>
       <c r="D17" s="58"/>
-      <c r="E17" s="63"/>
+      <c r="E17" s="60"/>
       <c r="F17" s="56"/>
       <c r="G17" s="58"/>
-      <c r="H17" s="63"/>
+      <c r="H17" s="60"/>
       <c r="I17" s="56"/>
       <c r="J17" s="56"/>
-      <c r="K17" s="60"/>
+      <c r="K17" s="64"/>
     </row>
     <row r="18" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7"/>
@@ -23198,11 +23198,11 @@
       <c r="D29" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="64" t="s">
+      <c r="E29" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="64"/>
-      <c r="G29" s="64"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="65"/>
       <c r="J29" s="21"/>
       <c r="K29" s="22"/>
     </row>
@@ -23219,16 +23219,16 @@
       <c r="D30" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E30" s="65" t="s">
+      <c r="E30" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F30" s="59" t="s">
+      <c r="F30" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G30" s="61" t="s">
+      <c r="G30" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="62" t="s">
+      <c r="H30" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I30" s="55" t="s">
@@ -23237,7 +23237,7 @@
       <c r="J30" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K30" s="60" t="s">
+      <c r="K30" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -23246,13 +23246,13 @@
       <c r="B31" s="56"/>
       <c r="C31" s="56"/>
       <c r="D31" s="58"/>
-      <c r="E31" s="63"/>
+      <c r="E31" s="60"/>
       <c r="F31" s="56"/>
       <c r="G31" s="58"/>
-      <c r="H31" s="63"/>
+      <c r="H31" s="60"/>
       <c r="I31" s="56"/>
       <c r="J31" s="56"/>
-      <c r="K31" s="60"/>
+      <c r="K31" s="64"/>
     </row>
     <row r="32" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7"/>
@@ -23437,11 +23437,11 @@
       <c r="D43" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="64" t="s">
+      <c r="E43" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="64"/>
-      <c r="G43" s="64"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
       <c r="J43" s="21"/>
       <c r="K43" s="22"/>
     </row>
@@ -23458,16 +23458,16 @@
       <c r="D44" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="65" t="s">
+      <c r="E44" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="59" t="s">
+      <c r="F44" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G44" s="61" t="s">
+      <c r="G44" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H44" s="62" t="s">
+      <c r="H44" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I44" s="55" t="s">
@@ -23476,7 +23476,7 @@
       <c r="J44" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="60" t="s">
+      <c r="K44" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -23485,13 +23485,13 @@
       <c r="B45" s="56"/>
       <c r="C45" s="56"/>
       <c r="D45" s="58"/>
-      <c r="E45" s="63"/>
+      <c r="E45" s="60"/>
       <c r="F45" s="56"/>
       <c r="G45" s="58"/>
-      <c r="H45" s="63"/>
+      <c r="H45" s="60"/>
       <c r="I45" s="56"/>
       <c r="J45" s="56"/>
-      <c r="K45" s="60"/>
+      <c r="K45" s="64"/>
     </row>
     <row r="46" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7"/>
@@ -23676,11 +23676,11 @@
       <c r="D57" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E57" s="64" t="s">
+      <c r="E57" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="64"/>
-      <c r="G57" s="64"/>
+      <c r="F57" s="65"/>
+      <c r="G57" s="65"/>
       <c r="J57" s="21"/>
       <c r="K57" s="22"/>
     </row>
@@ -23697,16 +23697,16 @@
       <c r="D58" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="65" t="s">
+      <c r="E58" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F58" s="59" t="s">
+      <c r="F58" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G58" s="61" t="s">
+      <c r="G58" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H58" s="62" t="s">
+      <c r="H58" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I58" s="55" t="s">
@@ -23715,7 +23715,7 @@
       <c r="J58" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K58" s="60" t="s">
+      <c r="K58" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -23724,13 +23724,13 @@
       <c r="B59" s="56"/>
       <c r="C59" s="56"/>
       <c r="D59" s="58"/>
-      <c r="E59" s="63"/>
+      <c r="E59" s="60"/>
       <c r="F59" s="56"/>
       <c r="G59" s="58"/>
-      <c r="H59" s="63"/>
+      <c r="H59" s="60"/>
       <c r="I59" s="56"/>
       <c r="J59" s="56"/>
-      <c r="K59" s="60"/>
+      <c r="K59" s="64"/>
     </row>
     <row r="60" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="7"/>
@@ -23917,35 +23917,25 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="K30:K31"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="H58:H59"/>
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="C30:C31"/>
@@ -23958,25 +23948,35 @@
     <mergeCell ref="E44:E45"/>
     <mergeCell ref="F44:F45"/>
     <mergeCell ref="G44:G45"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="K44:K45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="K30:K31"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E15:G15"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="6">
@@ -24024,11 +24024,11 @@
       <c r="D1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="64" t="s">
+      <c r="E1" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
       <c r="J1" s="21"/>
       <c r="K1" s="22"/>
     </row>
@@ -24045,16 +24045,16 @@
       <c r="D2" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="65" t="s">
+      <c r="E2" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="59" t="s">
+      <c r="F2" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="61" t="s">
+      <c r="G2" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="62" t="s">
+      <c r="H2" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="55" t="s">
@@ -24063,7 +24063,7 @@
       <c r="J2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="60" t="s">
+      <c r="K2" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -24072,13 +24072,13 @@
       <c r="B3" s="56"/>
       <c r="C3" s="56"/>
       <c r="D3" s="58"/>
-      <c r="E3" s="63"/>
+      <c r="E3" s="60"/>
       <c r="F3" s="56"/>
       <c r="G3" s="58"/>
-      <c r="H3" s="63"/>
+      <c r="H3" s="60"/>
       <c r="I3" s="56"/>
       <c r="J3" s="56"/>
-      <c r="K3" s="60"/>
+      <c r="K3" s="64"/>
     </row>
     <row r="4" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="7"/>
@@ -24263,11 +24263,11 @@
       <c r="D15" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="64" t="s">
+      <c r="E15" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="65"/>
       <c r="J15" s="21"/>
       <c r="K15" s="22"/>
     </row>
@@ -24284,16 +24284,16 @@
       <c r="D16" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="65" t="s">
+      <c r="E16" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="59" t="s">
+      <c r="F16" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="61" t="s">
+      <c r="G16" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="62" t="s">
+      <c r="H16" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I16" s="55" t="s">
@@ -24302,7 +24302,7 @@
       <c r="J16" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="60" t="s">
+      <c r="K16" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -24311,13 +24311,13 @@
       <c r="B17" s="56"/>
       <c r="C17" s="56"/>
       <c r="D17" s="58"/>
-      <c r="E17" s="63"/>
+      <c r="E17" s="60"/>
       <c r="F17" s="56"/>
       <c r="G17" s="58"/>
-      <c r="H17" s="63"/>
+      <c r="H17" s="60"/>
       <c r="I17" s="56"/>
       <c r="J17" s="56"/>
-      <c r="K17" s="60"/>
+      <c r="K17" s="64"/>
     </row>
     <row r="18" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7"/>
@@ -24502,11 +24502,11 @@
       <c r="D29" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="64" t="s">
+      <c r="E29" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="64"/>
-      <c r="G29" s="64"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="65"/>
       <c r="J29" s="21"/>
       <c r="K29" s="22"/>
     </row>
@@ -24523,16 +24523,16 @@
       <c r="D30" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E30" s="65" t="s">
+      <c r="E30" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F30" s="59" t="s">
+      <c r="F30" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G30" s="61" t="s">
+      <c r="G30" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="62" t="s">
+      <c r="H30" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I30" s="55" t="s">
@@ -24541,7 +24541,7 @@
       <c r="J30" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K30" s="60" t="s">
+      <c r="K30" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -24550,13 +24550,13 @@
       <c r="B31" s="56"/>
       <c r="C31" s="56"/>
       <c r="D31" s="58"/>
-      <c r="E31" s="63"/>
+      <c r="E31" s="60"/>
       <c r="F31" s="56"/>
       <c r="G31" s="58"/>
-      <c r="H31" s="63"/>
+      <c r="H31" s="60"/>
       <c r="I31" s="56"/>
       <c r="J31" s="56"/>
-      <c r="K31" s="60"/>
+      <c r="K31" s="64"/>
     </row>
     <row r="32" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7"/>
@@ -24741,11 +24741,11 @@
       <c r="D43" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="64" t="s">
+      <c r="E43" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="64"/>
-      <c r="G43" s="64"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
       <c r="J43" s="21"/>
       <c r="K43" s="22"/>
     </row>
@@ -24762,16 +24762,16 @@
       <c r="D44" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="65" t="s">
+      <c r="E44" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="59" t="s">
+      <c r="F44" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G44" s="61" t="s">
+      <c r="G44" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H44" s="62" t="s">
+      <c r="H44" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I44" s="55" t="s">
@@ -24780,7 +24780,7 @@
       <c r="J44" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="60" t="s">
+      <c r="K44" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -24789,13 +24789,13 @@
       <c r="B45" s="56"/>
       <c r="C45" s="56"/>
       <c r="D45" s="58"/>
-      <c r="E45" s="63"/>
+      <c r="E45" s="60"/>
       <c r="F45" s="56"/>
       <c r="G45" s="58"/>
-      <c r="H45" s="63"/>
+      <c r="H45" s="60"/>
       <c r="I45" s="56"/>
       <c r="J45" s="56"/>
-      <c r="K45" s="60"/>
+      <c r="K45" s="64"/>
     </row>
     <row r="46" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7"/>
@@ -24980,11 +24980,11 @@
       <c r="D57" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E57" s="64" t="s">
+      <c r="E57" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="64"/>
-      <c r="G57" s="64"/>
+      <c r="F57" s="65"/>
+      <c r="G57" s="65"/>
       <c r="J57" s="21"/>
       <c r="K57" s="22"/>
     </row>
@@ -25001,16 +25001,16 @@
       <c r="D58" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="65" t="s">
+      <c r="E58" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F58" s="59" t="s">
+      <c r="F58" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G58" s="61" t="s">
+      <c r="G58" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H58" s="62" t="s">
+      <c r="H58" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I58" s="55" t="s">
@@ -25019,7 +25019,7 @@
       <c r="J58" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K58" s="60" t="s">
+      <c r="K58" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -25028,13 +25028,13 @@
       <c r="B59" s="56"/>
       <c r="C59" s="56"/>
       <c r="D59" s="58"/>
-      <c r="E59" s="63"/>
+      <c r="E59" s="60"/>
       <c r="F59" s="56"/>
       <c r="G59" s="58"/>
-      <c r="H59" s="63"/>
+      <c r="H59" s="60"/>
       <c r="I59" s="56"/>
       <c r="J59" s="56"/>
-      <c r="K59" s="60"/>
+      <c r="K59" s="64"/>
     </row>
     <row r="60" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="7"/>
@@ -25221,35 +25221,25 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="K30:K31"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="H58:H59"/>
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="C30:C31"/>
@@ -25262,25 +25252,35 @@
     <mergeCell ref="E44:E45"/>
     <mergeCell ref="F44:F45"/>
     <mergeCell ref="G44:G45"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="K44:K45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="K30:K31"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E15:G15"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="6">
@@ -25328,11 +25328,11 @@
       <c r="D1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="64" t="s">
+      <c r="E1" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
       <c r="J1" s="21"/>
       <c r="K1" s="22"/>
     </row>
@@ -25349,16 +25349,16 @@
       <c r="D2" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="65" t="s">
+      <c r="E2" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="59" t="s">
+      <c r="F2" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="61" t="s">
+      <c r="G2" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="62" t="s">
+      <c r="H2" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="55" t="s">
@@ -25367,7 +25367,7 @@
       <c r="J2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="60" t="s">
+      <c r="K2" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -25376,13 +25376,13 @@
       <c r="B3" s="56"/>
       <c r="C3" s="56"/>
       <c r="D3" s="58"/>
-      <c r="E3" s="63"/>
+      <c r="E3" s="60"/>
       <c r="F3" s="56"/>
       <c r="G3" s="58"/>
-      <c r="H3" s="63"/>
+      <c r="H3" s="60"/>
       <c r="I3" s="56"/>
       <c r="J3" s="56"/>
-      <c r="K3" s="60"/>
+      <c r="K3" s="64"/>
     </row>
     <row r="4" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="7"/>
@@ -25567,11 +25567,11 @@
       <c r="D15" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="64" t="s">
+      <c r="E15" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="65"/>
       <c r="J15" s="21"/>
       <c r="K15" s="22"/>
     </row>
@@ -25588,16 +25588,16 @@
       <c r="D16" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="65" t="s">
+      <c r="E16" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="59" t="s">
+      <c r="F16" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="61" t="s">
+      <c r="G16" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="62" t="s">
+      <c r="H16" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I16" s="55" t="s">
@@ -25606,7 +25606,7 @@
       <c r="J16" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="60" t="s">
+      <c r="K16" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -25615,13 +25615,13 @@
       <c r="B17" s="56"/>
       <c r="C17" s="56"/>
       <c r="D17" s="58"/>
-      <c r="E17" s="63"/>
+      <c r="E17" s="60"/>
       <c r="F17" s="56"/>
       <c r="G17" s="58"/>
-      <c r="H17" s="63"/>
+      <c r="H17" s="60"/>
       <c r="I17" s="56"/>
       <c r="J17" s="56"/>
-      <c r="K17" s="60"/>
+      <c r="K17" s="64"/>
     </row>
     <row r="18" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7"/>
@@ -25806,11 +25806,11 @@
       <c r="D29" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="64" t="s">
+      <c r="E29" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="64"/>
-      <c r="G29" s="64"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="65"/>
       <c r="J29" s="21"/>
       <c r="K29" s="22"/>
     </row>
@@ -25827,16 +25827,16 @@
       <c r="D30" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E30" s="65" t="s">
+      <c r="E30" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F30" s="59" t="s">
+      <c r="F30" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G30" s="61" t="s">
+      <c r="G30" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="62" t="s">
+      <c r="H30" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I30" s="55" t="s">
@@ -25845,7 +25845,7 @@
       <c r="J30" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K30" s="60" t="s">
+      <c r="K30" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -25854,13 +25854,13 @@
       <c r="B31" s="56"/>
       <c r="C31" s="56"/>
       <c r="D31" s="58"/>
-      <c r="E31" s="63"/>
+      <c r="E31" s="60"/>
       <c r="F31" s="56"/>
       <c r="G31" s="58"/>
-      <c r="H31" s="63"/>
+      <c r="H31" s="60"/>
       <c r="I31" s="56"/>
       <c r="J31" s="56"/>
-      <c r="K31" s="60"/>
+      <c r="K31" s="64"/>
     </row>
     <row r="32" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7"/>
@@ -26045,11 +26045,11 @@
       <c r="D43" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="64" t="s">
+      <c r="E43" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="64"/>
-      <c r="G43" s="64"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
       <c r="J43" s="21"/>
       <c r="K43" s="22"/>
     </row>
@@ -26066,16 +26066,16 @@
       <c r="D44" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="65" t="s">
+      <c r="E44" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="59" t="s">
+      <c r="F44" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G44" s="61" t="s">
+      <c r="G44" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H44" s="62" t="s">
+      <c r="H44" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I44" s="55" t="s">
@@ -26084,7 +26084,7 @@
       <c r="J44" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="60" t="s">
+      <c r="K44" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -26093,13 +26093,13 @@
       <c r="B45" s="56"/>
       <c r="C45" s="56"/>
       <c r="D45" s="58"/>
-      <c r="E45" s="63"/>
+      <c r="E45" s="60"/>
       <c r="F45" s="56"/>
       <c r="G45" s="58"/>
-      <c r="H45" s="63"/>
+      <c r="H45" s="60"/>
       <c r="I45" s="56"/>
       <c r="J45" s="56"/>
-      <c r="K45" s="60"/>
+      <c r="K45" s="64"/>
     </row>
     <row r="46" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7"/>
@@ -26284,11 +26284,11 @@
       <c r="D57" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E57" s="64" t="s">
+      <c r="E57" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="64"/>
-      <c r="G57" s="64"/>
+      <c r="F57" s="65"/>
+      <c r="G57" s="65"/>
       <c r="J57" s="21"/>
       <c r="K57" s="22"/>
     </row>
@@ -26305,16 +26305,16 @@
       <c r="D58" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="65" t="s">
+      <c r="E58" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F58" s="59" t="s">
+      <c r="F58" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G58" s="61" t="s">
+      <c r="G58" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H58" s="62" t="s">
+      <c r="H58" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I58" s="55" t="s">
@@ -26323,7 +26323,7 @@
       <c r="J58" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K58" s="60" t="s">
+      <c r="K58" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -26332,13 +26332,13 @@
       <c r="B59" s="56"/>
       <c r="C59" s="56"/>
       <c r="D59" s="58"/>
-      <c r="E59" s="63"/>
+      <c r="E59" s="60"/>
       <c r="F59" s="56"/>
       <c r="G59" s="58"/>
-      <c r="H59" s="63"/>
+      <c r="H59" s="60"/>
       <c r="I59" s="56"/>
       <c r="J59" s="56"/>
-      <c r="K59" s="60"/>
+      <c r="K59" s="64"/>
     </row>
     <row r="60" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="7"/>
@@ -26525,29 +26525,27 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="K44:K45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="E16:E17"/>
     <mergeCell ref="E57:G57"/>
     <mergeCell ref="J16:J17"/>
     <mergeCell ref="K16:K17"/>
@@ -26564,27 +26562,29 @@
     <mergeCell ref="H16:H17"/>
     <mergeCell ref="E43:G43"/>
     <mergeCell ref="G30:G31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="6">
@@ -26632,11 +26632,11 @@
       <c r="D1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="64" t="s">
+      <c r="E1" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
       <c r="J1" s="21"/>
       <c r="K1" s="22"/>
     </row>
@@ -26653,16 +26653,16 @@
       <c r="D2" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="65" t="s">
+      <c r="E2" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="59" t="s">
+      <c r="F2" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="61" t="s">
+      <c r="G2" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="62" t="s">
+      <c r="H2" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="55" t="s">
@@ -26671,7 +26671,7 @@
       <c r="J2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="60" t="s">
+      <c r="K2" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -26680,13 +26680,13 @@
       <c r="B3" s="56"/>
       <c r="C3" s="56"/>
       <c r="D3" s="58"/>
-      <c r="E3" s="63"/>
+      <c r="E3" s="60"/>
       <c r="F3" s="56"/>
       <c r="G3" s="58"/>
-      <c r="H3" s="63"/>
+      <c r="H3" s="60"/>
       <c r="I3" s="56"/>
       <c r="J3" s="56"/>
-      <c r="K3" s="60"/>
+      <c r="K3" s="64"/>
     </row>
     <row r="4" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="7"/>
@@ -26871,11 +26871,11 @@
       <c r="D15" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="64" t="s">
+      <c r="E15" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="65"/>
       <c r="J15" s="21"/>
       <c r="K15" s="22"/>
     </row>
@@ -26892,16 +26892,16 @@
       <c r="D16" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="65" t="s">
+      <c r="E16" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="59" t="s">
+      <c r="F16" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="61" t="s">
+      <c r="G16" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="62" t="s">
+      <c r="H16" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I16" s="55" t="s">
@@ -26910,7 +26910,7 @@
       <c r="J16" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="60" t="s">
+      <c r="K16" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -26919,13 +26919,13 @@
       <c r="B17" s="56"/>
       <c r="C17" s="56"/>
       <c r="D17" s="58"/>
-      <c r="E17" s="63"/>
+      <c r="E17" s="60"/>
       <c r="F17" s="56"/>
       <c r="G17" s="58"/>
-      <c r="H17" s="63"/>
+      <c r="H17" s="60"/>
       <c r="I17" s="56"/>
       <c r="J17" s="56"/>
-      <c r="K17" s="60"/>
+      <c r="K17" s="64"/>
     </row>
     <row r="18" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7"/>
@@ -27110,11 +27110,11 @@
       <c r="D29" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="64" t="s">
+      <c r="E29" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="64"/>
-      <c r="G29" s="64"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="65"/>
       <c r="J29" s="21"/>
       <c r="K29" s="22"/>
     </row>
@@ -27131,16 +27131,16 @@
       <c r="D30" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E30" s="65" t="s">
+      <c r="E30" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F30" s="59" t="s">
+      <c r="F30" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G30" s="61" t="s">
+      <c r="G30" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="62" t="s">
+      <c r="H30" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I30" s="55" t="s">
@@ -27149,7 +27149,7 @@
       <c r="J30" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K30" s="60" t="s">
+      <c r="K30" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -27158,13 +27158,13 @@
       <c r="B31" s="56"/>
       <c r="C31" s="56"/>
       <c r="D31" s="58"/>
-      <c r="E31" s="63"/>
+      <c r="E31" s="60"/>
       <c r="F31" s="56"/>
       <c r="G31" s="58"/>
-      <c r="H31" s="63"/>
+      <c r="H31" s="60"/>
       <c r="I31" s="56"/>
       <c r="J31" s="56"/>
-      <c r="K31" s="60"/>
+      <c r="K31" s="64"/>
     </row>
     <row r="32" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7"/>
@@ -27349,11 +27349,11 @@
       <c r="D43" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="64" t="s">
+      <c r="E43" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="64"/>
-      <c r="G43" s="64"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
       <c r="J43" s="21"/>
       <c r="K43" s="22"/>
     </row>
@@ -27370,16 +27370,16 @@
       <c r="D44" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="65" t="s">
+      <c r="E44" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="59" t="s">
+      <c r="F44" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G44" s="61" t="s">
+      <c r="G44" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H44" s="62" t="s">
+      <c r="H44" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I44" s="55" t="s">
@@ -27388,7 +27388,7 @@
       <c r="J44" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="60" t="s">
+      <c r="K44" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -27397,13 +27397,13 @@
       <c r="B45" s="56"/>
       <c r="C45" s="56"/>
       <c r="D45" s="58"/>
-      <c r="E45" s="63"/>
+      <c r="E45" s="60"/>
       <c r="F45" s="56"/>
       <c r="G45" s="58"/>
-      <c r="H45" s="63"/>
+      <c r="H45" s="60"/>
       <c r="I45" s="56"/>
       <c r="J45" s="56"/>
-      <c r="K45" s="60"/>
+      <c r="K45" s="64"/>
     </row>
     <row r="46" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7"/>
@@ -27588,11 +27588,11 @@
       <c r="D57" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E57" s="64" t="s">
+      <c r="E57" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="64"/>
-      <c r="G57" s="64"/>
+      <c r="F57" s="65"/>
+      <c r="G57" s="65"/>
       <c r="J57" s="21"/>
       <c r="K57" s="22"/>
     </row>
@@ -27609,16 +27609,16 @@
       <c r="D58" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="65" t="s">
+      <c r="E58" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F58" s="59" t="s">
+      <c r="F58" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G58" s="61" t="s">
+      <c r="G58" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H58" s="62" t="s">
+      <c r="H58" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I58" s="55" t="s">
@@ -27627,7 +27627,7 @@
       <c r="J58" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K58" s="60" t="s">
+      <c r="K58" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -27636,13 +27636,13 @@
       <c r="B59" s="56"/>
       <c r="C59" s="56"/>
       <c r="D59" s="58"/>
-      <c r="E59" s="63"/>
+      <c r="E59" s="60"/>
       <c r="F59" s="56"/>
       <c r="G59" s="58"/>
-      <c r="H59" s="63"/>
+      <c r="H59" s="60"/>
       <c r="I59" s="56"/>
       <c r="J59" s="56"/>
-      <c r="K59" s="60"/>
+      <c r="K59" s="64"/>
     </row>
     <row r="60" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="7"/>
@@ -27829,35 +27829,25 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="K30:K31"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="H58:H59"/>
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="C30:C31"/>
@@ -27870,25 +27860,35 @@
     <mergeCell ref="E44:E45"/>
     <mergeCell ref="F44:F45"/>
     <mergeCell ref="G44:G45"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="K44:K45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="K30:K31"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E15:G15"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="6">
@@ -30068,11 +30068,11 @@
       <c r="D1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="64" t="s">
+      <c r="E1" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
       <c r="J1" s="21"/>
       <c r="K1" s="22"/>
     </row>
@@ -30089,16 +30089,16 @@
       <c r="D2" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="65" t="s">
+      <c r="E2" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="59" t="s">
+      <c r="F2" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="61" t="s">
+      <c r="G2" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="62" t="s">
+      <c r="H2" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="55" t="s">
@@ -30107,7 +30107,7 @@
       <c r="J2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="60" t="s">
+      <c r="K2" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -30116,13 +30116,13 @@
       <c r="B3" s="56"/>
       <c r="C3" s="56"/>
       <c r="D3" s="58"/>
-      <c r="E3" s="63"/>
+      <c r="E3" s="60"/>
       <c r="F3" s="56"/>
       <c r="G3" s="58"/>
-      <c r="H3" s="63"/>
+      <c r="H3" s="60"/>
       <c r="I3" s="56"/>
       <c r="J3" s="56"/>
-      <c r="K3" s="60"/>
+      <c r="K3" s="64"/>
     </row>
     <row r="4" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="7"/>
@@ -30307,11 +30307,11 @@
       <c r="D15" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="64" t="s">
+      <c r="E15" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="65"/>
       <c r="J15" s="21"/>
       <c r="K15" s="22"/>
     </row>
@@ -30328,16 +30328,16 @@
       <c r="D16" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="65" t="s">
+      <c r="E16" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="59" t="s">
+      <c r="F16" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="61" t="s">
+      <c r="G16" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="62" t="s">
+      <c r="H16" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I16" s="55" t="s">
@@ -30346,7 +30346,7 @@
       <c r="J16" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="60" t="s">
+      <c r="K16" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -30355,13 +30355,13 @@
       <c r="B17" s="56"/>
       <c r="C17" s="56"/>
       <c r="D17" s="58"/>
-      <c r="E17" s="63"/>
+      <c r="E17" s="60"/>
       <c r="F17" s="56"/>
       <c r="G17" s="58"/>
-      <c r="H17" s="63"/>
+      <c r="H17" s="60"/>
       <c r="I17" s="56"/>
       <c r="J17" s="56"/>
-      <c r="K17" s="60"/>
+      <c r="K17" s="64"/>
     </row>
     <row r="18" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7"/>
@@ -30546,11 +30546,11 @@
       <c r="D29" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="64" t="s">
+      <c r="E29" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="64"/>
-      <c r="G29" s="64"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="65"/>
       <c r="J29" s="21"/>
       <c r="K29" s="22"/>
     </row>
@@ -30567,16 +30567,16 @@
       <c r="D30" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E30" s="65" t="s">
+      <c r="E30" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F30" s="59" t="s">
+      <c r="F30" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G30" s="61" t="s">
+      <c r="G30" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="62" t="s">
+      <c r="H30" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I30" s="55" t="s">
@@ -30585,7 +30585,7 @@
       <c r="J30" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K30" s="60" t="s">
+      <c r="K30" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -30594,13 +30594,13 @@
       <c r="B31" s="56"/>
       <c r="C31" s="56"/>
       <c r="D31" s="58"/>
-      <c r="E31" s="63"/>
+      <c r="E31" s="60"/>
       <c r="F31" s="56"/>
       <c r="G31" s="58"/>
-      <c r="H31" s="63"/>
+      <c r="H31" s="60"/>
       <c r="I31" s="56"/>
       <c r="J31" s="56"/>
-      <c r="K31" s="60"/>
+      <c r="K31" s="64"/>
     </row>
     <row r="32" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7"/>
@@ -30785,11 +30785,11 @@
       <c r="D43" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="64" t="s">
+      <c r="E43" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="64"/>
-      <c r="G43" s="64"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
       <c r="J43" s="21"/>
       <c r="K43" s="22"/>
     </row>
@@ -30806,16 +30806,16 @@
       <c r="D44" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="65" t="s">
+      <c r="E44" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="59" t="s">
+      <c r="F44" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G44" s="61" t="s">
+      <c r="G44" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H44" s="62" t="s">
+      <c r="H44" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I44" s="55" t="s">
@@ -30824,7 +30824,7 @@
       <c r="J44" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="60" t="s">
+      <c r="K44" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -30833,13 +30833,13 @@
       <c r="B45" s="56"/>
       <c r="C45" s="56"/>
       <c r="D45" s="58"/>
-      <c r="E45" s="63"/>
+      <c r="E45" s="60"/>
       <c r="F45" s="56"/>
       <c r="G45" s="58"/>
-      <c r="H45" s="63"/>
+      <c r="H45" s="60"/>
       <c r="I45" s="56"/>
       <c r="J45" s="56"/>
-      <c r="K45" s="60"/>
+      <c r="K45" s="64"/>
     </row>
     <row r="46" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7"/>
@@ -31024,11 +31024,11 @@
       <c r="D57" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E57" s="64" t="s">
+      <c r="E57" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="64"/>
-      <c r="G57" s="64"/>
+      <c r="F57" s="65"/>
+      <c r="G57" s="65"/>
       <c r="J57" s="21"/>
       <c r="K57" s="22"/>
     </row>
@@ -31045,16 +31045,16 @@
       <c r="D58" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="65" t="s">
+      <c r="E58" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F58" s="59" t="s">
+      <c r="F58" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G58" s="61" t="s">
+      <c r="G58" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H58" s="62" t="s">
+      <c r="H58" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I58" s="55" t="s">
@@ -31063,7 +31063,7 @@
       <c r="J58" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K58" s="60" t="s">
+      <c r="K58" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -31072,13 +31072,13 @@
       <c r="B59" s="56"/>
       <c r="C59" s="56"/>
       <c r="D59" s="58"/>
-      <c r="E59" s="63"/>
+      <c r="E59" s="60"/>
       <c r="F59" s="56"/>
       <c r="G59" s="58"/>
-      <c r="H59" s="63"/>
+      <c r="H59" s="60"/>
       <c r="I59" s="56"/>
       <c r="J59" s="56"/>
-      <c r="K59" s="60"/>
+      <c r="K59" s="64"/>
     </row>
     <row r="60" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="7"/>
@@ -31265,35 +31265,25 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="K30:K31"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="H58:H59"/>
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="C30:C31"/>
@@ -31306,25 +31296,35 @@
     <mergeCell ref="E44:E45"/>
     <mergeCell ref="F44:F45"/>
     <mergeCell ref="G44:G45"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="K44:K45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="K30:K31"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E15:G15"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="6">
@@ -31372,11 +31372,11 @@
       <c r="D1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="64" t="s">
+      <c r="E1" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
       <c r="J1" s="21"/>
       <c r="K1" s="22"/>
     </row>
@@ -31393,16 +31393,16 @@
       <c r="D2" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="65" t="s">
+      <c r="E2" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="59" t="s">
+      <c r="F2" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="61" t="s">
+      <c r="G2" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="62" t="s">
+      <c r="H2" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="55" t="s">
@@ -31411,7 +31411,7 @@
       <c r="J2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="60" t="s">
+      <c r="K2" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -31420,13 +31420,13 @@
       <c r="B3" s="56"/>
       <c r="C3" s="56"/>
       <c r="D3" s="58"/>
-      <c r="E3" s="63"/>
+      <c r="E3" s="60"/>
       <c r="F3" s="56"/>
       <c r="G3" s="58"/>
-      <c r="H3" s="63"/>
+      <c r="H3" s="60"/>
       <c r="I3" s="56"/>
       <c r="J3" s="56"/>
-      <c r="K3" s="60"/>
+      <c r="K3" s="64"/>
     </row>
     <row r="4" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="7"/>
@@ -31611,11 +31611,11 @@
       <c r="D15" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="64" t="s">
+      <c r="E15" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="65"/>
       <c r="J15" s="21"/>
       <c r="K15" s="22"/>
     </row>
@@ -31632,16 +31632,16 @@
       <c r="D16" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="65" t="s">
+      <c r="E16" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="59" t="s">
+      <c r="F16" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="61" t="s">
+      <c r="G16" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="62" t="s">
+      <c r="H16" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I16" s="55" t="s">
@@ -31650,7 +31650,7 @@
       <c r="J16" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="60" t="s">
+      <c r="K16" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -31659,13 +31659,13 @@
       <c r="B17" s="56"/>
       <c r="C17" s="56"/>
       <c r="D17" s="58"/>
-      <c r="E17" s="63"/>
+      <c r="E17" s="60"/>
       <c r="F17" s="56"/>
       <c r="G17" s="58"/>
-      <c r="H17" s="63"/>
+      <c r="H17" s="60"/>
       <c r="I17" s="56"/>
       <c r="J17" s="56"/>
-      <c r="K17" s="60"/>
+      <c r="K17" s="64"/>
     </row>
     <row r="18" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7"/>
@@ -31850,11 +31850,11 @@
       <c r="D29" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="64" t="s">
+      <c r="E29" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="64"/>
-      <c r="G29" s="64"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="65"/>
       <c r="J29" s="21"/>
       <c r="K29" s="22"/>
     </row>
@@ -31871,16 +31871,16 @@
       <c r="D30" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E30" s="65" t="s">
+      <c r="E30" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F30" s="59" t="s">
+      <c r="F30" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G30" s="61" t="s">
+      <c r="G30" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="62" t="s">
+      <c r="H30" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I30" s="55" t="s">
@@ -31889,7 +31889,7 @@
       <c r="J30" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K30" s="60" t="s">
+      <c r="K30" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -31898,13 +31898,13 @@
       <c r="B31" s="56"/>
       <c r="C31" s="56"/>
       <c r="D31" s="58"/>
-      <c r="E31" s="63"/>
+      <c r="E31" s="60"/>
       <c r="F31" s="56"/>
       <c r="G31" s="58"/>
-      <c r="H31" s="63"/>
+      <c r="H31" s="60"/>
       <c r="I31" s="56"/>
       <c r="J31" s="56"/>
-      <c r="K31" s="60"/>
+      <c r="K31" s="64"/>
     </row>
     <row r="32" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7"/>
@@ -32089,11 +32089,11 @@
       <c r="D43" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="64" t="s">
+      <c r="E43" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="64"/>
-      <c r="G43" s="64"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
       <c r="J43" s="21"/>
       <c r="K43" s="22"/>
     </row>
@@ -32110,16 +32110,16 @@
       <c r="D44" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="65" t="s">
+      <c r="E44" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="59" t="s">
+      <c r="F44" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G44" s="61" t="s">
+      <c r="G44" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H44" s="62" t="s">
+      <c r="H44" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I44" s="55" t="s">
@@ -32128,7 +32128,7 @@
       <c r="J44" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="60" t="s">
+      <c r="K44" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -32137,13 +32137,13 @@
       <c r="B45" s="56"/>
       <c r="C45" s="56"/>
       <c r="D45" s="58"/>
-      <c r="E45" s="63"/>
+      <c r="E45" s="60"/>
       <c r="F45" s="56"/>
       <c r="G45" s="58"/>
-      <c r="H45" s="63"/>
+      <c r="H45" s="60"/>
       <c r="I45" s="56"/>
       <c r="J45" s="56"/>
-      <c r="K45" s="60"/>
+      <c r="K45" s="64"/>
     </row>
     <row r="46" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7"/>
@@ -32328,11 +32328,11 @@
       <c r="D57" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E57" s="64" t="s">
+      <c r="E57" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="64"/>
-      <c r="G57" s="64"/>
+      <c r="F57" s="65"/>
+      <c r="G57" s="65"/>
       <c r="J57" s="21"/>
       <c r="K57" s="22"/>
     </row>
@@ -32349,16 +32349,16 @@
       <c r="D58" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="65" t="s">
+      <c r="E58" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F58" s="59" t="s">
+      <c r="F58" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G58" s="61" t="s">
+      <c r="G58" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H58" s="62" t="s">
+      <c r="H58" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I58" s="55" t="s">
@@ -32367,7 +32367,7 @@
       <c r="J58" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K58" s="60" t="s">
+      <c r="K58" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -32376,13 +32376,13 @@
       <c r="B59" s="56"/>
       <c r="C59" s="56"/>
       <c r="D59" s="58"/>
-      <c r="E59" s="63"/>
+      <c r="E59" s="60"/>
       <c r="F59" s="56"/>
       <c r="G59" s="58"/>
-      <c r="H59" s="63"/>
+      <c r="H59" s="60"/>
       <c r="I59" s="56"/>
       <c r="J59" s="56"/>
-      <c r="K59" s="60"/>
+      <c r="K59" s="64"/>
     </row>
     <row r="60" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="7"/>
@@ -32569,35 +32569,25 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="K30:K31"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="H58:H59"/>
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="C30:C31"/>
@@ -32610,25 +32600,35 @@
     <mergeCell ref="E44:E45"/>
     <mergeCell ref="F44:F45"/>
     <mergeCell ref="G44:G45"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="K44:K45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="K30:K31"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E15:G15"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="6">
@@ -32676,11 +32676,11 @@
       <c r="D1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="64" t="s">
+      <c r="E1" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
       <c r="J1" s="21"/>
       <c r="K1" s="22"/>
     </row>
@@ -32697,16 +32697,16 @@
       <c r="D2" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="65" t="s">
+      <c r="E2" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="59" t="s">
+      <c r="F2" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="61" t="s">
+      <c r="G2" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="62" t="s">
+      <c r="H2" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="55" t="s">
@@ -32715,7 +32715,7 @@
       <c r="J2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="60" t="s">
+      <c r="K2" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -32724,13 +32724,13 @@
       <c r="B3" s="56"/>
       <c r="C3" s="56"/>
       <c r="D3" s="58"/>
-      <c r="E3" s="63"/>
+      <c r="E3" s="60"/>
       <c r="F3" s="56"/>
       <c r="G3" s="58"/>
-      <c r="H3" s="63"/>
+      <c r="H3" s="60"/>
       <c r="I3" s="56"/>
       <c r="J3" s="56"/>
-      <c r="K3" s="60"/>
+      <c r="K3" s="64"/>
     </row>
     <row r="4" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="7"/>
@@ -32915,11 +32915,11 @@
       <c r="D15" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="64" t="s">
+      <c r="E15" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="65"/>
       <c r="J15" s="21"/>
       <c r="K15" s="22"/>
     </row>
@@ -32936,16 +32936,16 @@
       <c r="D16" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="65" t="s">
+      <c r="E16" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="59" t="s">
+      <c r="F16" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="61" t="s">
+      <c r="G16" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="62" t="s">
+      <c r="H16" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I16" s="55" t="s">
@@ -32954,7 +32954,7 @@
       <c r="J16" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="60" t="s">
+      <c r="K16" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -32963,13 +32963,13 @@
       <c r="B17" s="56"/>
       <c r="C17" s="56"/>
       <c r="D17" s="58"/>
-      <c r="E17" s="63"/>
+      <c r="E17" s="60"/>
       <c r="F17" s="56"/>
       <c r="G17" s="58"/>
-      <c r="H17" s="63"/>
+      <c r="H17" s="60"/>
       <c r="I17" s="56"/>
       <c r="J17" s="56"/>
-      <c r="K17" s="60"/>
+      <c r="K17" s="64"/>
     </row>
     <row r="18" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7"/>
@@ -33154,11 +33154,11 @@
       <c r="D29" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="64" t="s">
+      <c r="E29" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="64"/>
-      <c r="G29" s="64"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="65"/>
       <c r="J29" s="21"/>
       <c r="K29" s="22"/>
     </row>
@@ -33175,16 +33175,16 @@
       <c r="D30" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E30" s="65" t="s">
+      <c r="E30" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F30" s="59" t="s">
+      <c r="F30" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G30" s="61" t="s">
+      <c r="G30" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="62" t="s">
+      <c r="H30" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I30" s="55" t="s">
@@ -33193,7 +33193,7 @@
       <c r="J30" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K30" s="60" t="s">
+      <c r="K30" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -33202,13 +33202,13 @@
       <c r="B31" s="56"/>
       <c r="C31" s="56"/>
       <c r="D31" s="58"/>
-      <c r="E31" s="63"/>
+      <c r="E31" s="60"/>
       <c r="F31" s="56"/>
       <c r="G31" s="58"/>
-      <c r="H31" s="63"/>
+      <c r="H31" s="60"/>
       <c r="I31" s="56"/>
       <c r="J31" s="56"/>
-      <c r="K31" s="60"/>
+      <c r="K31" s="64"/>
     </row>
     <row r="32" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7"/>
@@ -33393,11 +33393,11 @@
       <c r="D43" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="64" t="s">
+      <c r="E43" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="64"/>
-      <c r="G43" s="64"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
       <c r="J43" s="21"/>
       <c r="K43" s="22"/>
     </row>
@@ -33414,16 +33414,16 @@
       <c r="D44" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="65" t="s">
+      <c r="E44" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="59" t="s">
+      <c r="F44" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G44" s="61" t="s">
+      <c r="G44" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H44" s="62" t="s">
+      <c r="H44" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I44" s="55" t="s">
@@ -33432,7 +33432,7 @@
       <c r="J44" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="60" t="s">
+      <c r="K44" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -33441,13 +33441,13 @@
       <c r="B45" s="56"/>
       <c r="C45" s="56"/>
       <c r="D45" s="58"/>
-      <c r="E45" s="63"/>
+      <c r="E45" s="60"/>
       <c r="F45" s="56"/>
       <c r="G45" s="58"/>
-      <c r="H45" s="63"/>
+      <c r="H45" s="60"/>
       <c r="I45" s="56"/>
       <c r="J45" s="56"/>
-      <c r="K45" s="60"/>
+      <c r="K45" s="64"/>
     </row>
     <row r="46" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7"/>
@@ -33632,11 +33632,11 @@
       <c r="D57" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E57" s="64" t="s">
+      <c r="E57" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="64"/>
-      <c r="G57" s="64"/>
+      <c r="F57" s="65"/>
+      <c r="G57" s="65"/>
       <c r="J57" s="21"/>
       <c r="K57" s="22"/>
     </row>
@@ -33653,16 +33653,16 @@
       <c r="D58" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="65" t="s">
+      <c r="E58" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F58" s="59" t="s">
+      <c r="F58" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G58" s="61" t="s">
+      <c r="G58" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H58" s="62" t="s">
+      <c r="H58" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I58" s="55" t="s">
@@ -33671,7 +33671,7 @@
       <c r="J58" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K58" s="60" t="s">
+      <c r="K58" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -33680,13 +33680,13 @@
       <c r="B59" s="56"/>
       <c r="C59" s="56"/>
       <c r="D59" s="58"/>
-      <c r="E59" s="63"/>
+      <c r="E59" s="60"/>
       <c r="F59" s="56"/>
       <c r="G59" s="58"/>
-      <c r="H59" s="63"/>
+      <c r="H59" s="60"/>
       <c r="I59" s="56"/>
       <c r="J59" s="56"/>
-      <c r="K59" s="60"/>
+      <c r="K59" s="64"/>
     </row>
     <row r="60" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="7"/>
@@ -33873,29 +33873,27 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="K44:K45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="E16:E17"/>
     <mergeCell ref="E57:G57"/>
     <mergeCell ref="J16:J17"/>
     <mergeCell ref="K16:K17"/>
@@ -33912,27 +33910,29 @@
     <mergeCell ref="H16:H17"/>
     <mergeCell ref="E43:G43"/>
     <mergeCell ref="G30:G31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="6">
@@ -33980,11 +33980,11 @@
       <c r="D1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="64" t="s">
+      <c r="E1" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
       <c r="J1" s="21"/>
       <c r="K1" s="22"/>
     </row>
@@ -34001,16 +34001,16 @@
       <c r="D2" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="65" t="s">
+      <c r="E2" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="59" t="s">
+      <c r="F2" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="61" t="s">
+      <c r="G2" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="62" t="s">
+      <c r="H2" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="55" t="s">
@@ -34019,7 +34019,7 @@
       <c r="J2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="60" t="s">
+      <c r="K2" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -34028,13 +34028,13 @@
       <c r="B3" s="56"/>
       <c r="C3" s="56"/>
       <c r="D3" s="58"/>
-      <c r="E3" s="63"/>
+      <c r="E3" s="60"/>
       <c r="F3" s="56"/>
       <c r="G3" s="58"/>
-      <c r="H3" s="63"/>
+      <c r="H3" s="60"/>
       <c r="I3" s="56"/>
       <c r="J3" s="56"/>
-      <c r="K3" s="60"/>
+      <c r="K3" s="64"/>
     </row>
     <row r="4" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="7"/>
@@ -34219,11 +34219,11 @@
       <c r="D15" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="64" t="s">
+      <c r="E15" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="65"/>
       <c r="J15" s="21"/>
       <c r="K15" s="22"/>
     </row>
@@ -34240,16 +34240,16 @@
       <c r="D16" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="65" t="s">
+      <c r="E16" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="59" t="s">
+      <c r="F16" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="61" t="s">
+      <c r="G16" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="62" t="s">
+      <c r="H16" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I16" s="55" t="s">
@@ -34258,7 +34258,7 @@
       <c r="J16" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="60" t="s">
+      <c r="K16" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -34267,13 +34267,13 @@
       <c r="B17" s="56"/>
       <c r="C17" s="56"/>
       <c r="D17" s="58"/>
-      <c r="E17" s="63"/>
+      <c r="E17" s="60"/>
       <c r="F17" s="56"/>
       <c r="G17" s="58"/>
-      <c r="H17" s="63"/>
+      <c r="H17" s="60"/>
       <c r="I17" s="56"/>
       <c r="J17" s="56"/>
-      <c r="K17" s="60"/>
+      <c r="K17" s="64"/>
     </row>
     <row r="18" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7"/>
@@ -34458,11 +34458,11 @@
       <c r="D29" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="64" t="s">
+      <c r="E29" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="64"/>
-      <c r="G29" s="64"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="65"/>
       <c r="J29" s="21"/>
       <c r="K29" s="22"/>
     </row>
@@ -34479,16 +34479,16 @@
       <c r="D30" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E30" s="65" t="s">
+      <c r="E30" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F30" s="59" t="s">
+      <c r="F30" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G30" s="61" t="s">
+      <c r="G30" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="62" t="s">
+      <c r="H30" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I30" s="55" t="s">
@@ -34497,7 +34497,7 @@
       <c r="J30" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K30" s="60" t="s">
+      <c r="K30" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -34506,13 +34506,13 @@
       <c r="B31" s="56"/>
       <c r="C31" s="56"/>
       <c r="D31" s="58"/>
-      <c r="E31" s="63"/>
+      <c r="E31" s="60"/>
       <c r="F31" s="56"/>
       <c r="G31" s="58"/>
-      <c r="H31" s="63"/>
+      <c r="H31" s="60"/>
       <c r="I31" s="56"/>
       <c r="J31" s="56"/>
-      <c r="K31" s="60"/>
+      <c r="K31" s="64"/>
     </row>
     <row r="32" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7"/>
@@ -34697,11 +34697,11 @@
       <c r="D43" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="64" t="s">
+      <c r="E43" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="64"/>
-      <c r="G43" s="64"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
       <c r="J43" s="21"/>
       <c r="K43" s="22"/>
     </row>
@@ -34718,16 +34718,16 @@
       <c r="D44" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="65" t="s">
+      <c r="E44" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="59" t="s">
+      <c r="F44" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G44" s="61" t="s">
+      <c r="G44" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H44" s="62" t="s">
+      <c r="H44" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I44" s="55" t="s">
@@ -34736,7 +34736,7 @@
       <c r="J44" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="60" t="s">
+      <c r="K44" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -34745,13 +34745,13 @@
       <c r="B45" s="56"/>
       <c r="C45" s="56"/>
       <c r="D45" s="58"/>
-      <c r="E45" s="63"/>
+      <c r="E45" s="60"/>
       <c r="F45" s="56"/>
       <c r="G45" s="58"/>
-      <c r="H45" s="63"/>
+      <c r="H45" s="60"/>
       <c r="I45" s="56"/>
       <c r="J45" s="56"/>
-      <c r="K45" s="60"/>
+      <c r="K45" s="64"/>
     </row>
     <row r="46" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7"/>
@@ -34936,11 +34936,11 @@
       <c r="D57" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E57" s="64" t="s">
+      <c r="E57" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="64"/>
-      <c r="G57" s="64"/>
+      <c r="F57" s="65"/>
+      <c r="G57" s="65"/>
       <c r="J57" s="21"/>
       <c r="K57" s="22"/>
     </row>
@@ -34957,16 +34957,16 @@
       <c r="D58" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="65" t="s">
+      <c r="E58" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F58" s="59" t="s">
+      <c r="F58" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G58" s="61" t="s">
+      <c r="G58" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H58" s="62" t="s">
+      <c r="H58" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I58" s="55" t="s">
@@ -34975,7 +34975,7 @@
       <c r="J58" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K58" s="60" t="s">
+      <c r="K58" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -34984,13 +34984,13 @@
       <c r="B59" s="56"/>
       <c r="C59" s="56"/>
       <c r="D59" s="58"/>
-      <c r="E59" s="63"/>
+      <c r="E59" s="60"/>
       <c r="F59" s="56"/>
       <c r="G59" s="58"/>
-      <c r="H59" s="63"/>
+      <c r="H59" s="60"/>
       <c r="I59" s="56"/>
       <c r="J59" s="56"/>
-      <c r="K59" s="60"/>
+      <c r="K59" s="64"/>
     </row>
     <row r="60" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="7"/>
@@ -35177,35 +35177,25 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="K30:K31"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="H58:H59"/>
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="C30:C31"/>
@@ -35218,25 +35208,35 @@
     <mergeCell ref="E44:E45"/>
     <mergeCell ref="F44:F45"/>
     <mergeCell ref="G44:G45"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="K44:K45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="K30:K31"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E15:G15"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="6">
@@ -35284,11 +35284,11 @@
       <c r="D1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="64" t="s">
+      <c r="E1" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
       <c r="J1" s="21"/>
       <c r="K1" s="22"/>
     </row>
@@ -35305,16 +35305,16 @@
       <c r="D2" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="65" t="s">
+      <c r="E2" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="59" t="s">
+      <c r="F2" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="61" t="s">
+      <c r="G2" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="62" t="s">
+      <c r="H2" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="55" t="s">
@@ -35323,7 +35323,7 @@
       <c r="J2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="60" t="s">
+      <c r="K2" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -35332,13 +35332,13 @@
       <c r="B3" s="56"/>
       <c r="C3" s="56"/>
       <c r="D3" s="58"/>
-      <c r="E3" s="63"/>
+      <c r="E3" s="60"/>
       <c r="F3" s="56"/>
       <c r="G3" s="58"/>
-      <c r="H3" s="63"/>
+      <c r="H3" s="60"/>
       <c r="I3" s="56"/>
       <c r="J3" s="56"/>
-      <c r="K3" s="60"/>
+      <c r="K3" s="64"/>
     </row>
     <row r="4" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="7"/>
@@ -35523,11 +35523,11 @@
       <c r="D15" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="64" t="s">
+      <c r="E15" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="65"/>
       <c r="J15" s="21"/>
       <c r="K15" s="22"/>
     </row>
@@ -35544,16 +35544,16 @@
       <c r="D16" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="65" t="s">
+      <c r="E16" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="59" t="s">
+      <c r="F16" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="61" t="s">
+      <c r="G16" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="62" t="s">
+      <c r="H16" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I16" s="55" t="s">
@@ -35562,7 +35562,7 @@
       <c r="J16" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="60" t="s">
+      <c r="K16" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -35571,13 +35571,13 @@
       <c r="B17" s="56"/>
       <c r="C17" s="56"/>
       <c r="D17" s="58"/>
-      <c r="E17" s="63"/>
+      <c r="E17" s="60"/>
       <c r="F17" s="56"/>
       <c r="G17" s="58"/>
-      <c r="H17" s="63"/>
+      <c r="H17" s="60"/>
       <c r="I17" s="56"/>
       <c r="J17" s="56"/>
-      <c r="K17" s="60"/>
+      <c r="K17" s="64"/>
     </row>
     <row r="18" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7"/>
@@ -35762,11 +35762,11 @@
       <c r="D29" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="64" t="s">
+      <c r="E29" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="64"/>
-      <c r="G29" s="64"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="65"/>
       <c r="J29" s="21"/>
       <c r="K29" s="22"/>
     </row>
@@ -35783,16 +35783,16 @@
       <c r="D30" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E30" s="65" t="s">
+      <c r="E30" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F30" s="59" t="s">
+      <c r="F30" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G30" s="61" t="s">
+      <c r="G30" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="62" t="s">
+      <c r="H30" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I30" s="55" t="s">
@@ -35801,7 +35801,7 @@
       <c r="J30" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K30" s="60" t="s">
+      <c r="K30" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -35810,13 +35810,13 @@
       <c r="B31" s="56"/>
       <c r="C31" s="56"/>
       <c r="D31" s="58"/>
-      <c r="E31" s="63"/>
+      <c r="E31" s="60"/>
       <c r="F31" s="56"/>
       <c r="G31" s="58"/>
-      <c r="H31" s="63"/>
+      <c r="H31" s="60"/>
       <c r="I31" s="56"/>
       <c r="J31" s="56"/>
-      <c r="K31" s="60"/>
+      <c r="K31" s="64"/>
     </row>
     <row r="32" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7"/>
@@ -36001,11 +36001,11 @@
       <c r="D43" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="64" t="s">
+      <c r="E43" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="64"/>
-      <c r="G43" s="64"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
       <c r="J43" s="21"/>
       <c r="K43" s="22"/>
     </row>
@@ -36022,16 +36022,16 @@
       <c r="D44" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="65" t="s">
+      <c r="E44" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="59" t="s">
+      <c r="F44" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G44" s="61" t="s">
+      <c r="G44" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H44" s="62" t="s">
+      <c r="H44" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I44" s="55" t="s">
@@ -36040,7 +36040,7 @@
       <c r="J44" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="60" t="s">
+      <c r="K44" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -36049,13 +36049,13 @@
       <c r="B45" s="56"/>
       <c r="C45" s="56"/>
       <c r="D45" s="58"/>
-      <c r="E45" s="63"/>
+      <c r="E45" s="60"/>
       <c r="F45" s="56"/>
       <c r="G45" s="58"/>
-      <c r="H45" s="63"/>
+      <c r="H45" s="60"/>
       <c r="I45" s="56"/>
       <c r="J45" s="56"/>
-      <c r="K45" s="60"/>
+      <c r="K45" s="64"/>
     </row>
     <row r="46" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7"/>
@@ -36240,11 +36240,11 @@
       <c r="D57" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E57" s="64" t="s">
+      <c r="E57" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="64"/>
-      <c r="G57" s="64"/>
+      <c r="F57" s="65"/>
+      <c r="G57" s="65"/>
       <c r="J57" s="21"/>
       <c r="K57" s="22"/>
     </row>
@@ -36261,16 +36261,16 @@
       <c r="D58" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="65" t="s">
+      <c r="E58" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F58" s="59" t="s">
+      <c r="F58" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G58" s="61" t="s">
+      <c r="G58" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H58" s="62" t="s">
+      <c r="H58" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I58" s="55" t="s">
@@ -36279,7 +36279,7 @@
       <c r="J58" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K58" s="60" t="s">
+      <c r="K58" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -36288,13 +36288,13 @@
       <c r="B59" s="56"/>
       <c r="C59" s="56"/>
       <c r="D59" s="58"/>
-      <c r="E59" s="63"/>
+      <c r="E59" s="60"/>
       <c r="F59" s="56"/>
       <c r="G59" s="58"/>
-      <c r="H59" s="63"/>
+      <c r="H59" s="60"/>
       <c r="I59" s="56"/>
       <c r="J59" s="56"/>
-      <c r="K59" s="60"/>
+      <c r="K59" s="64"/>
     </row>
     <row r="60" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="7"/>
@@ -36481,35 +36481,25 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="K30:K31"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="H58:H59"/>
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="C30:C31"/>
@@ -36522,25 +36512,35 @@
     <mergeCell ref="E44:E45"/>
     <mergeCell ref="F44:F45"/>
     <mergeCell ref="G44:G45"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="K44:K45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="K30:K31"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E15:G15"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="6">
@@ -36588,11 +36588,11 @@
       <c r="D1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="64" t="s">
+      <c r="E1" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
       <c r="J1" s="21"/>
       <c r="K1" s="22"/>
     </row>
@@ -36609,16 +36609,16 @@
       <c r="D2" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="65" t="s">
+      <c r="E2" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="59" t="s">
+      <c r="F2" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="61" t="s">
+      <c r="G2" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="62" t="s">
+      <c r="H2" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="55" t="s">
@@ -36627,7 +36627,7 @@
       <c r="J2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="60" t="s">
+      <c r="K2" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -36636,13 +36636,13 @@
       <c r="B3" s="56"/>
       <c r="C3" s="56"/>
       <c r="D3" s="58"/>
-      <c r="E3" s="63"/>
+      <c r="E3" s="60"/>
       <c r="F3" s="56"/>
       <c r="G3" s="58"/>
-      <c r="H3" s="63"/>
+      <c r="H3" s="60"/>
       <c r="I3" s="56"/>
       <c r="J3" s="56"/>
-      <c r="K3" s="60"/>
+      <c r="K3" s="64"/>
     </row>
     <row r="4" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="7"/>
@@ -36827,11 +36827,11 @@
       <c r="D15" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="64" t="s">
+      <c r="E15" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="65"/>
       <c r="J15" s="21"/>
       <c r="K15" s="22"/>
     </row>
@@ -36848,16 +36848,16 @@
       <c r="D16" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="65" t="s">
+      <c r="E16" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="59" t="s">
+      <c r="F16" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="61" t="s">
+      <c r="G16" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="62" t="s">
+      <c r="H16" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I16" s="55" t="s">
@@ -36866,7 +36866,7 @@
       <c r="J16" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K16" s="60" t="s">
+      <c r="K16" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -36875,13 +36875,13 @@
       <c r="B17" s="56"/>
       <c r="C17" s="56"/>
       <c r="D17" s="58"/>
-      <c r="E17" s="63"/>
+      <c r="E17" s="60"/>
       <c r="F17" s="56"/>
       <c r="G17" s="58"/>
-      <c r="H17" s="63"/>
+      <c r="H17" s="60"/>
       <c r="I17" s="56"/>
       <c r="J17" s="56"/>
-      <c r="K17" s="60"/>
+      <c r="K17" s="64"/>
     </row>
     <row r="18" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7"/>
@@ -37066,11 +37066,11 @@
       <c r="D29" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="64" t="s">
+      <c r="E29" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="64"/>
-      <c r="G29" s="64"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="65"/>
       <c r="J29" s="21"/>
       <c r="K29" s="22"/>
     </row>
@@ -37087,16 +37087,16 @@
       <c r="D30" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E30" s="65" t="s">
+      <c r="E30" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F30" s="59" t="s">
+      <c r="F30" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G30" s="61" t="s">
+      <c r="G30" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="62" t="s">
+      <c r="H30" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I30" s="55" t="s">
@@ -37105,7 +37105,7 @@
       <c r="J30" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K30" s="60" t="s">
+      <c r="K30" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -37114,13 +37114,13 @@
       <c r="B31" s="56"/>
       <c r="C31" s="56"/>
       <c r="D31" s="58"/>
-      <c r="E31" s="63"/>
+      <c r="E31" s="60"/>
       <c r="F31" s="56"/>
       <c r="G31" s="58"/>
-      <c r="H31" s="63"/>
+      <c r="H31" s="60"/>
       <c r="I31" s="56"/>
       <c r="J31" s="56"/>
-      <c r="K31" s="60"/>
+      <c r="K31" s="64"/>
     </row>
     <row r="32" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7"/>
@@ -37305,11 +37305,11 @@
       <c r="D43" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="64" t="s">
+      <c r="E43" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="64"/>
-      <c r="G43" s="64"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
       <c r="J43" s="21"/>
       <c r="K43" s="22"/>
     </row>
@@ -37326,16 +37326,16 @@
       <c r="D44" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="65" t="s">
+      <c r="E44" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="59" t="s">
+      <c r="F44" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G44" s="61" t="s">
+      <c r="G44" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H44" s="62" t="s">
+      <c r="H44" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I44" s="55" t="s">
@@ -37344,7 +37344,7 @@
       <c r="J44" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K44" s="60" t="s">
+      <c r="K44" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -37353,13 +37353,13 @@
       <c r="B45" s="56"/>
       <c r="C45" s="56"/>
       <c r="D45" s="58"/>
-      <c r="E45" s="63"/>
+      <c r="E45" s="60"/>
       <c r="F45" s="56"/>
       <c r="G45" s="58"/>
-      <c r="H45" s="63"/>
+      <c r="H45" s="60"/>
       <c r="I45" s="56"/>
       <c r="J45" s="56"/>
-      <c r="K45" s="60"/>
+      <c r="K45" s="64"/>
     </row>
     <row r="46" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="7"/>
@@ -37544,11 +37544,11 @@
       <c r="D57" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E57" s="64" t="s">
+      <c r="E57" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="F57" s="64"/>
-      <c r="G57" s="64"/>
+      <c r="F57" s="65"/>
+      <c r="G57" s="65"/>
       <c r="J57" s="21"/>
       <c r="K57" s="22"/>
     </row>
@@ -37565,16 +37565,16 @@
       <c r="D58" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="E58" s="65" t="s">
+      <c r="E58" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="F58" s="59" t="s">
+      <c r="F58" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="G58" s="61" t="s">
+      <c r="G58" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="H58" s="62" t="s">
+      <c r="H58" s="63" t="s">
         <v>4</v>
       </c>
       <c r="I58" s="55" t="s">
@@ -37583,7 +37583,7 @@
       <c r="J58" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="K58" s="60" t="s">
+      <c r="K58" s="64" t="s">
         <v>7</v>
       </c>
     </row>
@@ -37592,13 +37592,13 @@
       <c r="B59" s="56"/>
       <c r="C59" s="56"/>
       <c r="D59" s="58"/>
-      <c r="E59" s="63"/>
+      <c r="E59" s="60"/>
       <c r="F59" s="56"/>
       <c r="G59" s="58"/>
-      <c r="H59" s="63"/>
+      <c r="H59" s="60"/>
       <c r="I59" s="56"/>
       <c r="J59" s="56"/>
-      <c r="K59" s="60"/>
+      <c r="K59" s="64"/>
     </row>
     <row r="60" spans="1:11" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="7"/>
@@ -37785,35 +37785,25 @@
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="K30:K31"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="H58:H59"/>
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="C30:C31"/>
@@ -37826,25 +37816,35 @@
     <mergeCell ref="E44:E45"/>
     <mergeCell ref="F44:F45"/>
     <mergeCell ref="G44:G45"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="K44:K45"/>
-    <mergeCell ref="H44:H45"/>
-    <mergeCell ref="I44:I45"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="K30:K31"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E15:G15"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations count="6">
